--- a/AuditTrail_today.xlsx
+++ b/AuditTrail_today.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>today</t>
+          <t>LabLIMSv1</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>01-Jan-2026  →  31-Mar-2026</t>
+          <t>01-Jan-2024  →  31-Mar-2026</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>993  (99.3%)</t>
+          <t>994  (99.4%)</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>4 of 7 escalated events</t>
+          <t>4 of 6 escalated events</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>3 of 7 escalated events</t>
+          <t>2 of 6 escalated events</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>0 of 7 escalated events</t>
+          <t>0 of 6 escalated events</t>
         </is>
       </c>
     </row>
@@ -1108,12 +1108,14 @@
       </c>
       <c r="B33" s="8" t="inlineStr"/>
     </row>
-    <row r="34" ht="90" customHeight="1">
+    <row r="34" ht="132" customHeight="1">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t>The audit trail for today was reviewed from 01-Jan-2026 to 31-Mar-2026. Of 1,000 recorded events, 7 were escalated for review (4 Critical, 3 High). Full dataset tier distribution is available in the Full Audit Log sheet.
-5 instances of missing or inadequate change rationale were observed across multiple records, indicating deficiencies in data attribution practices.
+          <t>The audit trail for LabLIMSv1 was reviewed from 01-Jan-2024 to 31-Mar-2026. Of 1,000 recorded events, 6 were escalated for review (4 Critical, 2 High). Full dataset tier distribution is available in the Full Audit Log sheet.
+4 instances of missing or inadequate change rationale were observed across multiple records, indicating deficiencies in data attribution practices.
 A system administrator (admin_sys) directly modified production BATCH_RELEASE data on record BATCH-999, which is inconsistent with Segregation of Duties expectations under 21 CFR Part 11 §11.10(d).
+Non-personal account 'analyst_x' performed a DELETE action on RESULTS on record RES-5050. This action cannot be attributed to a specific individual.
+A delete-and-recreate pattern was identified on record RES-8888 by user 'analyst_y', a known method for circumventing locked record controls.
 Overall, the system presents a high risk to data integrity and requires immediate corrective actions, particularly in access control and audit trail integrity.</t>
         </is>
       </c>
@@ -1129,7 +1131,7 @@
     <row r="37" ht="72" customHeight="1">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>This audit trail review was performed using rule-based anomaly detection with system-generated narrative summaries. All risk classifications are derived from deterministic rules; narrative text does not influence risk scoring or tier assignment. 1,000 records were reviewed across the period 01-Jan-2026 to 31-Mar-2026. 99.3% of records were automatically cleared as low risk. The 7 records requiring review are documented in the 'Events for Review' sheet. Each finding has been independently reviewed and dispositioned by the undersigned reviewer. The 'System-Proposed Disposition' column is informational only; the reviewer's determination in the 'Reviewer Decision' column reflects independent human judgement and is the authoritative record. Regulatory basis: 21 CFR Part 11 §11.10(e) and EU Annex 11 Clause 9.
+          <t>This audit trail review was performed using rule-based anomaly detection with system-generated narrative summaries. All risk classifications are derived from deterministic rules; narrative text does not influence risk scoring or tier assignment. 1,000 records were reviewed across the period 01-Jan-2024 to 31-Mar-2026. 99.4% of records were automatically cleared as low risk. The 6 records requiring review are documented in the 'Events for Review' sheet. Each finding has been independently reviewed and dispositioned by the undersigned reviewer. The 'System-Proposed Disposition' column is informational only; the reviewer's determination in the 'Reviewer Decision' column reflects independent human judgement and is the authoritative record. Regulatory basis: 21 CFR Part 11 §11.10(e) and EU Annex 11 Clause 9.
 Timezone note: Off-hours scoring (Rule 11) assumes all timestamps in the uploaded file are in the same timezone. If your system exports timestamps in UTC or a non-local timezone, off-hours flags should be interpreted accordingly. Reviewers should verify local shift patterns before dispositing temporal anomalies.</t>
         </is>
       </c>
@@ -1187,7 +1189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1559,75 +1561,75 @@
       <c r="A5" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="C5" s="24" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
       <c r="D5" s="24" t="inlineStr">
         <is>
-          <t>2026-07-04 11:00:00</t>
+          <t>2026-03-23 09:00:00</t>
         </is>
       </c>
       <c r="E5" s="24" t="inlineStr">
         <is>
-          <t>analyst_y</t>
+          <t>admin_sys</t>
         </is>
       </c>
       <c r="F5" s="24" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>INSERT</t>
         </is>
       </c>
       <c r="G5" s="24" t="inlineStr">
         <is>
-          <t>RESULTS</t>
+          <t>BATCH_RELEASE</t>
         </is>
       </c>
       <c r="H5" s="24" t="inlineStr">
         <is>
-          <t>RES-1500</t>
+          <t>BATCH-999</t>
         </is>
       </c>
       <c r="I5" s="24" t="inlineStr">
         <is>
-          <t>Holiday work</t>
+          <t>Urgent release</t>
         </is>
       </c>
       <c r="J5" s="24" t="inlineStr">
         <is>
-          <t>Rule 14 — Dormant Account Sudden Activity [HIGH]</t>
+          <t>Rule 3 — Admin/GxP Conflict [CRITICAL]</t>
         </is>
       </c>
       <c r="K5" s="24" t="inlineStr"/>
       <c r="L5" s="24" t="inlineStr">
         <is>
-          <t>21 CFR Part 11 §11.10(d) — User access rights must be reviewed periodically and must be formally re-authorised following extended periods of inactivity.</t>
+          <t>21 CFR Part 11 §11.10(d); Segregation of Duties principle — Administrative accounts are authorised for system configuration only and must not directly create or modify GxP production records.</t>
         </is>
       </c>
       <c r="M5" s="24" t="inlineStr">
         <is>
-          <t>analyst_y performed UPDATE on RESULTS/RES-1500 at 11:00 on 04-Jul-2026; comment reads "Holiday work".</t>
+          <t>admin_sys performed INSERT on BATCH_RELEASE/BATCH-999 at 09:00 on 23-Mar-2026; comment reads "Urgent release".</t>
         </is>
       </c>
       <c r="N5" s="24" t="inlineStr">
         <is>
-          <t>Verify the current employment and access authorisation status of this user. Confirm whether access was formally reviewed and re-approved before this re-activation. If no re-authorisation record exists, assess this event for data integrity impact.</t>
-        </is>
-      </c>
-      <c r="O5" s="26" t="inlineStr">
-        <is>
-          <t>Investigate — Verify Source Data</t>
+          <t>Obtain documented business justification for this administrative action on production data. Verify whether an Emergency Access Request was approved prior to this action. If no documented authorisation exists, assess impact on GxP record integrity and raise a non-conformance.</t>
+        </is>
+      </c>
+      <c r="O5" s="20" t="inlineStr">
+        <is>
+          <t>Escalate to CAPA</t>
         </is>
       </c>
       <c r="P5" s="21" t="inlineStr">
         <is>
-          <t>A gap in audit trail coverage was detected — verify whether this aligns with an approved maintenance window or scheduled system downtime.</t>
+          <t>An administrative account directly modified production GxP data — administrative accounts are authorised for system configuration only, not direct data modification.</t>
         </is>
       </c>
       <c r="Q5" s="22" t="inlineStr">
@@ -1641,75 +1643,75 @@
       <c r="A6" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>2026-03-23 09:00:00</t>
+          <t>2026-03-23 10:15:00</t>
         </is>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
-          <t>admin_sys</t>
+          <t>analyst_x</t>
         </is>
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
-          <t>INSERT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="G6" s="16" t="inlineStr">
         <is>
-          <t>BATCH_RELEASE</t>
+          <t>RESULTS</t>
         </is>
       </c>
       <c r="H6" s="16" t="inlineStr">
         <is>
-          <t>BATCH-999</t>
+          <t>RES-5050</t>
         </is>
       </c>
       <c r="I6" s="16" t="inlineStr">
         <is>
-          <t>Urgent release</t>
+          <t>Cleaning up error</t>
         </is>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>Rule 3 — Admin/GxP Conflict [CRITICAL]</t>
+          <t>Rule 1 — Vague Rationale [HIGH]</t>
         </is>
       </c>
       <c r="K6" s="16" t="inlineStr"/>
       <c r="L6" s="16" t="inlineStr">
         <is>
-          <t>21 CFR Part 11 §11.10(d); Segregation of Duties principle — Administrative accounts are authorised for system configuration only and must not directly create or modify GxP production records.</t>
+          <t>ALCOA+ Attributable and Legible principles; FDA Data Integrity Guidance (2018) — GxP data changes must be accompanied by a specific, scientifically justified rationale attributable to the performing individual.</t>
         </is>
       </c>
       <c r="M6" s="16" t="inlineStr">
         <is>
-          <t>admin_sys performed INSERT on BATCH_RELEASE/BATCH-999 at 09:00 on 23-Mar-2026; comment reads "Urgent release".</t>
+          <t>analyst_x performed DELETE on RESULTS/RES-5050 at 10:15 on 23-Mar-2026; comment reads "Cleaning up error".</t>
         </is>
       </c>
       <c r="N6" s="16" t="inlineStr">
         <is>
-          <t>Obtain documented business justification for this administrative action on production data. Verify whether an Emergency Access Request was approved prior to this action. If no documented authorisation exists, assess impact on GxP record integrity and raise a non-conformance.</t>
-        </is>
-      </c>
-      <c r="O6" s="20" t="inlineStr">
-        <is>
-          <t>Escalate to CAPA</t>
+          <t>Obtain a retrospective written amendment from the analyst explaining what changed and why. Assess whether the undocumented change could affect the quality or disposition of the associated batch or result.</t>
+        </is>
+      </c>
+      <c r="O6" s="27" t="inlineStr">
+        <is>
+          <t>Amendment Required</t>
         </is>
       </c>
       <c r="P6" s="21" t="inlineStr">
         <is>
-          <t>An administrative account directly modified production GxP data — administrative accounts are authorised for system configuration only, not direct data modification.</t>
+          <t>The change reason recorded is insufficient or uses non-descriptive language — a retrospective written amendment from the analyst is required.</t>
         </is>
       </c>
       <c r="Q6" s="22" t="inlineStr">
@@ -1723,29 +1725,29 @@
       <c r="A7" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
-          <t>2026-03-23 10:15:00</t>
+          <t>2026-03-23 18:15:00</t>
         </is>
       </c>
       <c r="E7" s="24" t="inlineStr">
         <is>
-          <t>analyst_x</t>
+          <t>analyst_y</t>
         </is>
       </c>
       <c r="F7" s="24" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>INSERT</t>
         </is>
       </c>
       <c r="G7" s="24" t="inlineStr">
@@ -1755,43 +1757,47 @@
       </c>
       <c r="H7" s="24" t="inlineStr">
         <is>
-          <t>RES-5050</t>
+          <t>RES-8888</t>
         </is>
       </c>
       <c r="I7" s="24" t="inlineStr">
         <is>
-          <t>Cleaning up error</t>
+          <t>Correction</t>
         </is>
       </c>
       <c r="J7" s="24" t="inlineStr">
         <is>
-          <t>Rule 1 — Vague Rationale [HIGH]</t>
-        </is>
-      </c>
-      <c r="K7" s="24" t="inlineStr"/>
+          <t>Rule 6 — Record Reconstruction Pattern [CRITICAL]</t>
+        </is>
+      </c>
+      <c r="K7" s="24" t="inlineStr">
+        <is>
+          <t>Part of delete-recreate sequence — record (RES-8888) recreated here after deletion</t>
+        </is>
+      </c>
       <c r="L7" s="24" t="inlineStr">
         <is>
-          <t>ALCOA+ Attributable and Legible principles; FDA Data Integrity Guidance (2018) — GxP data changes must be accompanied by a specific, scientifically justified rationale attributable to the performing individual.</t>
+          <t>ALCOA+ Original principle; 21 CFR Part 11 §11.10(e) — GxP data must not be altered by deleting and recreating records. Tier 1 (D→I): DELETE then INSERT on same record — score 9.0. Tier 2 (U→D→I): UPDATE then DELETE then INSERT — score 9.5, indicating deliberate evasion: the actor modified, then destroyed the modification history, then recreated the record.</t>
         </is>
       </c>
       <c r="M7" s="24" t="inlineStr">
         <is>
-          <t>analyst_x performed DELETE on RESULTS/RES-5050 at 10:15 on 23-Mar-2026; comment reads "Cleaning up error".</t>
+          <t>analyst_y performed INSERT on RESULTS/RES-8888 at 18:15 on 23-Mar-2026 with comment "Correction"; record was recreated after deletion in delete-recreate sequence.</t>
         </is>
       </c>
       <c r="N7" s="24" t="inlineStr">
         <is>
-          <t>Obtain a retrospective written amendment from the analyst explaining what changed and why. Assess whether the undocumented change could affect the quality or disposition of the associated batch or result.</t>
-        </is>
-      </c>
-      <c r="O7" s="27" t="inlineStr">
-        <is>
-          <t>Amendment Required</t>
+          <t>Retrieve both the original deleted record and the recreated record. Compare all field values for discrepancies. Obtain a retrospective written explanation from the user. If the change cannot be justified, initiate a data integrity investigation.</t>
+        </is>
+      </c>
+      <c r="O7" s="20" t="inlineStr">
+        <is>
+          <t>Escalate to CAPA</t>
         </is>
       </c>
       <c r="P7" s="21" t="inlineStr">
         <is>
-          <t>The change reason recorded is insufficient or uses non-descriptive language — a retrospective written amendment from the analyst is required.</t>
+          <t>Update, Delete, and re-Insert were performed on the same record within 30 minutes — this sequence is the primary method for altering locked GxP records while obscuring the original data.</t>
         </is>
       </c>
       <c r="Q7" s="22" t="inlineStr">
@@ -1800,92 +1806,6 @@
         </is>
       </c>
       <c r="R7" s="22" t="inlineStr"/>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>2026-03-23 18:15:00</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>analyst_y</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>INSERT</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>RESULTS</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>RES-8888</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>Correction</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>Rule 6 — Record Reconstruction Pattern [CRITICAL]</t>
-        </is>
-      </c>
-      <c r="K8" s="16" t="inlineStr">
-        <is>
-          <t>Part of delete-recreate sequence — record (RES-8888) recreated here after deletion</t>
-        </is>
-      </c>
-      <c r="L8" s="16" t="inlineStr">
-        <is>
-          <t>ALCOA+ Original principle; 21 CFR Part 11 §11.10(e) — GxP data must not be altered by deleting and recreating records. Tier 1 (D→I): DELETE then INSERT on same record — score 9.0. Tier 2 (U→D→I): UPDATE then DELETE then INSERT — score 9.5, indicating deliberate evasion: the actor modified, then destroyed the modification history, then recreated the record.</t>
-        </is>
-      </c>
-      <c r="M8" s="16" t="inlineStr">
-        <is>
-          <t>analyst_y performed INSERT on RESULTS/RES-8888 at 18:15 on 23-Mar-2026 as part of delete-recreate sequence; comment reads "Correction".</t>
-        </is>
-      </c>
-      <c r="N8" s="16" t="inlineStr">
-        <is>
-          <t>Retrieve both the original deleted record and the recreated record. Compare all field values for discrepancies. Obtain a retrospective written explanation from the user. If the change cannot be justified, initiate a data integrity investigation.</t>
-        </is>
-      </c>
-      <c r="O8" s="20" t="inlineStr">
-        <is>
-          <t>Escalate to CAPA</t>
-        </is>
-      </c>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t>Update, Delete, and re-Insert were performed on the same record within 30 minutes — this sequence is the primary method for altering locked GxP records while obscuring the original data.</t>
-        </is>
-      </c>
-      <c r="Q8" s="22" t="inlineStr">
-        <is>
-          <t>☐ Justified     ☐ Escalate to CAPA     ☐ False Positive</t>
-        </is>
-      </c>
-      <c r="R8" s="22" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:R1"/>
@@ -2021,7 +1941,7 @@
       </c>
       <c r="J2" s="29" t="inlineStr">
         <is>
-          <t>Rule 7 — Audit Trail Integrity Event; Rule 8 — Privileged User on GxP Data; Rule 13 — Service/Shared Account Action</t>
+          <t>Rule 7 — Audit Trail Integrity Event; Rule 8 — Privileged User on GxP Data; Rule 12 — Service/Shared Account Action</t>
         </is>
       </c>
       <c r="K2" s="29" t="inlineStr"/>
@@ -2074,7 +1994,7 @@
       </c>
       <c r="J3" s="31" t="inlineStr">
         <is>
-          <t>Rule 1 — Vague Rationale; Rule 6 — Record Reconstruction Pattern; Rule 16 — First-Time Behavior</t>
+          <t>Rule 1 — Vague Rationale; Rule 6 — Record Reconstruction Pattern; Rule 13 — First-Time Behavior</t>
         </is>
       </c>
       <c r="K3" s="31" t="inlineStr">
@@ -2131,7 +2051,7 @@
       </c>
       <c r="J4" s="29" t="inlineStr">
         <is>
-          <t>Rule 1 — Vague Rationale; Rule 4 — Change Control Drift; Rule 11 — Off-Hours Activity</t>
+          <t>Rule 1 — Vague Rationale; Rule 4 — Change Control Drift; Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K4" s="29" t="inlineStr"/>
@@ -2167,9 +2087,9 @@
           <t>Holiday work</t>
         </is>
       </c>
-      <c r="G5" s="32" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="G5" s="31" t="inlineStr">
+        <is>
+          <t>Out of Period</t>
         </is>
       </c>
       <c r="H5" s="31" t="inlineStr">
@@ -2179,12 +2099,12 @@
       </c>
       <c r="I5" s="31" t="inlineStr">
         <is>
-          <t>Rule 14 — Dormant Account Sudden Activity [HIGH]</t>
+          <t>Out of Period — excluded from review scope</t>
         </is>
       </c>
       <c r="J5" s="31" t="inlineStr">
         <is>
-          <t>Rule 10 — Audit Trail Timestamp Gap; Rule 11 — Off-Hours Activity; Rule 14 — Dormant Account Sudden Activity</t>
+          <t>Rule 9 — Audit Trail Timestamp Gap; Rule 10 — Off-Hours Activity; Rule 13 — Dormant Account Sudden Activity</t>
         </is>
       </c>
       <c r="K5" s="31" t="inlineStr"/>
@@ -2290,7 +2210,7 @@
       </c>
       <c r="J7" s="31" t="inlineStr">
         <is>
-          <t>Rule 1 — Vague Rationale; Rule 16 — First-Time Behavior</t>
+          <t>Rule 1 — Vague Rationale; Rule 13 — First-Time Behavior</t>
         </is>
       </c>
       <c r="K7" s="31" t="inlineStr"/>
@@ -3186,12 +3106,12 @@
       </c>
       <c r="I24" s="29" t="inlineStr">
         <is>
-          <t>Rule 10 — Audit Trail Timestamp Gap [MEDIUM]</t>
+          <t>Rule 9 — Audit Trail Timestamp Gap [MEDIUM]</t>
         </is>
       </c>
       <c r="J24" s="29" t="inlineStr">
         <is>
-          <t>Rule 10 — Audit Trail Timestamp Gap; Rule 11 — Off-Hours Activity</t>
+          <t>Rule 9 — Audit Trail Timestamp Gap; Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K24" s="29" t="inlineStr"/>
@@ -3239,12 +3159,12 @@
       </c>
       <c r="I25" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J25" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K25" s="31" t="inlineStr"/>
@@ -3292,12 +3212,12 @@
       </c>
       <c r="I26" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J26" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K26" s="29" t="inlineStr"/>
@@ -3345,12 +3265,12 @@
       </c>
       <c r="I27" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J27" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K27" s="31" t="inlineStr"/>
@@ -3398,12 +3318,12 @@
       </c>
       <c r="I28" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J28" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K28" s="29" t="inlineStr"/>
@@ -3451,12 +3371,12 @@
       </c>
       <c r="I29" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J29" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K29" s="31" t="inlineStr"/>
@@ -3504,12 +3424,12 @@
       </c>
       <c r="I30" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J30" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K30" s="29" t="inlineStr"/>
@@ -3557,12 +3477,12 @@
       </c>
       <c r="I31" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J31" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K31" s="31" t="inlineStr"/>
@@ -3610,12 +3530,12 @@
       </c>
       <c r="I32" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J32" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K32" s="29" t="inlineStr"/>
@@ -3663,12 +3583,12 @@
       </c>
       <c r="I33" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J33" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K33" s="31" t="inlineStr"/>
@@ -3716,12 +3636,12 @@
       </c>
       <c r="I34" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J34" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K34" s="29" t="inlineStr"/>
@@ -3769,12 +3689,12 @@
       </c>
       <c r="I35" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J35" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K35" s="31" t="inlineStr"/>
@@ -3822,12 +3742,12 @@
       </c>
       <c r="I36" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J36" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K36" s="29" t="inlineStr"/>
@@ -3875,12 +3795,12 @@
       </c>
       <c r="I37" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J37" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K37" s="31" t="inlineStr"/>
@@ -3928,12 +3848,12 @@
       </c>
       <c r="I38" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J38" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K38" s="29" t="inlineStr"/>
@@ -3981,12 +3901,12 @@
       </c>
       <c r="I39" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J39" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K39" s="31" t="inlineStr"/>
@@ -4034,12 +3954,12 @@
       </c>
       <c r="I40" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J40" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K40" s="29" t="inlineStr"/>
@@ -4087,12 +4007,12 @@
       </c>
       <c r="I41" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J41" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K41" s="31" t="inlineStr"/>
@@ -4140,12 +4060,12 @@
       </c>
       <c r="I42" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J42" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K42" s="29" t="inlineStr"/>
@@ -4193,12 +4113,12 @@
       </c>
       <c r="I43" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J43" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K43" s="31" t="inlineStr"/>
@@ -4246,12 +4166,12 @@
       </c>
       <c r="I44" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J44" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K44" s="29" t="inlineStr"/>
@@ -4299,12 +4219,12 @@
       </c>
       <c r="I45" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J45" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K45" s="31" t="inlineStr"/>
@@ -4352,12 +4272,12 @@
       </c>
       <c r="I46" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J46" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K46" s="29" t="inlineStr"/>
@@ -4405,12 +4325,12 @@
       </c>
       <c r="I47" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J47" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K47" s="31" t="inlineStr"/>
@@ -4458,12 +4378,12 @@
       </c>
       <c r="I48" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J48" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K48" s="29" t="inlineStr"/>
@@ -4511,12 +4431,12 @@
       </c>
       <c r="I49" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J49" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K49" s="31" t="inlineStr"/>
@@ -4564,12 +4484,12 @@
       </c>
       <c r="I50" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J50" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K50" s="29" t="inlineStr"/>
@@ -4617,12 +4537,12 @@
       </c>
       <c r="I51" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J51" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K51" s="31" t="inlineStr"/>
@@ -4670,12 +4590,12 @@
       </c>
       <c r="I52" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J52" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K52" s="29" t="inlineStr"/>
@@ -4723,12 +4643,12 @@
       </c>
       <c r="I53" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J53" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K53" s="31" t="inlineStr"/>
@@ -4776,12 +4696,12 @@
       </c>
       <c r="I54" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J54" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K54" s="29" t="inlineStr"/>
@@ -4829,12 +4749,12 @@
       </c>
       <c r="I55" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J55" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K55" s="31" t="inlineStr"/>
@@ -4882,12 +4802,12 @@
       </c>
       <c r="I56" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J56" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K56" s="29" t="inlineStr"/>
@@ -4935,12 +4855,12 @@
       </c>
       <c r="I57" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J57" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K57" s="31" t="inlineStr"/>
@@ -4988,12 +4908,12 @@
       </c>
       <c r="I58" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J58" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K58" s="29" t="inlineStr"/>
@@ -5041,12 +4961,12 @@
       </c>
       <c r="I59" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J59" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K59" s="31" t="inlineStr"/>
@@ -5094,12 +5014,12 @@
       </c>
       <c r="I60" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J60" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K60" s="29" t="inlineStr"/>
@@ -5147,12 +5067,12 @@
       </c>
       <c r="I61" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J61" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K61" s="31" t="inlineStr"/>
@@ -5200,12 +5120,12 @@
       </c>
       <c r="I62" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J62" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K62" s="29" t="inlineStr"/>
@@ -5253,12 +5173,12 @@
       </c>
       <c r="I63" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J63" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K63" s="31" t="inlineStr"/>
@@ -5306,12 +5226,12 @@
       </c>
       <c r="I64" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J64" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K64" s="29" t="inlineStr"/>
@@ -5359,12 +5279,12 @@
       </c>
       <c r="I65" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J65" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K65" s="31" t="inlineStr"/>
@@ -5412,12 +5332,12 @@
       </c>
       <c r="I66" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J66" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K66" s="29" t="inlineStr"/>
@@ -5465,12 +5385,12 @@
       </c>
       <c r="I67" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J67" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K67" s="31" t="inlineStr"/>
@@ -5518,12 +5438,12 @@
       </c>
       <c r="I68" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J68" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K68" s="29" t="inlineStr"/>
@@ -5571,12 +5491,12 @@
       </c>
       <c r="I69" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J69" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K69" s="31" t="inlineStr"/>
@@ -5624,12 +5544,12 @@
       </c>
       <c r="I70" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J70" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K70" s="29" t="inlineStr"/>
@@ -5677,12 +5597,12 @@
       </c>
       <c r="I71" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J71" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K71" s="31" t="inlineStr"/>
@@ -5730,12 +5650,12 @@
       </c>
       <c r="I72" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J72" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K72" s="29" t="inlineStr"/>
@@ -5783,12 +5703,12 @@
       </c>
       <c r="I73" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J73" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K73" s="31" t="inlineStr"/>
@@ -5836,12 +5756,12 @@
       </c>
       <c r="I74" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J74" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K74" s="29" t="inlineStr"/>
@@ -5889,12 +5809,12 @@
       </c>
       <c r="I75" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J75" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K75" s="31" t="inlineStr"/>
@@ -5942,12 +5862,12 @@
       </c>
       <c r="I76" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J76" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K76" s="29" t="inlineStr"/>
@@ -5995,12 +5915,12 @@
       </c>
       <c r="I77" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J77" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K77" s="31" t="inlineStr"/>
@@ -6048,12 +5968,12 @@
       </c>
       <c r="I78" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J78" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K78" s="29" t="inlineStr"/>
@@ -6101,12 +6021,12 @@
       </c>
       <c r="I79" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J79" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K79" s="31" t="inlineStr"/>
@@ -6154,12 +6074,12 @@
       </c>
       <c r="I80" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J80" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K80" s="29" t="inlineStr"/>
@@ -6207,12 +6127,12 @@
       </c>
       <c r="I81" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J81" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K81" s="31" t="inlineStr"/>
@@ -6260,12 +6180,12 @@
       </c>
       <c r="I82" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J82" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K82" s="29" t="inlineStr"/>
@@ -6313,12 +6233,12 @@
       </c>
       <c r="I83" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J83" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K83" s="31" t="inlineStr"/>
@@ -6366,12 +6286,12 @@
       </c>
       <c r="I84" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J84" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K84" s="29" t="inlineStr"/>
@@ -6419,12 +6339,12 @@
       </c>
       <c r="I85" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J85" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K85" s="31" t="inlineStr"/>
@@ -6472,12 +6392,12 @@
       </c>
       <c r="I86" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J86" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K86" s="29" t="inlineStr"/>
@@ -6525,12 +6445,12 @@
       </c>
       <c r="I87" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J87" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K87" s="31" t="inlineStr"/>
@@ -6578,12 +6498,12 @@
       </c>
       <c r="I88" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J88" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K88" s="29" t="inlineStr"/>
@@ -6631,12 +6551,12 @@
       </c>
       <c r="I89" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J89" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K89" s="31" t="inlineStr"/>
@@ -6684,12 +6604,12 @@
       </c>
       <c r="I90" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J90" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K90" s="29" t="inlineStr"/>
@@ -6737,12 +6657,12 @@
       </c>
       <c r="I91" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J91" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K91" s="31" t="inlineStr"/>
@@ -6790,12 +6710,12 @@
       </c>
       <c r="I92" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J92" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K92" s="29" t="inlineStr"/>
@@ -6843,12 +6763,12 @@
       </c>
       <c r="I93" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J93" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K93" s="31" t="inlineStr"/>
@@ -6896,12 +6816,12 @@
       </c>
       <c r="I94" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J94" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K94" s="29" t="inlineStr"/>
@@ -6949,12 +6869,12 @@
       </c>
       <c r="I95" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J95" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K95" s="31" t="inlineStr"/>
@@ -7002,12 +6922,12 @@
       </c>
       <c r="I96" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J96" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K96" s="29" t="inlineStr"/>
@@ -7055,12 +6975,12 @@
       </c>
       <c r="I97" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J97" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K97" s="31" t="inlineStr"/>
@@ -7108,12 +7028,12 @@
       </c>
       <c r="I98" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J98" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K98" s="29" t="inlineStr"/>
@@ -7161,12 +7081,12 @@
       </c>
       <c r="I99" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J99" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K99" s="31" t="inlineStr"/>
@@ -7214,12 +7134,12 @@
       </c>
       <c r="I100" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J100" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K100" s="29" t="inlineStr"/>
@@ -7267,12 +7187,12 @@
       </c>
       <c r="I101" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J101" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K101" s="31" t="inlineStr"/>
@@ -7320,12 +7240,12 @@
       </c>
       <c r="I102" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J102" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K102" s="29" t="inlineStr"/>
@@ -7373,12 +7293,12 @@
       </c>
       <c r="I103" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J103" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K103" s="31" t="inlineStr"/>
@@ -7426,12 +7346,12 @@
       </c>
       <c r="I104" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J104" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K104" s="29" t="inlineStr"/>
@@ -7479,12 +7399,12 @@
       </c>
       <c r="I105" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J105" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K105" s="31" t="inlineStr"/>
@@ -7532,12 +7452,12 @@
       </c>
       <c r="I106" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J106" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K106" s="29" t="inlineStr"/>
@@ -7585,12 +7505,12 @@
       </c>
       <c r="I107" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J107" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K107" s="31" t="inlineStr"/>
@@ -7638,12 +7558,12 @@
       </c>
       <c r="I108" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J108" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K108" s="29" t="inlineStr"/>
@@ -7691,12 +7611,12 @@
       </c>
       <c r="I109" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J109" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K109" s="31" t="inlineStr"/>
@@ -7744,12 +7664,12 @@
       </c>
       <c r="I110" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J110" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K110" s="29" t="inlineStr"/>
@@ -7797,12 +7717,12 @@
       </c>
       <c r="I111" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J111" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K111" s="31" t="inlineStr"/>
@@ -7850,12 +7770,12 @@
       </c>
       <c r="I112" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J112" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K112" s="29" t="inlineStr"/>
@@ -7903,12 +7823,12 @@
       </c>
       <c r="I113" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J113" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K113" s="31" t="inlineStr"/>
@@ -7956,12 +7876,12 @@
       </c>
       <c r="I114" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J114" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K114" s="29" t="inlineStr"/>
@@ -8009,12 +7929,12 @@
       </c>
       <c r="I115" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J115" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K115" s="31" t="inlineStr"/>
@@ -8062,12 +7982,12 @@
       </c>
       <c r="I116" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J116" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K116" s="29" t="inlineStr"/>
@@ -8115,12 +8035,12 @@
       </c>
       <c r="I117" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J117" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K117" s="31" t="inlineStr"/>
@@ -8168,12 +8088,12 @@
       </c>
       <c r="I118" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J118" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K118" s="29" t="inlineStr"/>
@@ -8221,12 +8141,12 @@
       </c>
       <c r="I119" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J119" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K119" s="31" t="inlineStr"/>
@@ -8274,12 +8194,12 @@
       </c>
       <c r="I120" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J120" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K120" s="29" t="inlineStr"/>
@@ -8327,12 +8247,12 @@
       </c>
       <c r="I121" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J121" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K121" s="31" t="inlineStr"/>
@@ -8380,12 +8300,12 @@
       </c>
       <c r="I122" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J122" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K122" s="29" t="inlineStr"/>
@@ -8433,12 +8353,12 @@
       </c>
       <c r="I123" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J123" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K123" s="31" t="inlineStr"/>
@@ -8486,12 +8406,12 @@
       </c>
       <c r="I124" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J124" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K124" s="29" t="inlineStr"/>
@@ -8539,12 +8459,12 @@
       </c>
       <c r="I125" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J125" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K125" s="31" t="inlineStr"/>
@@ -8592,12 +8512,12 @@
       </c>
       <c r="I126" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J126" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K126" s="29" t="inlineStr"/>
@@ -8645,12 +8565,12 @@
       </c>
       <c r="I127" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J127" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K127" s="31" t="inlineStr"/>
@@ -8698,12 +8618,12 @@
       </c>
       <c r="I128" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J128" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K128" s="29" t="inlineStr"/>
@@ -8751,12 +8671,12 @@
       </c>
       <c r="I129" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J129" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K129" s="31" t="inlineStr"/>
@@ -8804,12 +8724,12 @@
       </c>
       <c r="I130" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J130" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K130" s="29" t="inlineStr"/>
@@ -8857,12 +8777,12 @@
       </c>
       <c r="I131" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J131" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K131" s="31" t="inlineStr"/>
@@ -8910,12 +8830,12 @@
       </c>
       <c r="I132" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J132" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K132" s="29" t="inlineStr"/>
@@ -8963,12 +8883,12 @@
       </c>
       <c r="I133" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J133" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K133" s="31" t="inlineStr"/>
@@ -9016,12 +8936,12 @@
       </c>
       <c r="I134" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J134" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K134" s="29" t="inlineStr"/>
@@ -9069,12 +8989,12 @@
       </c>
       <c r="I135" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J135" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K135" s="31" t="inlineStr"/>
@@ -9122,12 +9042,12 @@
       </c>
       <c r="I136" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J136" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K136" s="29" t="inlineStr"/>
@@ -9175,12 +9095,12 @@
       </c>
       <c r="I137" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J137" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K137" s="31" t="inlineStr"/>
@@ -9228,12 +9148,12 @@
       </c>
       <c r="I138" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J138" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K138" s="29" t="inlineStr"/>
@@ -9281,12 +9201,12 @@
       </c>
       <c r="I139" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J139" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K139" s="31" t="inlineStr"/>
@@ -9334,12 +9254,12 @@
       </c>
       <c r="I140" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J140" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K140" s="29" t="inlineStr"/>
@@ -9387,12 +9307,12 @@
       </c>
       <c r="I141" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J141" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K141" s="31" t="inlineStr"/>
@@ -9440,12 +9360,12 @@
       </c>
       <c r="I142" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J142" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K142" s="29" t="inlineStr"/>
@@ -9493,12 +9413,12 @@
       </c>
       <c r="I143" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J143" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K143" s="31" t="inlineStr"/>
@@ -9546,12 +9466,12 @@
       </c>
       <c r="I144" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J144" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K144" s="29" t="inlineStr"/>
@@ -9599,12 +9519,12 @@
       </c>
       <c r="I145" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J145" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K145" s="31" t="inlineStr"/>
@@ -9652,12 +9572,12 @@
       </c>
       <c r="I146" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J146" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K146" s="29" t="inlineStr"/>
@@ -9705,12 +9625,12 @@
       </c>
       <c r="I147" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J147" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K147" s="31" t="inlineStr"/>
@@ -9758,12 +9678,12 @@
       </c>
       <c r="I148" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J148" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K148" s="29" t="inlineStr"/>
@@ -9811,12 +9731,12 @@
       </c>
       <c r="I149" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J149" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K149" s="31" t="inlineStr"/>
@@ -9864,12 +9784,12 @@
       </c>
       <c r="I150" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J150" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K150" s="29" t="inlineStr"/>
@@ -9917,12 +9837,12 @@
       </c>
       <c r="I151" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J151" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K151" s="31" t="inlineStr"/>
@@ -9970,12 +9890,12 @@
       </c>
       <c r="I152" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J152" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K152" s="29" t="inlineStr"/>
@@ -10023,12 +9943,12 @@
       </c>
       <c r="I153" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J153" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K153" s="31" t="inlineStr"/>
@@ -10076,12 +9996,12 @@
       </c>
       <c r="I154" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J154" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K154" s="29" t="inlineStr"/>
@@ -10129,12 +10049,12 @@
       </c>
       <c r="I155" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J155" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K155" s="31" t="inlineStr"/>
@@ -10182,12 +10102,12 @@
       </c>
       <c r="I156" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J156" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K156" s="29" t="inlineStr"/>
@@ -10235,12 +10155,12 @@
       </c>
       <c r="I157" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J157" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K157" s="31" t="inlineStr"/>
@@ -10288,12 +10208,12 @@
       </c>
       <c r="I158" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J158" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K158" s="29" t="inlineStr"/>
@@ -10341,12 +10261,12 @@
       </c>
       <c r="I159" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J159" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K159" s="31" t="inlineStr"/>
@@ -10394,12 +10314,12 @@
       </c>
       <c r="I160" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J160" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K160" s="29" t="inlineStr"/>
@@ -10447,12 +10367,12 @@
       </c>
       <c r="I161" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J161" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K161" s="31" t="inlineStr"/>
@@ -10500,12 +10420,12 @@
       </c>
       <c r="I162" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J162" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K162" s="29" t="inlineStr"/>
@@ -10553,12 +10473,12 @@
       </c>
       <c r="I163" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J163" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K163" s="31" t="inlineStr"/>
@@ -10606,12 +10526,12 @@
       </c>
       <c r="I164" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J164" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K164" s="29" t="inlineStr"/>
@@ -10659,12 +10579,12 @@
       </c>
       <c r="I165" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J165" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K165" s="31" t="inlineStr"/>
@@ -10712,12 +10632,12 @@
       </c>
       <c r="I166" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J166" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K166" s="29" t="inlineStr"/>
@@ -10765,12 +10685,12 @@
       </c>
       <c r="I167" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J167" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K167" s="31" t="inlineStr"/>
@@ -10818,12 +10738,12 @@
       </c>
       <c r="I168" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J168" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K168" s="29" t="inlineStr"/>
@@ -10871,12 +10791,12 @@
       </c>
       <c r="I169" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J169" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K169" s="31" t="inlineStr"/>
@@ -10924,12 +10844,12 @@
       </c>
       <c r="I170" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J170" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K170" s="29" t="inlineStr"/>
@@ -10977,12 +10897,12 @@
       </c>
       <c r="I171" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J171" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K171" s="31" t="inlineStr"/>
@@ -11030,12 +10950,12 @@
       </c>
       <c r="I172" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J172" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K172" s="29" t="inlineStr"/>
@@ -11083,12 +11003,12 @@
       </c>
       <c r="I173" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J173" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K173" s="31" t="inlineStr"/>
@@ -11136,12 +11056,12 @@
       </c>
       <c r="I174" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J174" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K174" s="29" t="inlineStr"/>
@@ -11189,12 +11109,12 @@
       </c>
       <c r="I175" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J175" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K175" s="31" t="inlineStr"/>
@@ -11242,12 +11162,12 @@
       </c>
       <c r="I176" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J176" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K176" s="29" t="inlineStr"/>
@@ -11295,12 +11215,12 @@
       </c>
       <c r="I177" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J177" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K177" s="31" t="inlineStr"/>
@@ -11348,12 +11268,12 @@
       </c>
       <c r="I178" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J178" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K178" s="29" t="inlineStr"/>
@@ -11401,12 +11321,12 @@
       </c>
       <c r="I179" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J179" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K179" s="31" t="inlineStr"/>
@@ -11454,12 +11374,12 @@
       </c>
       <c r="I180" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J180" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K180" s="29" t="inlineStr"/>
@@ -11507,12 +11427,12 @@
       </c>
       <c r="I181" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J181" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K181" s="31" t="inlineStr"/>
@@ -11560,12 +11480,12 @@
       </c>
       <c r="I182" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J182" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K182" s="29" t="inlineStr"/>
@@ -11613,12 +11533,12 @@
       </c>
       <c r="I183" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J183" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K183" s="31" t="inlineStr"/>
@@ -11666,12 +11586,12 @@
       </c>
       <c r="I184" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J184" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K184" s="29" t="inlineStr"/>
@@ -11719,12 +11639,12 @@
       </c>
       <c r="I185" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J185" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K185" s="31" t="inlineStr"/>
@@ -11772,12 +11692,12 @@
       </c>
       <c r="I186" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J186" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K186" s="29" t="inlineStr"/>
@@ -11825,12 +11745,12 @@
       </c>
       <c r="I187" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J187" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K187" s="31" t="inlineStr"/>
@@ -11878,12 +11798,12 @@
       </c>
       <c r="I188" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J188" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K188" s="29" t="inlineStr"/>
@@ -11931,12 +11851,12 @@
       </c>
       <c r="I189" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J189" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K189" s="31" t="inlineStr"/>
@@ -11984,12 +11904,12 @@
       </c>
       <c r="I190" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J190" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K190" s="29" t="inlineStr"/>
@@ -12037,12 +11957,12 @@
       </c>
       <c r="I191" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J191" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K191" s="31" t="inlineStr"/>
@@ -12090,12 +12010,12 @@
       </c>
       <c r="I192" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J192" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K192" s="29" t="inlineStr"/>
@@ -12143,12 +12063,12 @@
       </c>
       <c r="I193" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J193" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K193" s="31" t="inlineStr"/>
@@ -12196,12 +12116,12 @@
       </c>
       <c r="I194" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J194" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K194" s="29" t="inlineStr"/>
@@ -12249,12 +12169,12 @@
       </c>
       <c r="I195" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J195" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K195" s="31" t="inlineStr"/>
@@ -12302,12 +12222,12 @@
       </c>
       <c r="I196" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J196" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K196" s="29" t="inlineStr"/>
@@ -12355,12 +12275,12 @@
       </c>
       <c r="I197" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J197" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K197" s="31" t="inlineStr"/>
@@ -12408,12 +12328,12 @@
       </c>
       <c r="I198" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J198" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K198" s="29" t="inlineStr"/>
@@ -12461,12 +12381,12 @@
       </c>
       <c r="I199" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J199" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K199" s="31" t="inlineStr"/>
@@ -12514,12 +12434,12 @@
       </c>
       <c r="I200" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J200" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K200" s="29" t="inlineStr"/>
@@ -12567,12 +12487,12 @@
       </c>
       <c r="I201" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J201" s="31" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K201" s="31" t="inlineStr"/>
@@ -12620,12 +12540,12 @@
       </c>
       <c r="I202" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours/Holiday Activity [MEDIUM]</t>
+          <t>Rule 10 — Off-Hours/Holiday Activity [MEDIUM]</t>
         </is>
       </c>
       <c r="J202" s="29" t="inlineStr">
         <is>
-          <t>Rule 11 — Off-Hours Activity</t>
+          <t>Rule 10 — Off-Hours Activity</t>
         </is>
       </c>
       <c r="K202" s="29" t="inlineStr"/>
@@ -20929,9 +20849,9 @@
           <t>Standard value entry per SOP-01</t>
         </is>
       </c>
-      <c r="G359" s="32" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="G359" s="31" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="H359" s="31" t="inlineStr">
@@ -20941,12 +20861,12 @@
       </c>
       <c r="I359" s="31" t="inlineStr">
         <is>
-          <t>Rule 10 — Audit Trail Timestamp Gap [MEDIUM]</t>
+          <t>Rule 9 — Audit Trail Timestamp Gap [MEDIUM]</t>
         </is>
       </c>
       <c r="J359" s="31" t="inlineStr">
         <is>
-          <t>Rule 10 — Audit Trail Timestamp Gap</t>
+          <t>Rule 9 — Audit Trail Timestamp Gap</t>
         </is>
       </c>
       <c r="K359" s="31" t="inlineStr"/>

--- a/AuditTrail_today.xlsx
+++ b/AuditTrail_today.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>LabLIMSv1</t>
+          <t>BioSysv1</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>01-Jan-2024  →  31-Mar-2026</t>
+          <t>01-Jan-2022  →  31-Mar-2026</t>
         </is>
       </c>
     </row>
@@ -1108,13 +1108,12 @@
       </c>
       <c r="B33" s="8" t="inlineStr"/>
     </row>
-    <row r="34" ht="132" customHeight="1">
+    <row r="34" ht="110" customHeight="1">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t>The audit trail for LabLIMSv1 was reviewed from 01-Jan-2024 to 31-Mar-2026. Of 1,000 recorded events, 6 were escalated for review (4 Critical, 2 High). Full dataset tier distribution is available in the Full Audit Log sheet.
+          <t>The audit trail for BioSysv1 was reviewed from 01-Jan-2022 to 31-Mar-2026. Of 1,000 recorded events, 6 were escalated for review (4 Critical, 2 High). Full dataset tier distribution is available in the Full Audit Log sheet.
 4 instances of missing or inadequate change rationale were observed across multiple records, indicating deficiencies in data attribution practices.
 A system administrator (admin_sys) directly modified production BATCH_RELEASE data on record BATCH-999, which is inconsistent with Segregation of Duties expectations under 21 CFR Part 11 §11.10(d).
-Non-personal account 'analyst_x' performed a DELETE action on RESULTS on record RES-5050. This action cannot be attributed to a specific individual.
 A delete-and-recreate pattern was identified on record RES-8888 by user 'analyst_y', a known method for circumventing locked record controls.
 Overall, the system presents a high risk to data integrity and requires immediate corrective actions, particularly in access control and audit trail integrity.</t>
         </is>
@@ -1131,8 +1130,8 @@
     <row r="37" ht="72" customHeight="1">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>This audit trail review was performed using rule-based anomaly detection with system-generated narrative summaries. All risk classifications are derived from deterministic rules; narrative text does not influence risk scoring or tier assignment. 1,000 records were reviewed across the period 01-Jan-2024 to 31-Mar-2026. 99.4% of records were automatically cleared as low risk. The 6 records requiring review are documented in the 'Events for Review' sheet. Each finding has been independently reviewed and dispositioned by the undersigned reviewer. The 'System-Proposed Disposition' column is informational only; the reviewer's determination in the 'Reviewer Decision' column reflects independent human judgement and is the authoritative record. Regulatory basis: 21 CFR Part 11 §11.10(e) and EU Annex 11 Clause 9.
-Timezone note: Off-hours scoring (Rule 11) assumes all timestamps in the uploaded file are in the same timezone. If your system exports timestamps in UTC or a non-local timezone, off-hours flags should be interpreted accordingly. Reviewers should verify local shift patterns before dispositing temporal anomalies.</t>
+          <t>This audit trail review was performed using rule-based anomaly detection with system-generated narrative summaries. All risk classifications are derived from deterministic rules; narrative text does not influence risk scoring or tier assignment. 1,000 records were reviewed across the period 01-Jan-2022 to 31-Mar-2026. 99.4% of records were automatically cleared as low risk. The 6 records requiring review are documented in the 'Events for Review' sheet. Each finding has been independently reviewed and dispositioned by the undersigned reviewer. The 'System-Proposed Disposition' column is informational only; the reviewer's determination in the 'Reviewer Decision' column reflects independent human judgement and is the authoritative record. Regulatory basis: 21 CFR Part 11 §11.10(e) and EU Annex 11 Clause 9.
+Timezone note: Off-hours scoring (Rule 10) assumes all timestamps in the uploaded file are in the same timezone. If your system exports timestamps in UTC or a non-local timezone, off-hours flags should be interpreted accordingly. Reviewers should verify local shift patterns before dispositing temporal anomalies.</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1993,7 @@
       </c>
       <c r="J3" s="31" t="inlineStr">
         <is>
-          <t>Rule 1 — Vague Rationale; Rule 6 — Record Reconstruction Pattern; Rule 13 — First-Time Behavior</t>
+          <t>Rule 1 — Vague Rationale; Rule 6 — Record Reconstruction Pattern; Rule 14 — First-Time Behavior</t>
         </is>
       </c>
       <c r="K3" s="31" t="inlineStr">
@@ -2210,7 +2209,7 @@
       </c>
       <c r="J7" s="31" t="inlineStr">
         <is>
-          <t>Rule 1 — Vague Rationale; Rule 13 — First-Time Behavior</t>
+          <t>Rule 1 — Vague Rationale; Rule 14 — First-Time Behavior</t>
         </is>
       </c>
       <c r="K7" s="31" t="inlineStr"/>
@@ -3106,7 +3105,7 @@
       </c>
       <c r="I24" s="29" t="inlineStr">
         <is>
-          <t>Rule 9 — Audit Trail Timestamp Gap [MEDIUM]</t>
+          <t>Rule 9 — Audit Trail Timestamp Gap [HIGH]</t>
         </is>
       </c>
       <c r="J24" s="29" t="inlineStr">
@@ -54906,7 +54905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A444"/>
+  <dimension ref="A1:A429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -54963,7 +54962,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="37" t="inlineStr">
         <is>
-          <t>**Total rules implemented: 16**</t>
+          <t>**Total rules implemented: 14**</t>
         </is>
       </c>
     </row>
@@ -54977,14 +54976,14 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="36" t="inlineStr">
         <is>
-          <t>Rules 6–11: Dimension-based rules (pattern and behavioural anomalies)</t>
+          <t>Rules 6–10: Dimension-based rules (pattern and behavioural anomalies)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="36" t="inlineStr">
         <is>
-          <t>Rules 12–16: Advanced integrity rules (no second file required)</t>
+          <t>Rules 11–14: Advanced integrity rules (no second file required)</t>
         </is>
       </c>
     </row>
@@ -55750,7 +55749,7 @@
     <row r="134" ht="18" customHeight="1">
       <c r="A134" s="35" t="inlineStr">
         <is>
-          <t>### Rule 10 — Audit Trail Timestamp Gap [Risk: HIGH]</t>
+          <t>### Rule 9 — Audit Trail Timestamp Gap [Risk: HIGH]</t>
         </is>
       </c>
     </row>
@@ -55812,7 +55811,7 @@
     <row r="144" ht="18" customHeight="1">
       <c r="A144" s="35" t="inlineStr">
         <is>
-          <t>### Rule 11 — Off-Hours and Federal Holiday Activity [Risk: HIGH / MEDIUM]</t>
+          <t>### Rule 10 — Off-Hours and Federal Holiday Activity [Risk: HIGH / MEDIUM]</t>
         </is>
       </c>
     </row>
@@ -55931,7 +55930,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" s="36" t="inlineStr">
         <is>
-          <t>dispositing any Rule 11 finding. A flag at 02:00 UTC may be 10:00 local time</t>
+          <t>dispositing any Rule 10 finding. A flag at 02:00 UTC may be 10:00 local time</t>
         </is>
       </c>
     </row>
@@ -55982,7 +55981,7 @@
     <row r="170" ht="18" customHeight="1">
       <c r="A170" s="35" t="inlineStr">
         <is>
-          <t>### Rule 12 — Timestamp Reversal [Risk: CRITICAL]</t>
+          <t>### Rule 11 — Timestamp Reversal [Risk: CRITICAL]</t>
         </is>
       </c>
     </row>
@@ -56093,7 +56092,7 @@
     <row r="187" ht="18" customHeight="1">
       <c r="A187" s="35" t="inlineStr">
         <is>
-          <t>### Rule 13 — Service / Shared Account GxP Action [Risk: CRITICAL / HIGH]</t>
+          <t>### Rule 12 — Service / Shared Account GxP Action [Risk: CRITICAL / HIGH]</t>
         </is>
       </c>
     </row>
@@ -56220,132 +56219,120 @@
     <row r="208" ht="18" customHeight="1">
       <c r="A208" s="35" t="inlineStr">
         <is>
-          <t>### Rule 15 — Suspicious Action Sequence: UPDATE → DELETE → INSERT [Risk: CRITICAL]</t>
+          <t>### Rule 15 — Suspicious Action Sequence *(Retired — merged into Rule 6)*</t>
         </is>
       </c>
     </row>
     <row r="209" ht="15" customHeight="1">
-      <c r="A209" s="37" t="inlineStr">
-        <is>
-          <t>**Target:** All record types with a populated record_id column.</t>
+      <c r="A209" s="36" t="inlineStr">
+        <is>
+          <t>UPDATE → DELETE → INSERT three-step sequence detection was merged into Rule 6</t>
         </is>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
-      <c r="A210" s="37" t="inlineStr">
-        <is>
-          <t>**Trigger:** Same user performs UPDATE (or MODIFY/EDIT/AMEND), then DELETE,</t>
+      <c r="A210" s="36" t="inlineStr">
+        <is>
+          <t>(Record Reconstruction Pattern). Rule 6 now covers both two-step and three-step</t>
         </is>
       </c>
     </row>
     <row r="211" ht="15" customHeight="1">
       <c r="A211" s="36" t="inlineStr">
         <is>
-          <t>then INSERT/CREATE on the same record_id, all within 30 minutes.</t>
+          <t>reconstructions. This rule number is retired and will not appear in outputs.</t>
         </is>
       </c>
     </row>
     <row r="212" ht="15" customHeight="1">
-      <c r="A212" s="36" t="inlineStr">
-        <is>
-          <t>Score: 10.0 on all three events. An Event Chain ID (EC-NNN) links all three rows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="213" ht="15" customHeight="1">
-      <c r="A213" s="37" t="inlineStr">
-        <is>
-          <t>**Regulatory basis:** 21 CFR Part 11 §11.10(e); ALCOA+ Original.</t>
+      <c r="A212" s="36" t="inlineStr"/>
+    </row>
+    <row r="213" ht="8" customHeight="1">
+      <c r="A213" s="38" t="inlineStr">
+        <is>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="214" ht="15" customHeight="1">
-      <c r="A214" s="37" t="inlineStr">
-        <is>
-          <t>**Why Critical:** GxP systems lock approved records to prevent direct editing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="215" ht="15" customHeight="1">
-      <c r="A215" s="36" t="inlineStr">
-        <is>
-          <t>This three-step sequence — modify, delete, recreate — is the primary method</t>
+      <c r="A214" s="36" t="inlineStr"/>
+    </row>
+    <row r="215" ht="18" customHeight="1">
+      <c r="A215" s="35" t="inlineStr">
+        <is>
+          <t>## Event Chain IDs</t>
         </is>
       </c>
     </row>
     <row r="216" ht="15" customHeight="1">
-      <c r="A216" s="36" t="inlineStr">
-        <is>
-          <t>for altering a locked record while making the change appear as a new entry,</t>
-        </is>
-      </c>
+      <c r="A216" s="36" t="inlineStr"/>
     </row>
     <row r="217" ht="15" customHeight="1">
       <c r="A217" s="36" t="inlineStr">
         <is>
-          <t>obscuring the original modification from the audit trail.</t>
+          <t>When multiple events are causally linked, the engine assigns a shared Event Chain</t>
         </is>
       </c>
     </row>
     <row r="218" ht="15" customHeight="1">
-      <c r="A218" s="37" t="inlineStr">
-        <is>
-          <t>**Distinction from Rule 6 (Delete-Recreate):** Rule 6 detects DELETE → INSERT</t>
+      <c r="A218" s="36" t="inlineStr">
+        <is>
+          <t>ID (format: EC-001, EC-002 etc.) to all related events. This allows reviewers to</t>
         </is>
       </c>
     </row>
     <row r="219" ht="15" customHeight="1">
       <c r="A219" s="36" t="inlineStr">
         <is>
-          <t>(two steps). Rule 15 detects UPDATE → DELETE → INSERT (three steps), which is</t>
+          <t>filter the Full Audit Log by chain ID and read the complete event story in sequence.</t>
         </is>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
-      <c r="A220" s="36" t="inlineStr">
-        <is>
-          <t>more specific — it indicates the user first tried to modify the locked record,</t>
-        </is>
-      </c>
+      <c r="A220" s="36" t="inlineStr"/>
     </row>
     <row r="221" ht="15" customHeight="1">
       <c r="A221" s="36" t="inlineStr">
         <is>
-          <t>then switched to the delete-recreate method.</t>
+          <t>Chains are assigned for:</t>
         </is>
       </c>
     </row>
     <row r="222" ht="15" customHeight="1">
-      <c r="A222" s="37" t="inlineStr">
-        <is>
-          <t>**30-minute window:** Captures same-session sequences while excluding coincidental</t>
+      <c r="A222" s="36" t="inlineStr">
+        <is>
+          <t>- **Rule 6** (Delete → Recreate and UPDATE → DELETE → INSERT): all linked events share one chain ID</t>
         </is>
       </c>
     </row>
     <row r="223" ht="15" customHeight="1">
       <c r="A223" s="36" t="inlineStr">
         <is>
-          <t>patterns across different working sessions.</t>
+          <t>- **Rule 5** (Failed Login → Manipulation): all login attempts and the triggering</t>
         </is>
       </c>
     </row>
     <row r="224" ht="15" customHeight="1">
-      <c r="A224" s="36" t="inlineStr"/>
-    </row>
-    <row r="225" ht="8" customHeight="1">
-      <c r="A225" s="38" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="A224" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  data action share one chain ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="15" customHeight="1">
+      <c r="A225" s="36" t="inlineStr"/>
     </row>
     <row r="226" ht="15" customHeight="1">
-      <c r="A226" s="36" t="inlineStr"/>
-    </row>
-    <row r="227" ht="18" customHeight="1">
-      <c r="A227" s="35" t="inlineStr">
-        <is>
-          <t>## Event Chain IDs</t>
+      <c r="A226" s="36" t="inlineStr">
+        <is>
+          <t>The Event_Chain_ID column appears in both the Events for Review sheet and the</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="15" customHeight="1">
+      <c r="A227" s="36" t="inlineStr">
+        <is>
+          <t>Full Audit Log sheet in the Excel output.</t>
         </is>
       </c>
     </row>
@@ -56353,950 +56340,954 @@
       <c r="A228" s="36" t="inlineStr"/>
     </row>
     <row r="229" ht="15" customHeight="1">
-      <c r="A229" s="36" t="inlineStr">
-        <is>
-          <t>When multiple events are causally linked, the engine assigns a shared Event Chain</t>
-        </is>
-      </c>
-    </row>
-    <row r="230" ht="15" customHeight="1">
-      <c r="A230" s="36" t="inlineStr">
-        <is>
-          <t>ID (format: EC-001, EC-002 etc.) to all related events. This allows reviewers to</t>
+      <c r="A229" s="36" t="inlineStr"/>
+    </row>
+    <row r="230" ht="8" customHeight="1">
+      <c r="A230" s="38" t="inlineStr">
+        <is>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="231" ht="15" customHeight="1">
-      <c r="A231" s="36" t="inlineStr">
-        <is>
-          <t>filter the Full Audit Log by chain ID and read the complete event story in sequence.</t>
-        </is>
-      </c>
-    </row>
-    <row r="232" ht="15" customHeight="1">
-      <c r="A232" s="36" t="inlineStr"/>
+      <c r="A231" s="36" t="inlineStr"/>
+    </row>
+    <row r="232" ht="18" customHeight="1">
+      <c r="A232" s="35" t="inlineStr">
+        <is>
+          <t>### Rule 14 — First-Time Behavior Detection [Risk: HIGH]</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="15" customHeight="1">
-      <c r="A233" s="36" t="inlineStr">
-        <is>
-          <t>Chains are assigned for:</t>
+      <c r="A233" s="37" t="inlineStr">
+        <is>
+          <t>**Target:** All users with at least 5 prior recorded events in the uploaded file.</t>
         </is>
       </c>
     </row>
     <row r="234" ht="15" customHeight="1">
-      <c r="A234" s="36" t="inlineStr">
-        <is>
-          <t>- **Rule 15** (UPDATE → DELETE → INSERT): all three steps share one chain ID</t>
+      <c r="A234" s="37" t="inlineStr">
+        <is>
+          <t>**Trigger:** A user performs an action_type they have never performed before</t>
         </is>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1">
       <c r="A235" s="36" t="inlineStr">
         <is>
-          <t>- **Rule 5** (Failed Login → Manipulation): all login attempts and the triggering</t>
+          <t>in their recorded audit trail history. Score varies by prior history and action risk:</t>
         </is>
       </c>
     </row>
     <row r="236" ht="15" customHeight="1">
-      <c r="A236" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  data action share one chain ID</t>
-        </is>
-      </c>
+      <c r="A236" s="36" t="inlineStr"/>
     </row>
     <row r="237" ht="15" customHeight="1">
-      <c r="A237" s="36" t="inlineStr">
-        <is>
-          <t>- **Rule 6** (Delete → Recreate): both events share one chain ID</t>
+      <c r="A237" s="37" t="inlineStr">
+        <is>
+          <t>| Prior events | Action type | Score |</t>
         </is>
       </c>
     </row>
     <row r="238" ht="15" customHeight="1">
-      <c r="A238" s="36" t="inlineStr"/>
+      <c r="A238" s="36" t="inlineStr">
+        <is>
+          <t>|---|---|---|</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="15" customHeight="1">
-      <c r="A239" s="36" t="inlineStr">
-        <is>
-          <t>The Event_Chain_ID column appears in both the Events for Review sheet and the</t>
+      <c r="A239" s="37" t="inlineStr">
+        <is>
+          <t>| ≥50 | First-time DELETE/APPROVE on GxP table | 9.0 |</t>
         </is>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
-      <c r="A240" s="36" t="inlineStr">
-        <is>
-          <t>Full Audit Log sheet in the Excel output.</t>
+      <c r="A240" s="37" t="inlineStr">
+        <is>
+          <t>| ≥20 | First-time DELETE/APPROVE on any table | 8.0 |</t>
         </is>
       </c>
     </row>
     <row r="241" ht="15" customHeight="1">
-      <c r="A241" s="36" t="inlineStr"/>
+      <c r="A241" s="37" t="inlineStr">
+        <is>
+          <t>| ≥20 | First-time any action | 6.0 |</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="15" customHeight="1">
-      <c r="A242" s="36" t="inlineStr"/>
-    </row>
-    <row r="243" ht="8" customHeight="1">
-      <c r="A243" s="38" t="inlineStr">
-        <is>
-          <t>---</t>
+      <c r="A242" s="37" t="inlineStr">
+        <is>
+          <t>| ≥5  | First-time high-risk action | 5.0 |</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="15" customHeight="1">
+      <c r="A243" s="37" t="inlineStr">
+        <is>
+          <t>| &lt;5  | (not enough history — skipped) | 0.0 |</t>
         </is>
       </c>
     </row>
     <row r="244" ht="15" customHeight="1">
       <c r="A244" s="36" t="inlineStr"/>
     </row>
-    <row r="245" ht="18" customHeight="1">
-      <c r="A245" s="35" t="inlineStr">
-        <is>
-          <t>### Rule 16 — First-Time Behavior Detection [Risk: HIGH]</t>
+    <row r="245" ht="15" customHeight="1">
+      <c r="A245" s="37" t="inlineStr">
+        <is>
+          <t>**High-risk action types detected:** delete, del, remove, purge, void, cancel,</t>
         </is>
       </c>
     </row>
     <row r="246" ht="15" customHeight="1">
-      <c r="A246" s="37" t="inlineStr">
-        <is>
-          <t>**Target:** All users with at least 5 prior recorded events in the uploaded file.</t>
+      <c r="A246" s="36" t="inlineStr">
+        <is>
+          <t>approve, release, authorise, authorize, sign, override, batch_release, approve_result.</t>
         </is>
       </c>
     </row>
     <row r="247" ht="15" customHeight="1">
       <c r="A247" s="37" t="inlineStr">
         <is>
-          <t>**Trigger:** A user performs an action_type they have never performed before</t>
+          <t>**Regulatory basis:** 21 CFR Part 11 §11.10(d) access controls; ALCOA+ Attributable.</t>
         </is>
       </c>
     </row>
     <row r="248" ht="15" customHeight="1">
-      <c r="A248" s="36" t="inlineStr">
-        <is>
-          <t>in their recorded audit trail history. Score varies by prior history and action risk:</t>
+      <c r="A248" s="37" t="inlineStr">
+        <is>
+          <t>**Why this matters:** An established user who suddenly performs an action they</t>
         </is>
       </c>
     </row>
     <row r="249" ht="15" customHeight="1">
-      <c r="A249" s="36" t="inlineStr"/>
+      <c r="A249" s="36" t="inlineStr">
+        <is>
+          <t>have never done before — especially a high-risk action like delete or approve —</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="15" customHeight="1">
-      <c r="A250" s="37" t="inlineStr">
-        <is>
-          <t>| Prior events | Action type | Score |</t>
+      <c r="A250" s="36" t="inlineStr">
+        <is>
+          <t>is a meaningful insider risk signal. This pattern may indicate:</t>
         </is>
       </c>
     </row>
     <row r="251" ht="15" customHeight="1">
       <c r="A251" s="36" t="inlineStr">
         <is>
-          <t>|---|---|---|</t>
+          <t>- Unauthorised escalation of access or responsibilities</t>
         </is>
       </c>
     </row>
     <row r="252" ht="15" customHeight="1">
-      <c r="A252" s="37" t="inlineStr">
-        <is>
-          <t>| ≥50 | First-time DELETE/APPROVE on GxP table | 9.0 |</t>
+      <c r="A252" s="36" t="inlineStr">
+        <is>
+          <t>- Credential sharing (someone else used the account)</t>
         </is>
       </c>
     </row>
     <row r="253" ht="15" customHeight="1">
-      <c r="A253" s="37" t="inlineStr">
-        <is>
-          <t>| ≥20 | First-time DELETE/APPROVE on any table | 8.0 |</t>
+      <c r="A253" s="36" t="inlineStr">
+        <is>
+          <t>- A data integrity incident being covered up</t>
         </is>
       </c>
     </row>
     <row r="254" ht="15" customHeight="1">
-      <c r="A254" s="37" t="inlineStr">
-        <is>
-          <t>| ≥20 | First-time any action | 6.0 |</t>
-        </is>
-      </c>
+      <c r="A254" s="36" t="inlineStr"/>
     </row>
     <row r="255" ht="15" customHeight="1">
       <c r="A255" s="37" t="inlineStr">
         <is>
-          <t>| ≥5  | First-time high-risk action | 5.0 |</t>
+          <t>**Confidence labelling:** The rationale always states the number of prior events</t>
         </is>
       </c>
     </row>
     <row r="256" ht="15" customHeight="1">
-      <c r="A256" s="37" t="inlineStr">
-        <is>
-          <t>| &lt;5  | (not enough history — skipped) | 0.0 |</t>
+      <c r="A256" s="36" t="inlineStr">
+        <is>
+          <t>observed, so the reviewer can judge statistical significance. A user with 200 prior</t>
         </is>
       </c>
     </row>
     <row r="257" ht="15" customHeight="1">
-      <c r="A257" s="36" t="inlineStr"/>
+      <c r="A257" s="36" t="inlineStr">
+        <is>
+          <t>events performing their first-ever delete is far more anomalous than a user with 6.</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="15" customHeight="1">
-      <c r="A258" s="37" t="inlineStr">
-        <is>
-          <t>**High-risk action types detected:** delete, del, remove, purge, void, cancel,</t>
-        </is>
-      </c>
+      <c r="A258" s="36" t="inlineStr"/>
     </row>
     <row r="259" ht="15" customHeight="1">
-      <c r="A259" s="36" t="inlineStr">
-        <is>
-          <t>approve, release, authorise, authorize, sign, override, batch_release, approve_result.</t>
+      <c r="A259" s="37" t="inlineStr">
+        <is>
+          <t>**Important limitation:** This rule requires sufficient history in the uploaded file.</t>
         </is>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
-      <c r="A260" s="37" t="inlineStr">
-        <is>
-          <t>**Regulatory basis:** 21 CFR Part 11 §11.10(d) access controls; ALCOA+ Attributable.</t>
+      <c r="A260" s="36" t="inlineStr">
+        <is>
+          <t>Short-period exports (under 30 days) will produce many "first-time" flags that</t>
         </is>
       </c>
     </row>
     <row r="261" ht="15" customHeight="1">
-      <c r="A261" s="37" t="inlineStr">
-        <is>
-          <t>**Why this matters:** An established user who suddenly performs an action they</t>
+      <c r="A261" s="36" t="inlineStr">
+        <is>
+          <t>are simply normal activity not captured in the window. For reliable detection,</t>
         </is>
       </c>
     </row>
     <row r="262" ht="15" customHeight="1">
       <c r="A262" s="36" t="inlineStr">
         <is>
-          <t>have never done before — especially a high-risk action like delete or approve —</t>
+          <t>upload audit trails covering at least 3 months.</t>
         </is>
       </c>
     </row>
     <row r="263" ht="15" customHeight="1">
-      <c r="A263" s="36" t="inlineStr">
-        <is>
-          <t>is a meaningful insider risk signal. This pattern may indicate:</t>
-        </is>
-      </c>
+      <c r="A263" s="36" t="inlineStr"/>
     </row>
     <row r="264" ht="15" customHeight="1">
-      <c r="A264" s="36" t="inlineStr">
-        <is>
-          <t>- Unauthorised escalation of access or responsibilities</t>
+      <c r="A264" s="37" t="inlineStr">
+        <is>
+          <t>**Minimum prior events:** 5. Users with fewer than 5 recorded events are skipped</t>
         </is>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
       <c r="A265" s="36" t="inlineStr">
         <is>
-          <t>- Credential sharing (someone else used the account)</t>
+          <t>to exclude newly created accounts where any action is technically a "first time."</t>
         </is>
       </c>
     </row>
     <row r="266" ht="15" customHeight="1">
-      <c r="A266" s="36" t="inlineStr">
-        <is>
-          <t>- A data integrity incident being covered up</t>
-        </is>
-      </c>
-    </row>
-    <row r="267" ht="15" customHeight="1">
-      <c r="A267" s="36" t="inlineStr"/>
+      <c r="A266" s="36" t="inlineStr"/>
+    </row>
+    <row r="267" ht="18" customHeight="1">
+      <c r="A267" s="35" t="inlineStr">
+        <is>
+          <t>### Rule 13 — Dormant Account Sudden Activity [Risk: HIGH]</t>
+        </is>
+      </c>
     </row>
     <row r="268" ht="15" customHeight="1">
       <c r="A268" s="37" t="inlineStr">
         <is>
-          <t>**Confidence labelling:** The rationale always states the number of prior events</t>
+          <t>**Target:** All users with at least 4 events in the uploaded audit trail.</t>
         </is>
       </c>
     </row>
     <row r="269" ht="15" customHeight="1">
-      <c r="A269" s="36" t="inlineStr">
-        <is>
-          <t>observed, so the reviewer can judge statistical significance. A user with 200 prior</t>
+      <c r="A269" s="37" t="inlineStr">
+        <is>
+          <t>**Trigger:** A user has no activity for 90 or more consecutive days, then</t>
         </is>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
       <c r="A270" s="36" t="inlineStr">
         <is>
-          <t>events performing their first-ever delete is far more anomalous than a user with 6.</t>
+          <t>performs a data action on a GxP-sensitive record type or performs</t>
         </is>
       </c>
     </row>
     <row r="271" ht="15" customHeight="1">
-      <c r="A271" s="36" t="inlineStr"/>
+      <c r="A271" s="36" t="inlineStr">
+        <is>
+          <t>update/modify/delete/insert/approve/release on any record. Score: 8.0.</t>
+        </is>
+      </c>
     </row>
     <row r="272" ht="15" customHeight="1">
       <c r="A272" s="37" t="inlineStr">
         <is>
-          <t>**Important limitation:** This rule requires sufficient history in the uploaded file.</t>
+          <t>**Only the first re-activation event per user is flagged** to avoid filling</t>
         </is>
       </c>
     </row>
     <row r="273" ht="15" customHeight="1">
       <c r="A273" s="36" t="inlineStr">
         <is>
-          <t>Short-period exports (under 30 days) will produce many "first-time" flags that</t>
+          <t>the Top 20 with multiple events from the same dormant account.</t>
         </is>
       </c>
     </row>
     <row r="274" ht="15" customHeight="1">
-      <c r="A274" s="36" t="inlineStr">
-        <is>
-          <t>are simply normal activity not captured in the window. For reliable detection,</t>
+      <c r="A274" s="37" t="inlineStr">
+        <is>
+          <t>**Regulatory basis:** 21 CFR Part 11 §11.10(d) — access controls; access review</t>
         </is>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
       <c r="A275" s="36" t="inlineStr">
         <is>
-          <t>upload audit trails covering at least 3 months.</t>
+          <t>best practice requiring deactivation of accounts inactive for 90+ days.</t>
         </is>
       </c>
     </row>
     <row r="276" ht="15" customHeight="1">
-      <c r="A276" s="36" t="inlineStr"/>
+      <c r="A276" s="37" t="inlineStr">
+        <is>
+          <t>**Limitation:** Requires the uploaded audit trail to cover at least 90+ days of</t>
+        </is>
+      </c>
     </row>
     <row r="277" ht="15" customHeight="1">
-      <c r="A277" s="37" t="inlineStr">
-        <is>
-          <t>**Minimum prior events:** 5. Users with fewer than 5 recorded events are skipped</t>
+      <c r="A277" s="36" t="inlineStr">
+        <is>
+          <t>history for reliable detection. Short-period extracts will not trigger this rule.</t>
         </is>
       </c>
     </row>
     <row r="278" ht="15" customHeight="1">
-      <c r="A278" s="36" t="inlineStr">
-        <is>
-          <t>to exclude newly created accounts where any action is technically a "first time."</t>
+      <c r="A278" s="37" t="inlineStr">
+        <is>
+          <t>**Minimum event count:** A user must have at least 3 prior events before the gap</t>
         </is>
       </c>
     </row>
     <row r="279" ht="15" customHeight="1">
-      <c r="A279" s="36" t="inlineStr"/>
-    </row>
-    <row r="280" ht="18" customHeight="1">
-      <c r="A280" s="35" t="inlineStr">
-        <is>
-          <t>### Rule 14 — Dormant Account Sudden Activity [Risk: HIGH]</t>
-        </is>
-      </c>
-    </row>
-    <row r="281" ht="15" customHeight="1">
-      <c r="A281" s="37" t="inlineStr">
-        <is>
-          <t>**Target:** All users with at least 4 events in the uploaded audit trail.</t>
+      <c r="A279" s="36" t="inlineStr">
+        <is>
+          <t>to be considered an established account (excludes newly created accounts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="15" customHeight="1">
+      <c r="A280" s="36" t="inlineStr"/>
+    </row>
+    <row r="281" ht="8" customHeight="1">
+      <c r="A281" s="38" t="inlineStr">
+        <is>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="282" ht="15" customHeight="1">
-      <c r="A282" s="37" t="inlineStr">
-        <is>
-          <t>**Trigger:** A user has no activity for 90 or more consecutive days, then</t>
-        </is>
-      </c>
-    </row>
-    <row r="283" ht="15" customHeight="1">
-      <c r="A283" s="36" t="inlineStr">
-        <is>
-          <t>performs a data action on a GxP-sensitive record type or performs</t>
+      <c r="A282" s="36" t="inlineStr"/>
+    </row>
+    <row r="283" ht="18" customHeight="1">
+      <c r="A283" s="35" t="inlineStr">
+        <is>
+          <t>## Composite Scoring</t>
         </is>
       </c>
     </row>
     <row r="284" ht="15" customHeight="1">
-      <c r="A284" s="36" t="inlineStr">
-        <is>
-          <t>update/modify/delete/insert/approve/release on any record. Score: 8.0.</t>
-        </is>
-      </c>
+      <c r="A284" s="36" t="inlineStr"/>
     </row>
     <row r="285" ht="15" customHeight="1">
-      <c r="A285" s="37" t="inlineStr">
-        <is>
-          <t>**Only the first re-activation event per user is flagged** to avoid filling</t>
+      <c r="A285" s="36" t="inlineStr">
+        <is>
+          <t>Each event receives scores across all 14 active rules. A weighted composite (0–10):</t>
         </is>
       </c>
     </row>
     <row r="286" ht="15" customHeight="1">
-      <c r="A286" s="36" t="inlineStr">
-        <is>
-          <t>the Top 20 with multiple events from the same dormant account.</t>
-        </is>
-      </c>
+      <c r="A286" s="36" t="inlineStr"/>
     </row>
     <row r="287" ht="15" customHeight="1">
       <c r="A287" s="37" t="inlineStr">
         <is>
-          <t>**Regulatory basis:** 21 CFR Part 11 §11.10(d) — access controls; access review</t>
+          <t>| Rule | Dimension / Name | Weight |</t>
         </is>
       </c>
     </row>
     <row r="288" ht="15" customHeight="1">
       <c r="A288" s="36" t="inlineStr">
         <is>
-          <t>best practice requiring deactivation of accounts inactive for 90+ days.</t>
+          <t>|------|-----------------|--------|</t>
         </is>
       </c>
     </row>
     <row r="289" ht="15" customHeight="1">
       <c r="A289" s="37" t="inlineStr">
         <is>
-          <t>**Limitation:** Requires the uploaded audit trail to cover at least 90+ days of</t>
+          <t>| 1  | Vague Rationale | 7% |</t>
         </is>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1">
-      <c r="A290" s="36" t="inlineStr">
-        <is>
-          <t>history for reliable detection. Short-period extracts will not trigger this rule.</t>
+      <c r="A290" s="37" t="inlineStr">
+        <is>
+          <t>| 2  | Contemporaneous Burst | 7% |</t>
         </is>
       </c>
     </row>
     <row r="291" ht="15" customHeight="1">
       <c r="A291" s="37" t="inlineStr">
         <is>
-          <t>**Minimum event count:** A user must have at least 3 prior events before the gap</t>
+          <t>| 3  | Admin/GxP Conflict | 10% |</t>
         </is>
       </c>
     </row>
     <row r="292" ht="15" customHeight="1">
-      <c r="A292" s="36" t="inlineStr">
-        <is>
-          <t>to be considered an established account (excludes newly created accounts).</t>
+      <c r="A292" s="37" t="inlineStr">
+        <is>
+          <t>| 4  | Change Control Drift | 6% |</t>
         </is>
       </c>
     </row>
     <row r="293" ht="15" customHeight="1">
-      <c r="A293" s="36" t="inlineStr"/>
-    </row>
-    <row r="294" ht="8" customHeight="1">
-      <c r="A294" s="38" t="inlineStr">
-        <is>
-          <t>---</t>
+      <c r="A293" s="37" t="inlineStr">
+        <is>
+          <t>| 5  | Failed Login → Data Manipulation | 8% |</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="15" customHeight="1">
+      <c r="A294" s="37" t="inlineStr">
+        <is>
+          <t>| 6  | Record Reconstruction (Delete-Recreate) | 10% |</t>
         </is>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
-      <c r="A295" s="36" t="inlineStr"/>
-    </row>
-    <row r="296" ht="18" customHeight="1">
-      <c r="A296" s="35" t="inlineStr">
-        <is>
-          <t>## Composite Scoring</t>
+      <c r="A295" s="37" t="inlineStr">
+        <is>
+          <t>| 7  | Audit Trail Integrity / Record Sensitivity | 8% |</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="15" customHeight="1">
+      <c r="A296" s="37" t="inlineStr">
+        <is>
+          <t>| 8  | Privileged User on GxP Data | 9% |</t>
         </is>
       </c>
     </row>
     <row r="297" ht="15" customHeight="1">
-      <c r="A297" s="36" t="inlineStr"/>
+      <c r="A297" s="37" t="inlineStr">
+        <is>
+          <t>| 9  | Timestamp Gap | 6% |</t>
+        </is>
+      </c>
     </row>
     <row r="298" ht="15" customHeight="1">
-      <c r="A298" s="36" t="inlineStr">
-        <is>
-          <t>Each event receives scores across all 12 rules. A weighted composite (0–10):</t>
+      <c r="A298" s="37" t="inlineStr">
+        <is>
+          <t>| 10 | Off-Hours / Holiday Activity | 6% |</t>
         </is>
       </c>
     </row>
     <row r="299" ht="15" customHeight="1">
-      <c r="A299" s="36" t="inlineStr"/>
+      <c r="A299" s="37" t="inlineStr">
+        <is>
+          <t>| 11 | Timestamp Reversal | 9% |</t>
+        </is>
+      </c>
     </row>
     <row r="300" ht="15" customHeight="1">
       <c r="A300" s="37" t="inlineStr">
         <is>
-          <t>| Rule | Dimension | Weight |</t>
+          <t>| 12 | Service / Shared Account GxP Action | 9% |</t>
         </is>
       </c>
     </row>
     <row r="301" ht="15" customHeight="1">
-      <c r="A301" s="36" t="inlineStr">
-        <is>
-          <t>|------|-----------|--------|</t>
+      <c r="A301" s="37" t="inlineStr">
+        <is>
+          <t>| 13 | Dormant Account Sudden Activity | 7% |</t>
         </is>
       </c>
     </row>
     <row r="302" ht="15" customHeight="1">
       <c r="A302" s="37" t="inlineStr">
         <is>
-          <t>| 11 | Temporal / Holiday | 6% |</t>
+          <t>| 14 | First-Time Behavior Detection | 7% |</t>
         </is>
       </c>
     </row>
     <row r="303" ht="15" customHeight="1">
       <c r="A303" s="37" t="inlineStr">
         <is>
-          <t>| 9  | Velocity burst | 7% |</t>
+          <t>| | **Total** | **109%** |</t>
         </is>
       </c>
     </row>
     <row r="304" ht="15" customHeight="1">
-      <c r="A304" s="37" t="inlineStr">
-        <is>
-          <t>| 8  | Privilege | 9% |</t>
-        </is>
-      </c>
+      <c r="A304" s="36" t="inlineStr"/>
     </row>
     <row r="305" ht="15" customHeight="1">
-      <c r="A305" s="37" t="inlineStr">
-        <is>
-          <t>| 7  | Record sensitivity | 8% |</t>
+      <c r="A305" s="36" t="inlineStr">
+        <is>
+          <t>*Note: Weights are normalised internally — the sum does not need to equal 100%.*</t>
         </is>
       </c>
     </row>
     <row r="306" ht="15" customHeight="1">
-      <c r="A306" s="37" t="inlineStr">
-        <is>
-          <t>| 6  | Delete-Recreate | 8% |</t>
-        </is>
-      </c>
+      <c r="A306" s="36" t="inlineStr"/>
     </row>
     <row r="307" ht="15" customHeight="1">
       <c r="A307" s="37" t="inlineStr">
         <is>
-          <t>| 10 | Timestamp gap | 6% |</t>
+          <t>**Named rule tier overrides:** Rules 3, 5, 11, and 12 at score ≥9 always produce</t>
         </is>
       </c>
     </row>
     <row r="308" ht="15" customHeight="1">
-      <c r="A308" s="37" t="inlineStr">
-        <is>
-          <t>| 1  | Vague Rationale | 7% |</t>
+      <c r="A308" s="36" t="inlineStr">
+        <is>
+          <t>a Critical tier, regardless of composite score. Rule 6 at ≥9 and Rule 7 at 10.0</t>
         </is>
       </c>
     </row>
     <row r="309" ht="15" customHeight="1">
-      <c r="A309" s="37" t="inlineStr">
-        <is>
-          <t>| 2  | Contemporaneous Burst | 7% |</t>
+      <c r="A309" s="36" t="inlineStr">
+        <is>
+          <t>also produce Critical. This ensures named Critical violations are never</t>
         </is>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
-      <c r="A310" s="37" t="inlineStr">
-        <is>
-          <t>| 3  | Admin/GxP Conflict | 10% |</t>
+      <c r="A310" s="36" t="inlineStr">
+        <is>
+          <t>downgraded by a low composite score.</t>
         </is>
       </c>
     </row>
     <row r="311" ht="15" customHeight="1">
-      <c r="A311" s="37" t="inlineStr">
-        <is>
-          <t>| 4  | Change Control Drift | 6% |</t>
-        </is>
-      </c>
-    </row>
-    <row r="312" ht="15" customHeight="1">
-      <c r="A312" s="37" t="inlineStr">
-        <is>
-          <t>| 5  | Failed Login | 8% |</t>
+      <c r="A311" s="36" t="inlineStr"/>
+    </row>
+    <row r="312" ht="8" customHeight="1">
+      <c r="A312" s="38" t="inlineStr">
+        <is>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="313" ht="15" customHeight="1">
-      <c r="A313" s="37" t="inlineStr">
-        <is>
-          <t>| 12 | Timestamp Reversal | 9% |</t>
-        </is>
-      </c>
-    </row>
-    <row r="314" ht="15" customHeight="1">
-      <c r="A314" s="37" t="inlineStr">
-        <is>
-          <t>| 13 | Service Account | 9% |</t>
+      <c r="A313" s="36" t="inlineStr"/>
+    </row>
+    <row r="314" ht="18" customHeight="1">
+      <c r="A314" s="35" t="inlineStr">
+        <is>
+          <t>## Suggested Disposition Logic</t>
         </is>
       </c>
     </row>
     <row r="315" ht="15" customHeight="1">
-      <c r="A315" s="37" t="inlineStr">
-        <is>
-          <t>| 14 | Dormant Account | 7% |</t>
-        </is>
-      </c>
+      <c r="A315" s="36" t="inlineStr"/>
     </row>
     <row r="316" ht="15" customHeight="1">
       <c r="A316" s="37" t="inlineStr">
         <is>
-          <t>| 15 | Suspicious Sequence | 9% |</t>
+          <t>| Condition | Suggested Disposition |</t>
         </is>
       </c>
     </row>
     <row r="317" ht="15" customHeight="1">
-      <c r="A317" s="37" t="inlineStr">
-        <is>
-          <t>| 16 | First-Time Behavior | 7% |</t>
+      <c r="A317" s="36" t="inlineStr">
+        <is>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="318" ht="15" customHeight="1">
       <c r="A318" s="37" t="inlineStr">
         <is>
-          <t>| | **Total** | **123%** |</t>
+          <t>| Rule 11 fired | Escalate to CAPA |</t>
         </is>
       </c>
     </row>
     <row r="319" ht="15" customHeight="1">
-      <c r="A319" s="36" t="inlineStr"/>
+      <c r="A319" s="37" t="inlineStr">
+        <is>
+          <t>| Rule 12 fired (Critical) | Escalate to CAPA |</t>
+        </is>
+      </c>
     </row>
     <row r="320" ht="15" customHeight="1">
-      <c r="A320" s="36" t="inlineStr">
-        <is>
-          <t>*Note: Weights are normalised internally — the sum does not need to equal 100%.*</t>
+      <c r="A320" s="37" t="inlineStr">
+        <is>
+          <t>| Rule 5 fired | Escalate to CAPA |</t>
         </is>
       </c>
     </row>
     <row r="321" ht="15" customHeight="1">
-      <c r="A321" s="36" t="inlineStr"/>
+      <c r="A321" s="37" t="inlineStr">
+        <is>
+          <t>| Rule 3 fired | Escalate to CAPA |</t>
+        </is>
+      </c>
     </row>
     <row r="322" ht="15" customHeight="1">
       <c r="A322" s="37" t="inlineStr">
         <is>
-          <t>**Named rule tier overrides:** Rules 3, 5, 12, and 13 at score ≥9 always produce</t>
+          <t>| Rule 6 fired | Escalate to CAPA |</t>
         </is>
       </c>
     </row>
     <row r="323" ht="15" customHeight="1">
-      <c r="A323" s="36" t="inlineStr">
-        <is>
-          <t>a Critical tier, regardless of composite score. Rule 6 at ≥9 and Rule 7 at 10.0</t>
+      <c r="A323" s="37" t="inlineStr">
+        <is>
+          <t>| Rule 7 (audit ctrl) fired | Escalate to CAPA |</t>
         </is>
       </c>
     </row>
     <row r="324" ht="15" customHeight="1">
-      <c r="A324" s="36" t="inlineStr">
-        <is>
-          <t>also produce Critical. This ensures named Critical violations are never</t>
+      <c r="A324" s="37" t="inlineStr">
+        <is>
+          <t>| Rule 9 (gap) during business hours | Escalate to CAPA |</t>
         </is>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
-      <c r="A325" s="36" t="inlineStr">
-        <is>
-          <t>downgraded by a low composite score.</t>
+      <c r="A325" s="37" t="inlineStr">
+        <is>
+          <t>| Rule 9 (gap) outside business hours | Investigate — Verify Source Data |</t>
         </is>
       </c>
     </row>
     <row r="326" ht="15" customHeight="1">
-      <c r="A326" s="36" t="inlineStr"/>
-    </row>
-    <row r="327" ht="8" customHeight="1">
-      <c r="A327" s="38" t="inlineStr">
-        <is>
-          <t>---</t>
+      <c r="A326" s="37" t="inlineStr">
+        <is>
+          <t>| Rule 4 fired | Escalate to CAPA |</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="15" customHeight="1">
+      <c r="A327" s="37" t="inlineStr">
+        <is>
+          <t>| Rule 1 — blank comment | Escalate to CAPA |</t>
         </is>
       </c>
     </row>
     <row r="328" ht="15" customHeight="1">
-      <c r="A328" s="36" t="inlineStr"/>
-    </row>
-    <row r="329" ht="18" customHeight="1">
-      <c r="A329" s="35" t="inlineStr">
-        <is>
-          <t>## Suggested Disposition Logic</t>
+      <c r="A328" s="37" t="inlineStr">
+        <is>
+          <t>| Rule 1 — vague term | Justified — Amendment Required |</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="15" customHeight="1">
+      <c r="A329" s="37" t="inlineStr">
+        <is>
+          <t>| Rule 13 fired | Investigate — Verify Source Data |</t>
         </is>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
-      <c r="A330" s="36" t="inlineStr"/>
+      <c r="A330" s="37" t="inlineStr">
+        <is>
+          <t>| Rule 2 burst | Investigate — Verify Source Data |</t>
+        </is>
+      </c>
     </row>
     <row r="331" ht="15" customHeight="1">
       <c r="A331" s="37" t="inlineStr">
         <is>
-          <t>| Condition | Suggested Disposition |</t>
+          <t>| Off-hours with comment | Justified — Document Rationale |</t>
         </is>
       </c>
     </row>
     <row r="332" ht="15" customHeight="1">
-      <c r="A332" s="36" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
+      <c r="A332" s="37" t="inlineStr">
+        <is>
+          <t>| Off-hours, no comment | Escalate to CAPA |</t>
         </is>
       </c>
     </row>
     <row r="333" ht="15" customHeight="1">
       <c r="A333" s="37" t="inlineStr">
         <is>
-          <t>| Rule 12 fired | Escalate to CAPA |</t>
+          <t>| No rule triggered significantly | Justified — No Action Required |</t>
         </is>
       </c>
     </row>
     <row r="334" ht="15" customHeight="1">
-      <c r="A334" s="37" t="inlineStr">
-        <is>
-          <t>| Rule 13 fired (Critical) | Escalate to CAPA |</t>
-        </is>
-      </c>
-    </row>
-    <row r="335" ht="15" customHeight="1">
-      <c r="A335" s="37" t="inlineStr">
-        <is>
-          <t>| Rule 5 fired | Escalate to CAPA |</t>
+      <c r="A334" s="36" t="inlineStr"/>
+    </row>
+    <row r="335" ht="8" customHeight="1">
+      <c r="A335" s="38" t="inlineStr">
+        <is>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="336" ht="15" customHeight="1">
-      <c r="A336" s="37" t="inlineStr">
-        <is>
-          <t>| Rule 3 fired | Escalate to CAPA |</t>
-        </is>
-      </c>
-    </row>
-    <row r="337" ht="15" customHeight="1">
-      <c r="A337" s="37" t="inlineStr">
-        <is>
-          <t>| Rule 6 fired | Escalate to CAPA |</t>
+      <c r="A336" s="36" t="inlineStr"/>
+    </row>
+    <row r="337" ht="18" customHeight="1">
+      <c r="A337" s="35" t="inlineStr">
+        <is>
+          <t>## Review Narrative (Summary Sheet)</t>
         </is>
       </c>
     </row>
     <row r="338" ht="15" customHeight="1">
-      <c r="A338" s="37" t="inlineStr">
-        <is>
-          <t>| Rule 7 (audit ctrl) fired | Escalate to CAPA |</t>
-        </is>
-      </c>
+      <c r="A338" s="36" t="inlineStr"/>
     </row>
     <row r="339" ht="15" customHeight="1">
-      <c r="A339" s="37" t="inlineStr">
-        <is>
-          <t>| Rule 10 (gap) during business hours | Escalate to CAPA |</t>
+      <c r="A339" s="36" t="inlineStr">
+        <is>
+          <t>Following the detection analysis, the Summary sheet includes a **Review Narrative**</t>
         </is>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1">
-      <c r="A340" s="37" t="inlineStr">
-        <is>
-          <t>| Rule 10 (gap) outside business hours | Investigate — Verify Source Data |</t>
+      <c r="A340" s="36" t="inlineStr">
+        <is>
+          <t>section — a plain-English paragraph summarising the key findings of the review.</t>
         </is>
       </c>
     </row>
     <row r="341" ht="15" customHeight="1">
-      <c r="A341" s="37" t="inlineStr">
-        <is>
-          <t>| Rule 4 fired | Escalate to CAPA |</t>
+      <c r="A341" s="36" t="inlineStr">
+        <is>
+          <t>This section is generated deterministically from the scored data with no LLM</t>
         </is>
       </c>
     </row>
     <row r="342" ht="15" customHeight="1">
-      <c r="A342" s="37" t="inlineStr">
-        <is>
-          <t>| Rule 1 — blank comment | Escalate to CAPA |</t>
+      <c r="A342" s="36" t="inlineStr">
+        <is>
+          <t>involvement, making it fully reproducible.</t>
         </is>
       </c>
     </row>
     <row r="343" ht="15" customHeight="1">
-      <c r="A343" s="37" t="inlineStr">
-        <is>
-          <t>| Rule 1 — vague term | Justified — Amendment Required |</t>
-        </is>
-      </c>
+      <c r="A343" s="36" t="inlineStr"/>
     </row>
     <row r="344" ht="15" customHeight="1">
-      <c r="A344" s="37" t="inlineStr">
-        <is>
-          <t>| Rule 14 fired | Investigate — Verify Source Data |</t>
+      <c r="A344" s="36" t="inlineStr">
+        <is>
+          <t>The narrative covers:</t>
         </is>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
-      <c r="A345" s="37" t="inlineStr">
-        <is>
-          <t>| Rule 2 burst | Investigate — Verify Source Data |</t>
+      <c r="A345" s="36" t="inlineStr">
+        <is>
+          <t>1. **Volume statement** — total events reviewed, period covered, events escalated</t>
         </is>
       </c>
     </row>
     <row r="346" ht="15" customHeight="1">
-      <c r="A346" s="37" t="inlineStr">
-        <is>
-          <t>| Off-hours with comment | Justified — Document Rationale |</t>
+      <c r="A346" s="36" t="inlineStr">
+        <is>
+          <t>2. **Key findings** — one sentence per significant rule triggered (max 4 findings),</t>
         </is>
       </c>
     </row>
     <row r="347" ht="15" customHeight="1">
-      <c r="A347" s="37" t="inlineStr">
-        <is>
-          <t>| Off-hours, no comment | Escalate to CAPA |</t>
+      <c r="A347" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   naming the user, record, and action type involved</t>
         </is>
       </c>
     </row>
     <row r="348" ht="15" customHeight="1">
-      <c r="A348" s="37" t="inlineStr">
-        <is>
-          <t>| No rule triggered significantly | Justified — No Action Required |</t>
+      <c r="A348" s="36" t="inlineStr">
+        <is>
+          <t>3. **Overall risk assessment** — concludes with one of five risk levels:</t>
         </is>
       </c>
     </row>
     <row r="349" ht="15" customHeight="1">
-      <c r="A349" s="36" t="inlineStr"/>
-    </row>
-    <row r="350" ht="8" customHeight="1">
-      <c r="A350" s="38" t="inlineStr">
-        <is>
-          <t>---</t>
+      <c r="A349" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - High risk — 2+ Critical findings</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" ht="15" customHeight="1">
+      <c r="A350" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Moderate-to-high risk — 1 Critical finding</t>
         </is>
       </c>
     </row>
     <row r="351" ht="15" customHeight="1">
-      <c r="A351" s="36" t="inlineStr"/>
-    </row>
-    <row r="352" ht="18" customHeight="1">
-      <c r="A352" s="35" t="inlineStr">
-        <is>
-          <t>## Review Narrative (Summary Sheet)</t>
+      <c r="A351" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Moderate risk — 3+ High findings</t>
+        </is>
+      </c>
+    </row>
+    <row r="352" ht="15" customHeight="1">
+      <c r="A352" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Low-to-moderate risk — 1–2 High findings</t>
         </is>
       </c>
     </row>
     <row r="353" ht="15" customHeight="1">
-      <c r="A353" s="36" t="inlineStr"/>
+      <c r="A353" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Low risk — no Critical or High findings</t>
+        </is>
+      </c>
     </row>
     <row r="354" ht="15" customHeight="1">
-      <c r="A354" s="36" t="inlineStr">
-        <is>
-          <t>Following the detection analysis, the Summary sheet includes a **Review Narrative**</t>
-        </is>
-      </c>
+      <c r="A354" s="36" t="inlineStr"/>
     </row>
     <row r="355" ht="15" customHeight="1">
       <c r="A355" s="36" t="inlineStr">
         <is>
-          <t>section — a plain-English paragraph summarising the key findings of the review.</t>
+          <t>The narrative is intended to be copied into the introduction of the Periodic Review</t>
         </is>
       </c>
     </row>
     <row r="356" ht="15" customHeight="1">
       <c r="A356" s="36" t="inlineStr">
         <is>
-          <t>This section is generated deterministically from the scored data with no LLM</t>
+          <t>Report Section 9.1.6 or used as a management summary.</t>
         </is>
       </c>
     </row>
     <row r="357" ht="15" customHeight="1">
-      <c r="A357" s="36" t="inlineStr">
-        <is>
-          <t>involvement, making it fully reproducible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="358" ht="15" customHeight="1">
-      <c r="A358" s="36" t="inlineStr"/>
+      <c r="A357" s="36" t="inlineStr"/>
+    </row>
+    <row r="358" ht="8" customHeight="1">
+      <c r="A358" s="38" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="359" ht="15" customHeight="1">
-      <c r="A359" s="36" t="inlineStr">
-        <is>
-          <t>The narrative covers:</t>
-        </is>
-      </c>
-    </row>
-    <row r="360" ht="15" customHeight="1">
-      <c r="A360" s="36" t="inlineStr">
-        <is>
-          <t>1. **Volume statement** — total events reviewed, period covered, events escalated</t>
+      <c r="A359" s="36" t="inlineStr"/>
+    </row>
+    <row r="360" ht="8" customHeight="1">
+      <c r="A360" s="38" t="inlineStr">
+        <is>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="361" ht="15" customHeight="1">
-      <c r="A361" s="36" t="inlineStr">
-        <is>
-          <t>2. **Key findings** — one sentence per significant rule triggered (max 4 findings),</t>
-        </is>
-      </c>
-    </row>
-    <row r="362" ht="15" customHeight="1">
-      <c r="A362" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   naming the user, record, and action type involved</t>
+      <c r="A361" s="36" t="inlineStr"/>
+    </row>
+    <row r="362" ht="18" customHeight="1">
+      <c r="A362" s="35" t="inlineStr">
+        <is>
+          <t>## Not Yet Implemented — Planned Rules</t>
         </is>
       </c>
     </row>
     <row r="363" ht="15" customHeight="1">
-      <c r="A363" s="36" t="inlineStr">
-        <is>
-          <t>3. **Overall risk assessment** — concludes with one of five risk levels:</t>
-        </is>
-      </c>
+      <c r="A363" s="36" t="inlineStr"/>
     </row>
     <row r="364" ht="15" customHeight="1">
       <c r="A364" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - High risk — 2+ Critical findings</t>
+          <t>These checks were designed and scoped but not yet built into the engine.</t>
         </is>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1">
       <c r="A365" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Moderate-to-high risk — 1 Critical finding</t>
+          <t>They are documented here for transparency and future CSV planning.</t>
         </is>
       </c>
     </row>
     <row r="366" ht="15" customHeight="1">
-      <c r="A366" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Moderate risk — 3+ High findings</t>
-        </is>
-      </c>
-    </row>
-    <row r="367" ht="15" customHeight="1">
-      <c r="A367" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Low-to-moderate risk — 1–2 High findings</t>
+      <c r="A366" s="36" t="inlineStr"/>
+    </row>
+    <row r="367" ht="18" customHeight="1">
+      <c r="A367" s="35" t="inlineStr">
+        <is>
+          <t>### Planned Rule 16 — Shared Account / Same User, Two Locations</t>
         </is>
       </c>
     </row>
     <row r="368" ht="15" customHeight="1">
-      <c r="A368" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Low risk — no Critical or High findings</t>
+      <c r="A368" s="37" t="inlineStr">
+        <is>
+          <t>**What it detects:** The same user_id performing actions from two different</t>
         </is>
       </c>
     </row>
     <row r="369" ht="15" customHeight="1">
-      <c r="A369" s="36" t="inlineStr"/>
+      <c r="A369" s="36" t="inlineStr">
+        <is>
+          <t>IP addresses within 30 minutes — physically impossible for one person.</t>
+        </is>
+      </c>
     </row>
     <row r="370" ht="15" customHeight="1">
-      <c r="A370" s="36" t="inlineStr">
-        <is>
-          <t>The narrative is intended to be copied into the introduction of the Periodic Review</t>
+      <c r="A370" s="37" t="inlineStr">
+        <is>
+          <t>**Why not yet built:** Requires an IP address or workstation column in the</t>
         </is>
       </c>
     </row>
     <row r="371" ht="15" customHeight="1">
       <c r="A371" s="36" t="inlineStr">
         <is>
-          <t>Report Section 9.1.6 or used as a management summary.</t>
+          <t>audit trail export. Many systems do not include this by default. Will be</t>
         </is>
       </c>
     </row>
     <row r="372" ht="15" customHeight="1">
-      <c r="A372" s="36" t="inlineStr"/>
-    </row>
-    <row r="373" ht="8" customHeight="1">
-      <c r="A373" s="38" t="inlineStr">
-        <is>
-          <t>---</t>
+      <c r="A372" s="36" t="inlineStr">
+        <is>
+          <t>activated automatically when the column mapper detects an IP column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="373" ht="15" customHeight="1">
+      <c r="A373" s="37" t="inlineStr">
+        <is>
+          <t>**Regulatory basis:** 21 CFR Part 11 §11.300.</t>
         </is>
       </c>
     </row>
     <row r="374" ht="15" customHeight="1">
       <c r="A374" s="36" t="inlineStr"/>
     </row>
-    <row r="375" ht="8" customHeight="1">
-      <c r="A375" s="38" t="inlineStr">
-        <is>
-          <t>---</t>
+    <row r="375" ht="18" customHeight="1">
+      <c r="A375" s="35" t="inlineStr">
+        <is>
+          <t>### Planned Rule 17 — Bulk Export Before Departure</t>
         </is>
       </c>
     </row>
     <row r="376" ht="15" customHeight="1">
-      <c r="A376" s="36" t="inlineStr"/>
-    </row>
-    <row r="377" ht="18" customHeight="1">
-      <c r="A377" s="35" t="inlineStr">
-        <is>
-          <t>## Not Yet Implemented — Planned Rules</t>
+      <c r="A376" s="37" t="inlineStr">
+        <is>
+          <t>**What it detects:** A user exporting or printing large volumes of records</t>
+        </is>
+      </c>
+    </row>
+    <row r="377" ht="15" customHeight="1">
+      <c r="A377" s="36" t="inlineStr">
+        <is>
+          <t>(SELECT, EXPORT, PRINT actions) close to their account deactivation date.</t>
         </is>
       </c>
     </row>
     <row r="378" ht="15" customHeight="1">
-      <c r="A378" s="36" t="inlineStr"/>
+      <c r="A378" s="37" t="inlineStr">
+        <is>
+          <t>**Why not yet built:** Requires an HR termination date as a second input file.</t>
+        </is>
+      </c>
     </row>
     <row r="379" ht="15" customHeight="1">
       <c r="A379" s="36" t="inlineStr">
         <is>
-          <t>These checks were designed and scoped but not yet built into the engine.</t>
+          <t>Cannot be determined from the audit trail alone.</t>
         </is>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1">
-      <c r="A380" s="36" t="inlineStr">
-        <is>
-          <t>They are documented here for transparency and future CSV planning.</t>
+      <c r="A380" s="37" t="inlineStr">
+        <is>
+          <t>**Regulatory basis:** Data protection and confidentiality requirements.</t>
         </is>
       </c>
     </row>
@@ -57306,49 +57297,49 @@
     <row r="382" ht="18" customHeight="1">
       <c r="A382" s="35" t="inlineStr">
         <is>
-          <t>### Planned Rule 16 — Shared Account / Same User, Two Locations</t>
+          <t>### Planned Rule 18 — Activity During Approved Maintenance Window</t>
         </is>
       </c>
     </row>
     <row r="383" ht="15" customHeight="1">
       <c r="A383" s="37" t="inlineStr">
         <is>
-          <t>**What it detects:** The same user_id performing actions from two different</t>
+          <t>**What it detects:** User activity during a scheduled system maintenance</t>
         </is>
       </c>
     </row>
     <row r="384" ht="15" customHeight="1">
       <c r="A384" s="36" t="inlineStr">
         <is>
-          <t>IP addresses within 30 minutes — physically impossible for one person.</t>
+          <t>window, indicating either the maintenance did not occur as planned, or</t>
         </is>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
-      <c r="A385" s="37" t="inlineStr">
-        <is>
-          <t>**Why not yet built:** Requires an IP address or workstation column in the</t>
+      <c r="A385" s="36" t="inlineStr">
+        <is>
+          <t>unauthorised activity occurred during the maintenance period.</t>
         </is>
       </c>
     </row>
     <row r="386" ht="15" customHeight="1">
-      <c r="A386" s="36" t="inlineStr">
-        <is>
-          <t>audit trail export. Many systems do not include this by default. Will be</t>
+      <c r="A386" s="37" t="inlineStr">
+        <is>
+          <t>**Why not yet built:** Requires the approved maintenance schedule (from the</t>
         </is>
       </c>
     </row>
     <row r="387" ht="15" customHeight="1">
       <c r="A387" s="36" t="inlineStr">
         <is>
-          <t>activated automatically when the column mapper detects an IP column.</t>
+          <t>change control system) as a second input file.</t>
         </is>
       </c>
     </row>
     <row r="388" ht="15" customHeight="1">
       <c r="A388" s="37" t="inlineStr">
         <is>
-          <t>**Regulatory basis:** 21 CFR Part 11 §11.300.</t>
+          <t>**Regulatory basis:** 21 CFR Part 11 §11.10(e).</t>
         </is>
       </c>
     </row>
@@ -57358,355 +57349,258 @@
     <row r="390" ht="18" customHeight="1">
       <c r="A390" s="35" t="inlineStr">
         <is>
-          <t>### Planned Rule 17 — Bulk Export Before Departure</t>
+          <t>### Planned Rule 19 — Account Created and Used Same Day</t>
         </is>
       </c>
     </row>
     <row r="391" ht="15" customHeight="1">
       <c r="A391" s="37" t="inlineStr">
         <is>
-          <t>**What it detects:** A user exporting or printing large volumes of records</t>
+          <t>**What it detects:** A new user account that is created and then used to</t>
         </is>
       </c>
     </row>
     <row r="392" ht="15" customHeight="1">
       <c r="A392" s="36" t="inlineStr">
         <is>
-          <t>(SELECT, EXPORT, PRINT actions) close to their account deactivation date.</t>
+          <t>perform GxP data actions on the same day, before training records could</t>
         </is>
       </c>
     </row>
     <row r="393" ht="15" customHeight="1">
-      <c r="A393" s="37" t="inlineStr">
-        <is>
-          <t>**Why not yet built:** Requires an HR termination date as a second input file.</t>
+      <c r="A393" s="36" t="inlineStr">
+        <is>
+          <t>have been completed.</t>
         </is>
       </c>
     </row>
     <row r="394" ht="15" customHeight="1">
-      <c r="A394" s="36" t="inlineStr">
-        <is>
-          <t>Cannot be determined from the audit trail alone.</t>
+      <c r="A394" s="37" t="inlineStr">
+        <is>
+          <t>**Why not yet built:** Requires a user account creation log or training</t>
         </is>
       </c>
     </row>
     <row r="395" ht="15" customHeight="1">
-      <c r="A395" s="37" t="inlineStr">
-        <is>
-          <t>**Regulatory basis:** Data protection and confidentiality requirements.</t>
+      <c r="A395" s="36" t="inlineStr">
+        <is>
+          <t>completion record as a second input file to confirm training status.</t>
         </is>
       </c>
     </row>
     <row r="396" ht="15" customHeight="1">
-      <c r="A396" s="36" t="inlineStr"/>
-    </row>
-    <row r="397" ht="18" customHeight="1">
-      <c r="A397" s="35" t="inlineStr">
-        <is>
-          <t>### Planned Rule 18 — Activity During Approved Maintenance Window</t>
-        </is>
-      </c>
-    </row>
-    <row r="398" ht="15" customHeight="1">
-      <c r="A398" s="37" t="inlineStr">
-        <is>
-          <t>**What it detects:** User activity during a scheduled system maintenance</t>
+      <c r="A396" s="37" t="inlineStr">
+        <is>
+          <t>**Regulatory basis:** 21 CFR Part 11 §11.10(i) — training.</t>
+        </is>
+      </c>
+    </row>
+    <row r="397" ht="15" customHeight="1">
+      <c r="A397" s="36" t="inlineStr"/>
+    </row>
+    <row r="398" ht="8" customHeight="1">
+      <c r="A398" s="38" t="inlineStr">
+        <is>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="399" ht="15" customHeight="1">
-      <c r="A399" s="36" t="inlineStr">
-        <is>
-          <t>window, indicating either the maintenance did not occur as planned, or</t>
-        </is>
-      </c>
-    </row>
-    <row r="400" ht="15" customHeight="1">
-      <c r="A400" s="36" t="inlineStr">
-        <is>
-          <t>unauthorised activity occurred during the maintenance period.</t>
+      <c r="A399" s="36" t="inlineStr"/>
+    </row>
+    <row r="400" ht="18" customHeight="1">
+      <c r="A400" s="35" t="inlineStr">
+        <is>
+          <t>## Validation Evidence</t>
         </is>
       </c>
     </row>
     <row r="401" ht="15" customHeight="1">
-      <c r="A401" s="37" t="inlineStr">
-        <is>
-          <t>**Why not yet built:** Requires the approved maintenance schedule (from the</t>
-        </is>
-      </c>
+      <c r="A401" s="36" t="inlineStr"/>
     </row>
     <row r="402" ht="15" customHeight="1">
       <c r="A402" s="36" t="inlineStr">
         <is>
-          <t>change control system) as a second input file.</t>
+          <t>This document constitutes part of the functional specification for the</t>
         </is>
       </c>
     </row>
     <row r="403" ht="15" customHeight="1">
-      <c r="A403" s="37" t="inlineStr">
-        <is>
-          <t>**Regulatory basis:** 21 CFR Part 11 §11.10(e).</t>
+      <c r="A403" s="36" t="inlineStr">
+        <is>
+          <t>Audit Trail Intelligence module. For Computer System Validation purposes,</t>
         </is>
       </c>
     </row>
     <row r="404" ht="15" customHeight="1">
-      <c r="A404" s="36" t="inlineStr"/>
-    </row>
-    <row r="405" ht="18" customHeight="1">
-      <c r="A405" s="35" t="inlineStr">
-        <is>
-          <t>### Planned Rule 19 — Account Created and Used Same Day</t>
+      <c r="A404" s="36" t="inlineStr">
+        <is>
+          <t>the following test cases should be executed against the sample CSV template</t>
+        </is>
+      </c>
+    </row>
+    <row r="405" ht="15" customHeight="1">
+      <c r="A405" s="36" t="inlineStr">
+        <is>
+          <t>(downloadable from the tool's upload screen) to verify each rule fires correctly:</t>
         </is>
       </c>
     </row>
     <row r="406" ht="15" customHeight="1">
-      <c r="A406" s="37" t="inlineStr">
-        <is>
-          <t>**What it detects:** A new user account that is created and then used to</t>
-        </is>
-      </c>
+      <c r="A406" s="36" t="inlineStr"/>
     </row>
     <row r="407" ht="15" customHeight="1">
-      <c r="A407" s="36" t="inlineStr">
-        <is>
-          <t>perform GxP data actions on the same day, before training records could</t>
+      <c r="A407" s="37" t="inlineStr">
+        <is>
+          <t>| Test Case | Expected Rule | Expected Tier |</t>
         </is>
       </c>
     </row>
     <row r="408" ht="15" customHeight="1">
       <c r="A408" s="36" t="inlineStr">
         <is>
-          <t>have been completed.</t>
+          <t>|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="409" ht="15" customHeight="1">
       <c r="A409" s="37" t="inlineStr">
         <is>
-          <t>**Why not yet built:** Requires a user account creation log or training</t>
+          <t>| UPDATE RESULTS with comment "fixed" | Rule 1 | High |</t>
         </is>
       </c>
     </row>
     <row r="410" ht="15" customHeight="1">
-      <c r="A410" s="36" t="inlineStr">
-        <is>
-          <t>completion record as a second input file to confirm training status.</t>
+      <c r="A410" s="37" t="inlineStr">
+        <is>
+          <t>| 12 RESULT_INSERT in 12 minutes, same user | Rule 2 | Medium |</t>
         </is>
       </c>
     </row>
     <row r="411" ht="15" customHeight="1">
       <c r="A411" s="37" t="inlineStr">
         <is>
-          <t>**Regulatory basis:** 21 CFR Part 11 §11.10(i) — training.</t>
+          <t>| admin_sys INSERT BATCH_RELEASE | Rule 3 | Critical |</t>
         </is>
       </c>
     </row>
     <row r="412" ht="15" customHeight="1">
-      <c r="A412" s="36" t="inlineStr"/>
-    </row>
-    <row r="413" ht="8" customHeight="1">
-      <c r="A413" s="38" t="inlineStr">
-        <is>
-          <t>---</t>
+      <c r="A412" s="37" t="inlineStr">
+        <is>
+          <t>| new_value = 147.3 when mean ≈ 7.1 | Rule 4 | High |</t>
+        </is>
+      </c>
+    </row>
+    <row r="413" ht="15" customHeight="1">
+      <c r="A413" s="37" t="inlineStr">
+        <is>
+          <t>| 3x LOGIN_FAILED → LOGIN → DELETE, 18 min | Rule 5 | Critical |</t>
         </is>
       </c>
     </row>
     <row r="414" ht="15" customHeight="1">
-      <c r="A414" s="36" t="inlineStr"/>
-    </row>
-    <row r="415" ht="18" customHeight="1">
-      <c r="A415" s="35" t="inlineStr">
-        <is>
-          <t>## Validation Evidence</t>
+      <c r="A414" s="37" t="inlineStr">
+        <is>
+          <t>| DELETE then INSERT same record_id, 3 min | Rule 6 | Critical |</t>
+        </is>
+      </c>
+    </row>
+    <row r="415" ht="15" customHeight="1">
+      <c r="A415" s="37" t="inlineStr">
+        <is>
+          <t>| UPDATE AUDIT_TRAIL, new_value = DISABLED | Rule 7 | Critical |</t>
         </is>
       </c>
     </row>
     <row r="416" ht="15" customHeight="1">
-      <c r="A416" s="36" t="inlineStr"/>
+      <c r="A416" s="37" t="inlineStr">
+        <is>
+          <t>| admin_sys DELETE RESULTS | Rule 8 | High |</t>
+        </is>
+      </c>
     </row>
     <row r="417" ht="15" customHeight="1">
-      <c r="A417" s="36" t="inlineStr">
-        <is>
-          <t>This document constitutes part of the functional specification for the</t>
+      <c r="A417" s="37" t="inlineStr">
+        <is>
+          <t>| Same user, same action, 5+ times in 60 min | Rule 2 | Medium |</t>
         </is>
       </c>
     </row>
     <row r="418" ht="15" customHeight="1">
-      <c r="A418" s="36" t="inlineStr">
-        <is>
-          <t>Audit Trail Intelligence module. For Computer System Validation purposes,</t>
+      <c r="A418" s="37" t="inlineStr">
+        <is>
+          <t>| &gt;2 hour gap in timestamps | Rule 9 | High |</t>
         </is>
       </c>
     </row>
     <row r="419" ht="15" customHeight="1">
-      <c r="A419" s="36" t="inlineStr">
-        <is>
-          <t>the following test cases should be executed against the sample CSV template</t>
+      <c r="A419" s="37" t="inlineStr">
+        <is>
+          <t>| Timestamp 02:14 AM weekday | Rule 10 | High |</t>
         </is>
       </c>
     </row>
     <row r="420" ht="15" customHeight="1">
-      <c r="A420" s="36" t="inlineStr">
-        <is>
-          <t>(downloadable from the tool's upload screen) to verify each rule fires correctly:</t>
+      <c r="A420" s="37" t="inlineStr">
+        <is>
+          <t>| Any event on 2024-07-04 | Rule 10 (Holiday) | Medium-High |</t>
         </is>
       </c>
     </row>
     <row r="421" ht="15" customHeight="1">
-      <c r="A421" s="36" t="inlineStr"/>
+      <c r="A421" s="37" t="inlineStr">
+        <is>
+          <t>| Approval timestamp before creation, same record | Rule 11 | Critical |</t>
+        </is>
+      </c>
     </row>
     <row r="422" ht="15" customHeight="1">
       <c r="A422" s="37" t="inlineStr">
         <is>
-          <t>| Test Case | Expected Rule | Expected Tier |</t>
+          <t>| svc_batch INSERT RESULTS | Rule 12 | Critical |</t>
         </is>
       </c>
     </row>
     <row r="423" ht="15" customHeight="1">
-      <c r="A423" s="36" t="inlineStr">
-        <is>
-          <t>|---|---|---|</t>
+      <c r="A423" s="37" t="inlineStr">
+        <is>
+          <t>| Same user, 90+ day gap, then GxP action | Rule 13 | High |</t>
         </is>
       </c>
     </row>
     <row r="424" ht="15" customHeight="1">
       <c r="A424" s="37" t="inlineStr">
         <is>
-          <t>| UPDATE RESULTS with comment "fixed" | Rule 1 | High |</t>
+          <t>| User with 50+ events performs first-ever DELETE | Rule 14 | High |</t>
         </is>
       </c>
     </row>
     <row r="425" ht="15" customHeight="1">
-      <c r="A425" s="37" t="inlineStr">
-        <is>
-          <t>| 12 RESULT_INSERT in 12 minutes, same user | Rule 2 | Medium |</t>
-        </is>
-      </c>
+      <c r="A425" s="36" t="inlineStr"/>
     </row>
     <row r="426" ht="15" customHeight="1">
-      <c r="A426" s="37" t="inlineStr">
-        <is>
-          <t>| admin_sys INSERT BATCH_RELEASE | Rule 3 | Critical |</t>
+      <c r="A426" s="36" t="inlineStr">
+        <is>
+          <t>*This document was generated by the Audit Trail Intelligence module and</t>
         </is>
       </c>
     </row>
     <row r="427" ht="15" customHeight="1">
-      <c r="A427" s="37" t="inlineStr">
-        <is>
-          <t>| new_value = 147.3 when mean ≈ 7.1 | Rule 4 | High |</t>
+      <c r="A427" s="36" t="inlineStr">
+        <is>
+          <t>represents the validated detection logic at the time of this release.</t>
         </is>
       </c>
     </row>
     <row r="428" ht="15" customHeight="1">
-      <c r="A428" s="37" t="inlineStr">
-        <is>
-          <t>| 3x LOGIN_FAILED → LOGIN → DELETE, 18 min | Rule 5 | Critical |</t>
+      <c r="A428" s="36" t="inlineStr">
+        <is>
+          <t>Review and approve as part of the Computer System Validation package.*</t>
         </is>
       </c>
     </row>
     <row r="429" ht="15" customHeight="1">
-      <c r="A429" s="37" t="inlineStr">
-        <is>
-          <t>| DELETE then INSERT same record_id, 3 min | Rule 6 | Critical |</t>
-        </is>
-      </c>
-    </row>
-    <row r="430" ht="15" customHeight="1">
-      <c r="A430" s="37" t="inlineStr">
-        <is>
-          <t>| UPDATE AUDIT_TRAIL, new_value = DISABLED | Rule 7 | Critical |</t>
-        </is>
-      </c>
-    </row>
-    <row r="431" ht="15" customHeight="1">
-      <c r="A431" s="37" t="inlineStr">
-        <is>
-          <t>| admin_sys DELETE RESULTS | Rule 8 | High |</t>
-        </is>
-      </c>
-    </row>
-    <row r="432" ht="15" customHeight="1">
-      <c r="A432" s="37" t="inlineStr">
-        <is>
-          <t>| Same user, same action, 5+ times in 60 min | Rule 9 | Medium |</t>
-        </is>
-      </c>
-    </row>
-    <row r="433" ht="15" customHeight="1">
-      <c r="A433" s="37" t="inlineStr">
-        <is>
-          <t>| &gt;2 hour gap in timestamps | Rule 10 | High |</t>
-        </is>
-      </c>
-    </row>
-    <row r="434" ht="15" customHeight="1">
-      <c r="A434" s="37" t="inlineStr">
-        <is>
-          <t>| Timestamp 02:14 AM weekday | Rule 11 | High |</t>
-        </is>
-      </c>
-    </row>
-    <row r="435" ht="15" customHeight="1">
-      <c r="A435" s="37" t="inlineStr">
-        <is>
-          <t>| Any event on 2024-07-04 | Rule 11 (Holiday) | Medium-High |</t>
-        </is>
-      </c>
-    </row>
-    <row r="436" ht="15" customHeight="1">
-      <c r="A436" s="37" t="inlineStr">
-        <is>
-          <t>| Approval timestamp before creation, same record | Rule 12 | Critical |</t>
-        </is>
-      </c>
-    </row>
-    <row r="437" ht="15" customHeight="1">
-      <c r="A437" s="37" t="inlineStr">
-        <is>
-          <t>| svc_batch INSERT RESULTS | Rule 13 | Critical |</t>
-        </is>
-      </c>
-    </row>
-    <row r="438" ht="15" customHeight="1">
-      <c r="A438" s="37" t="inlineStr">
-        <is>
-          <t>| Same user, 90+ day gap, then GxP action | Rule 14 | High |</t>
-        </is>
-      </c>
-    </row>
-    <row r="439" ht="15" customHeight="1">
-      <c r="A439" s="37" t="inlineStr">
-        <is>
-          <t>| User with 50+ events performs first-ever DELETE | Rule 16 | High |</t>
-        </is>
-      </c>
-    </row>
-    <row r="440" ht="15" customHeight="1">
-      <c r="A440" s="36" t="inlineStr"/>
-    </row>
-    <row r="441" ht="15" customHeight="1">
-      <c r="A441" s="36" t="inlineStr">
-        <is>
-          <t>*This document was generated by the Audit Trail Intelligence module and</t>
-        </is>
-      </c>
-    </row>
-    <row r="442" ht="15" customHeight="1">
-      <c r="A442" s="36" t="inlineStr">
-        <is>
-          <t>represents the validated detection logic at the time of this release.</t>
-        </is>
-      </c>
-    </row>
-    <row r="443" ht="15" customHeight="1">
-      <c r="A443" s="36" t="inlineStr">
-        <is>
-          <t>Review and approve as part of the Computer System Validation package.*</t>
-        </is>
-      </c>
-    </row>
-    <row r="444" ht="15" customHeight="1">
-      <c r="A444" s="36" t="inlineStr"/>
+      <c r="A429" s="36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AuditTrail_today.xlsx
+++ b/AuditTrail_today.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>BioSysv1</t>
+          <t>BioSysLIMSv2</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>01-Jan-2022  →  31-Mar-2026</t>
+          <t>01-Jan-2026  →  31-Mar-2026</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
     <row r="34" ht="110" customHeight="1">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t>The audit trail for BioSysv1 was reviewed from 01-Jan-2022 to 31-Mar-2026. Of 1,000 recorded events, 6 were escalated for review (4 Critical, 2 High). Full dataset tier distribution is available in the Full Audit Log sheet.
+          <t>The audit trail for BioSysLIMSv2 was reviewed from 01-Jan-2026 to 31-Mar-2026. Of 1,000 recorded events, 6 were escalated for review (4 Critical, 2 High). Full dataset tier distribution is available in the Full Audit Log sheet.
 4 instances of missing or inadequate change rationale were observed across multiple records, indicating deficiencies in data attribution practices.
 A system administrator (admin_sys) directly modified production BATCH_RELEASE data on record BATCH-999, which is inconsistent with Segregation of Duties expectations under 21 CFR Part 11 §11.10(d).
 A delete-and-recreate pattern was identified on record RES-8888 by user 'analyst_y', a known method for circumventing locked record controls.
@@ -1130,7 +1130,7 @@
     <row r="37" ht="72" customHeight="1">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>This audit trail review was performed using rule-based anomaly detection with system-generated narrative summaries. All risk classifications are derived from deterministic rules; narrative text does not influence risk scoring or tier assignment. 1,000 records were reviewed across the period 01-Jan-2022 to 31-Mar-2026. 99.4% of records were automatically cleared as low risk. The 6 records requiring review are documented in the 'Events for Review' sheet. Each finding has been independently reviewed and dispositioned by the undersigned reviewer. The 'System-Proposed Disposition' column is informational only; the reviewer's determination in the 'Reviewer Decision' column reflects independent human judgement and is the authoritative record. Regulatory basis: 21 CFR Part 11 §11.10(e) and EU Annex 11 Clause 9.
+          <t>This audit trail review was performed using rule-based anomaly detection with system-generated narrative summaries. All risk classifications are derived from deterministic rules; narrative text does not influence risk scoring or tier assignment. 1,000 records were reviewed across the period 01-Jan-2026 to 31-Mar-2026. 99.4% of records were automatically cleared as low risk. The 6 records requiring review are documented in the 'Events for Review' sheet. Each finding has been independently reviewed and dispositioned by the undersigned reviewer. The 'System-Proposed Disposition' column is informational only; the reviewer's determination in the 'Reviewer Decision' column reflects independent human judgement and is the authoritative record. Regulatory basis: 21 CFR Part 11 §11.10(e) and EU Annex 11 Clause 9.
 Timezone note: Off-hours scoring (Rule 10) assumes all timestamps in the uploaded file are in the same timezone. If your system exports timestamps in UTC or a non-local timezone, off-hours flags should be interpreted accordingly. Reviewers should verify local shift patterns before dispositing temporal anomalies.</t>
         </is>
       </c>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="M2" s="16" t="inlineStr">
         <is>
-          <t>dba_prod performed UPDATE on AUDIT_TRAIL/SYS-001 at 13:00 on 23-Mar-2026; comment reads "System maintenance".</t>
+          <t>dba_prod performed UPDATE on AUDIT_TRAIL/SYS-001 at 2026-03-23 13:00:00; comment on file reads 'System maintenance'.</t>
         </is>
       </c>
       <c r="N2" s="16" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="M3" s="24" t="inlineStr">
         <is>
-          <t>analyst_y performed DELETE on RESULTS/RES-8888 at 18:00 on 23-Mar-2026 as part of delete-recreate sequence; comment reads "Error".</t>
+          <t>analyst_y performed DELETE on RESULTS/RES-8888 at 2026-03-23 18:00:00; comment on file reads 'Error' — Part of delete-recreate sequence — original record (RES-8888) deleted here.</t>
         </is>
       </c>
       <c r="N3" s="24" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="M4" s="16" t="inlineStr">
         <is>
-          <t>analyst_z performed UPDATE on RESULTS/RES-1200 at 00:40 on 24-Mar-2026; comment reads "Outlier test".</t>
+          <t>analyst_z performed UPDATE on RESULTS/RES-1200 at 2026-03-24 00:40:00; comment on file reads 'Outlier test'.</t>
         </is>
       </c>
       <c r="N4" s="16" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="M5" s="24" t="inlineStr">
         <is>
-          <t>admin_sys performed INSERT on BATCH_RELEASE/BATCH-999 at 09:00 on 23-Mar-2026; comment reads "Urgent release".</t>
+          <t>admin_sys performed INSERT on BATCH_RELEASE/BATCH-999 at 2026-03-23 09:00:00; comment on file reads 'Urgent release'.</t>
         </is>
       </c>
       <c r="N5" s="24" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="M6" s="16" t="inlineStr">
         <is>
-          <t>analyst_x performed DELETE on RESULTS/RES-5050 at 10:15 on 23-Mar-2026; comment reads "Cleaning up error".</t>
+          <t>analyst_x performed DELETE on RESULTS/RES-5050 at 2026-03-23 10:15:00; comment on file reads 'Cleaning up error'.</t>
         </is>
       </c>
       <c r="N6" s="16" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="M7" s="24" t="inlineStr">
         <is>
-          <t>analyst_y performed INSERT on RESULTS/RES-8888 at 18:15 on 23-Mar-2026 with comment "Correction"; record was recreated after deletion in delete-recreate sequence.</t>
+          <t>analyst_y performed INSERT on RESULTS/RES-8888 at 2026-03-23 18:15:00; comment on file reads 'Correction' — Part of delete-recreate sequence — record (RES-8888) recreated here after deletion.</t>
         </is>
       </c>
       <c r="N7" s="24" t="inlineStr">
@@ -54905,7 +54905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A429"/>
+  <dimension ref="A1:A447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -55062,708 +55062,716 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="37" t="inlineStr">
         <is>
-          <t>**Regulatory basis:** 21 CFR Part 211.68; ALCOA+ Attributable and Legible.</t>
+          <t>**SOP reference exemption:** Comments that cite a procedure by reference</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="37" t="inlineStr">
-        <is>
-          <t>**Threshold justification:** Vague rationale terms leave GxP data changes</t>
+      <c r="A26" s="36" t="inlineStr">
+        <is>
+          <t>(e.g. "per SOP-01", "as per WOI-003") are exempt from copy-paste escalation</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="36" t="inlineStr">
         <is>
+          <t>regardless of how many records share the same comment, provided the comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="36" t="inlineStr">
+        <is>
+          <t>is not otherwise vague.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="37" t="inlineStr">
+        <is>
+          <t>**Regulatory basis:** 21 CFR Part 211.68; ALCOA+ Attributable and Legible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="37" t="inlineStr">
+        <is>
+          <t>**Threshold justification:** Vague rationale terms leave GxP data changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="36" t="inlineStr">
+        <is>
           <t>unattributable and untraceable, making them impossible to evaluate during an audit.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="36" t="inlineStr"/>
-    </row>
-    <row r="29" ht="8" customHeight="1">
-      <c r="A29" s="38" t="inlineStr">
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="36" t="inlineStr"/>
+    </row>
+    <row r="33" ht="8" customHeight="1">
+      <c r="A33" s="38" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="36" t="inlineStr"/>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="35" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="36" t="inlineStr"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="35" t="inlineStr">
         <is>
           <t>### Rule 2 — Contemporaneous Burst [Risk: MEDIUM]</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="37" t="inlineStr">
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="37" t="inlineStr">
         <is>
           <t>**Target:** INSERT, RESULT_INSERT, CREATE, ADD actions by any single user.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="37" t="inlineStr">
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="37" t="inlineStr">
         <is>
           <t>**Trigger:** More than 10 such actions by the same user within any 15-minute window.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="37" t="inlineStr">
-        <is>
-          <t>**Regulatory basis:** ALCOA+ Contemporaneous; EU Annex 11 Clause 9.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="37" t="inlineStr">
-        <is>
-          <t>**Threshold justification:** 10 entries in 15 minutes = one every 90 seconds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="36" t="inlineStr">
-        <is>
-          <t>Physiologically possible but statistically unusual for complex measurements.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="36" t="inlineStr">
-        <is>
-          <t>Threshold is conservative to minimise false positives on high-throughput workflows.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="37" t="inlineStr">
         <is>
-          <t>**Deduplication note:** When this rule fires across multiple rows from the same</t>
+          <t>**Regulatory basis:** ALCOA+ Contemporaneous; EU Annex 11 Clause 9.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="36" t="inlineStr">
-        <is>
-          <t>burst, only one representative event appears in the Top 20 escalated list.</t>
+      <c r="A39" s="37" t="inlineStr">
+        <is>
+          <t>**Threshold justification:** 10 entries in 15 minutes = one every 90 seconds.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="36" t="inlineStr">
         <is>
+          <t>Physiologically possible but statistically unusual for complex measurements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="36" t="inlineStr">
+        <is>
+          <t>Threshold is conservative to minimise false positives on high-throughput workflows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="37" t="inlineStr">
+        <is>
+          <t>**Deduplication note:** When this rule fires across multiple rows from the same</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="36" t="inlineStr">
+        <is>
+          <t>burst, only one representative event appears in the Top Events escalated list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="36" t="inlineStr">
+        <is>
           <t>All events remain visible in the Full Audit Log sheet.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="36" t="inlineStr"/>
-    </row>
-    <row r="42" ht="8" customHeight="1">
-      <c r="A42" s="38" t="inlineStr">
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="36" t="inlineStr"/>
+    </row>
+    <row r="46" ht="8" customHeight="1">
+      <c r="A46" s="38" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="36" t="inlineStr"/>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="35" t="inlineStr">
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="36" t="inlineStr"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="35" t="inlineStr">
         <is>
           <t>### Rule 3 — Admin / GxP Conflict [Risk: CRITICAL]</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="37" t="inlineStr">
-        <is>
-          <t>**Target:** Users with roles containing Admin, DBA, Administrator, Sysadmin.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="37" t="inlineStr">
-        <is>
-          <t>**Trigger:** That user performs INSERT, UPDATE, CREATE, or MODIFY on:</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="36" t="inlineStr">
-        <is>
-          <t>SAMPLE_DATA, BATCH_RELEASE, BATCH, RESULTS, or RESULT.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="37" t="inlineStr">
-        <is>
-          <t>**Regulatory basis:** 21 CFR Part 11 §11.10(d); Segregation of Duties.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" s="37" t="inlineStr">
         <is>
-          <t>**Why Critical:** Admin accounts are authorised for system configuration only.</t>
+          <t>**Target:** Users with roles containing Admin, DBA, Administrator, Sysadmin.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="36" t="inlineStr">
-        <is>
-          <t>Direct modification of production records bypasses the standard review workflow,</t>
+      <c r="A50" s="37" t="inlineStr">
+        <is>
+          <t>**Trigger:** That user performs INSERT, UPDATE, CREATE, or MODIFY on:</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="36" t="inlineStr">
         <is>
+          <t>SAMPLE_DATA, BATCH_RELEASE, BATCH, RESULTS, or RESULT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="37" t="inlineStr">
+        <is>
+          <t>**Regulatory basis:** 21 CFR Part 11 §11.10(d); Segregation of Duties.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="37" t="inlineStr">
+        <is>
+          <t>**Why Critical:** Admin accounts are authorised for system configuration only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" s="36" t="inlineStr">
+        <is>
+          <t>Direct modification of production records bypasses the standard review workflow,</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="36" t="inlineStr">
+        <is>
           <t>creating an uncontrolled change pathway with no independent oversight.</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="36" t="inlineStr"/>
-    </row>
-    <row r="53" ht="8" customHeight="1">
-      <c r="A53" s="38" t="inlineStr">
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="36" t="inlineStr"/>
+    </row>
+    <row r="57" ht="8" customHeight="1">
+      <c r="A57" s="38" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="36" t="inlineStr"/>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="35" t="inlineStr">
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="36" t="inlineStr"/>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="35" t="inlineStr">
         <is>
           <t>### Rule 4 — Change Control Drift [Risk: HIGH]</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="37" t="inlineStr">
-        <is>
-          <t>**Target:** Events with a populated new_value column containing numeric data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="37" t="inlineStr">
-        <is>
-          <t>**Trigger:** Numeric new_value deviates by more than 3 standard deviations from</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="36" t="inlineStr">
-        <is>
-          <t>the mean of all new_values for the same record_type in the uploaded file.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="15" customHeight="1">
-      <c r="A59" s="37" t="inlineStr">
-        <is>
-          <t>**Regulatory basis:** 21 CFR Part 820.70(b); validated state requirements.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="37" t="inlineStr">
         <is>
-          <t>**Threshold justification:** 3 standard deviations is a statistically robust</t>
+          <t>**Target:** Events with a populated new_value column containing numeric data.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
-      <c r="A61" s="36" t="inlineStr">
-        <is>
-          <t>outlier threshold. The reference distribution is computed from the uploaded file</t>
+      <c r="A61" s="37" t="inlineStr">
+        <is>
+          <t>**Trigger:** Numeric new_value deviates by more than 3 standard deviations from</t>
         </is>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="36" t="inlineStr">
         <is>
-          <t>itself, making the rule system-agnostic.</t>
+          <t>the mean of all new_values for the same record_type in the uploaded file.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" s="37" t="inlineStr">
         <is>
+          <t>**Regulatory basis:** 21 CFR Part 820.70(b); validated state requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="15" customHeight="1">
+      <c r="A64" s="37" t="inlineStr">
+        <is>
+          <t>**Threshold justification:** 3 standard deviations is a statistically robust</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="15" customHeight="1">
+      <c r="A65" s="36" t="inlineStr">
+        <is>
+          <t>outlier threshold. The reference distribution is computed from the uploaded file</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="15" customHeight="1">
+      <c r="A66" s="36" t="inlineStr">
+        <is>
+          <t>itself, making the rule system-agnostic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="15" customHeight="1">
+      <c r="A67" s="37" t="inlineStr">
+        <is>
           <t>**Limitation:** Only numeric new_value data is scored. Status values such as</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="15" customHeight="1">
-      <c r="A64" s="36" t="inlineStr">
+    <row r="68" ht="15" customHeight="1">
+      <c r="A68" s="36" t="inlineStr">
         <is>
           <t>RELEASED or PENDING are not evaluated by this rule.</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="15" customHeight="1">
-      <c r="A65" s="36" t="inlineStr"/>
-    </row>
-    <row r="66" ht="8" customHeight="1">
-      <c r="A66" s="38" t="inlineStr">
+    <row r="69" ht="15" customHeight="1">
+      <c r="A69" s="36" t="inlineStr"/>
+    </row>
+    <row r="70" ht="8" customHeight="1">
+      <c r="A70" s="38" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1">
-      <c r="A67" s="36" t="inlineStr"/>
-    </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="35" t="inlineStr">
+    <row r="71" ht="15" customHeight="1">
+      <c r="A71" s="36" t="inlineStr"/>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="35" t="inlineStr">
         <is>
           <t>### Rule 5 — Failed Login → Data Manipulation [Risk: CRITICAL]</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="15" customHeight="1">
-      <c r="A69" s="37" t="inlineStr">
-        <is>
-          <t>**Target:** All users.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="15" customHeight="1">
-      <c r="A70" s="37" t="inlineStr">
-        <is>
-          <t>**Trigger:** 3+ LOGIN_FAILED / AUTHENTICATION_FAILED events within 120 minutes</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="15" customHeight="1">
-      <c r="A71" s="36" t="inlineStr">
-        <is>
-          <t>before a successful LOGIN, followed by DELETE, UPDATE, MODIFY, or INSERT on a</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="15" customHeight="1">
-      <c r="A72" s="36" t="inlineStr">
-        <is>
-          <t>GxP record within 30 minutes of that login.</t>
         </is>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" s="37" t="inlineStr">
         <is>
-          <t>**Regulatory basis:** 21 CFR Part 11 §11.300; ALCOA+ Original.</t>
+          <t>**Target:** All users.</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="37" t="inlineStr">
         <is>
-          <t>**Threshold justification:** 3 failed attempts is the industry-standard threshold</t>
+          <t>**Trigger:** 3+ LOGIN_FAILED / AUTHENTICATION_FAILED events within 120 minutes</t>
         </is>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" s="36" t="inlineStr">
         <is>
-          <t>for flagging a brute-force or credential-stuffing attempt. The 30-minute post-login</t>
+          <t>before a successful LOGIN, followed by DELETE, UPDATE, MODIFY, or INSERT on a</t>
         </is>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" s="36" t="inlineStr">
         <is>
+          <t>GxP record within 30 minutes of that login.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="A77" s="37" t="inlineStr">
+        <is>
+          <t>**Regulatory basis:** 21 CFR Part 11 §11.300; ALCOA+ Original.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="A78" s="37" t="inlineStr">
+        <is>
+          <t>**Threshold justification:** 3 failed attempts is the industry-standard threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="A79" s="36" t="inlineStr">
+        <is>
+          <t>for flagging a brute-force or credential-stuffing attempt. The 30-minute post-login</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="15" customHeight="1">
+      <c r="A80" s="36" t="inlineStr">
+        <is>
           <t>window captures immediate post-access manipulation. The 120-minute lookback covers</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1">
-      <c r="A77" s="36" t="inlineStr">
+    <row r="81" ht="15" customHeight="1">
+      <c r="A81" s="36" t="inlineStr">
         <is>
           <t>slow credential attacks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="15" customHeight="1">
-      <c r="A78" s="36" t="inlineStr"/>
-    </row>
-    <row r="79" ht="8" customHeight="1">
-      <c r="A79" s="38" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="15" customHeight="1">
-      <c r="A80" s="36" t="inlineStr"/>
-    </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="35" t="inlineStr">
-        <is>
-          <t>## Dimension-Based Rules</t>
         </is>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" s="36" t="inlineStr"/>
     </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="35" t="inlineStr">
+    <row r="83" ht="8" customHeight="1">
+      <c r="A83" s="38" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="15" customHeight="1">
+      <c r="A84" s="36" t="inlineStr"/>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="35" t="inlineStr">
+        <is>
+          <t>## Dimension-Based Rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="15" customHeight="1">
+      <c r="A86" s="36" t="inlineStr"/>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="35" t="inlineStr">
         <is>
           <t>### Rule 6 — Delete and Recreate Pattern [Risk: CRITICAL]</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="15" customHeight="1">
-      <c r="A84" s="37" t="inlineStr">
-        <is>
-          <t>**Target:** All record types with a populated record_id column.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="15" customHeight="1">
-      <c r="A85" s="37" t="inlineStr">
-        <is>
-          <t>**Trigger:** Same user deletes a record_id and creates a new record with the same</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="15" customHeight="1">
-      <c r="A86" s="36" t="inlineStr">
-        <is>
-          <t>record_id within 4 hours. Score: 9.0 on both the delete and recreate events.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="15" customHeight="1">
-      <c r="A87" s="37" t="inlineStr">
-        <is>
-          <t>**Regulatory basis:** 21 CFR Part 11 §11.10(e); ALCOA+ Original.</t>
         </is>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1">
       <c r="A88" s="37" t="inlineStr">
         <is>
-          <t>**Why Critical:** GxP systems typically lock approved records to prevent editing.</t>
+          <t>**Target:** All record types with a populated record_id column.</t>
         </is>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1">
-      <c r="A89" s="36" t="inlineStr">
-        <is>
-          <t>Deleting and recreating the same record is a known method of modifying locked data</t>
+      <c r="A89" s="37" t="inlineStr">
+        <is>
+          <t>**Trigger:** Same user deletes a record_id and creates a new record with the same</t>
         </is>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
       <c r="A90" s="36" t="inlineStr">
         <is>
+          <t>record_id within 4 hours. Score: 9.0 on both the delete and recreate events.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="15" customHeight="1">
+      <c r="A91" s="36" t="inlineStr">
+        <is>
+          <t>Also detects three-step sequences (UPDATE → DELETE → INSERT) on the same record_id.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="15" customHeight="1">
+      <c r="A92" s="37" t="inlineStr">
+        <is>
+          <t>**Regulatory basis:** 21 CFR Part 11 §11.10(e); ALCOA+ Original.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="15" customHeight="1">
+      <c r="A93" s="37" t="inlineStr">
+        <is>
+          <t>**Why Critical:** GxP systems typically lock approved records to prevent editing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="15" customHeight="1">
+      <c r="A94" s="36" t="inlineStr">
+        <is>
+          <t>Deleting and recreating the same record is a known method of modifying locked data</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="15" customHeight="1">
+      <c r="A95" s="36" t="inlineStr">
+        <is>
           <t>while making the change appear as a new entry.</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="15" customHeight="1">
-      <c r="A91" s="37" t="inlineStr">
+    <row r="96" ht="15" customHeight="1">
+      <c r="A96" s="37" t="inlineStr">
         <is>
           <t>**4-hour window:** Set to capture same-session recreation while excluding legitimate</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="15" customHeight="1">
-      <c r="A92" s="36" t="inlineStr">
+    <row r="97" ht="15" customHeight="1">
+      <c r="A97" s="36" t="inlineStr">
         <is>
           <t>archival or system migration workflows that occur over longer periods.</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="15" customHeight="1">
-      <c r="A93" s="36" t="inlineStr"/>
-    </row>
-    <row r="94" ht="8" customHeight="1">
-      <c r="A94" s="38" t="inlineStr">
+    <row r="98" ht="15" customHeight="1">
+      <c r="A98" s="36" t="inlineStr"/>
+    </row>
+    <row r="99" ht="8" customHeight="1">
+      <c r="A99" s="38" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="15" customHeight="1">
-      <c r="A95" s="36" t="inlineStr"/>
-    </row>
-    <row r="96" ht="18" customHeight="1">
-      <c r="A96" s="35" t="inlineStr">
+    <row r="100" ht="15" customHeight="1">
+      <c r="A100" s="36" t="inlineStr"/>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="A101" s="35" t="inlineStr">
         <is>
           <t>### Rule 7 — Audit Trail Integrity Event [Risk: CRITICAL / HIGH / MEDIUM]</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="15" customHeight="1">
-      <c r="A97" s="37" t="inlineStr">
-        <is>
-          <t>**Trigger (Critical — 10.0):** action_type or record_type contains keywords</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="15" customHeight="1">
-      <c r="A98" s="36" t="inlineStr">
-        <is>
-          <t>indicating audit trail configuration was changed: audit trail, audit log,</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="15" customHeight="1">
-      <c r="A99" s="36" t="inlineStr">
-        <is>
-          <t>log enabled, log disabled, audit enabled, audit disabled, configuration change,</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="15" customHeight="1">
-      <c r="A100" s="36" t="inlineStr">
-        <is>
-          <t>system setting.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="15" customHeight="1">
-      <c r="A101" s="37" t="inlineStr">
-        <is>
-          <t>**Trigger (High — 8.0):** A delete action on a GxP-sensitive record type.</t>
         </is>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="A102" s="37" t="inlineStr">
         <is>
-          <t>**Note:** Non-destructive read/access actions on GxP-sensitive record types</t>
+          <t>**Trigger (Critical — 10.0):** action_type or record_type contains keywords</t>
         </is>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="A103" s="36" t="inlineStr">
         <is>
-          <t>(SELECT, VIEW, READ) are no longer scored. Only audit trail integrity events</t>
+          <t>indicating audit trail configuration was changed: audit trail, audit log,</t>
         </is>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1">
       <c r="A104" s="36" t="inlineStr">
         <is>
-          <t>(Critical) and sensitive record deletions (High) produce a Rule 7 score.</t>
+          <t>log enabled, log disabled, audit enabled, audit disabled, configuration change,</t>
         </is>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
       <c r="A105" s="36" t="inlineStr">
         <is>
-          <t>This prevents routine system use from appearing as false positives.</t>
+          <t>system setting.</t>
         </is>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1">
       <c r="A106" s="37" t="inlineStr">
         <is>
-          <t>**GxP-sensitive record types include:** batch record, audit trail, electronic</t>
+          <t>**Trigger (High — 8.0):** A delete action on a GxP-sensitive record type.</t>
         </is>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1">
-      <c r="A107" s="36" t="inlineStr">
-        <is>
-          <t>signature, test result, clinical, raw data, master data, configuration, user</t>
+      <c r="A107" s="37" t="inlineStr">
+        <is>
+          <t>**Note:** Non-destructive read/access actions on GxP-sensitive record types</t>
         </is>
       </c>
     </row>
     <row r="108" ht="15" customHeight="1">
       <c r="A108" s="36" t="inlineStr">
         <is>
+          <t>(SELECT, VIEW, READ) are no longer scored. Only audit trail integrity events</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="15" customHeight="1">
+      <c r="A109" s="36" t="inlineStr">
+        <is>
+          <t>(Critical) and sensitive record deletions (High) produce a Rule 7 score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="15" customHeight="1">
+      <c r="A110" s="36" t="inlineStr">
+        <is>
+          <t>This prevents routine system use from appearing as false positives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="15" customHeight="1">
+      <c r="A111" s="37" t="inlineStr">
+        <is>
+          <t>**GxP-sensitive record types include:** batch record, audit trail, electronic</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="15" customHeight="1">
+      <c r="A112" s="36" t="inlineStr">
+        <is>
+          <t>signature, test result, clinical, raw data, master data, configuration, user</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="15" customHeight="1">
+      <c r="A113" s="36" t="inlineStr">
+        <is>
           <t>account, role, permission, quality record, change control, deviation, CAPA, OOS.</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="15" customHeight="1">
-      <c r="A109" s="37" t="inlineStr">
-        <is>
-          <t>**Regulatory basis:** 21 CFR Part 11 §11.10(e).</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="15" customHeight="1">
-      <c r="A110" s="36" t="inlineStr"/>
-    </row>
-    <row r="111" ht="8" customHeight="1">
-      <c r="A111" s="38" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="15" customHeight="1">
-      <c r="A112" s="36" t="inlineStr"/>
-    </row>
-    <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="35" t="inlineStr">
-        <is>
-          <t>### Rule 8 — Privileged User on GxP Data [Risk: HIGH]</t>
         </is>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1">
       <c r="A114" s="37" t="inlineStr">
         <is>
+          <t>**Regulatory basis:** 21 CFR Part 11 §11.10(e).</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="15" customHeight="1">
+      <c r="A115" s="36" t="inlineStr"/>
+    </row>
+    <row r="116" ht="8" customHeight="1">
+      <c r="A116" s="38" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="15" customHeight="1">
+      <c r="A117" s="36" t="inlineStr"/>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="A118" s="35" t="inlineStr">
+        <is>
+          <t>### Rule 8 — Privileged User on GxP Data [Risk: HIGH]</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="15" customHeight="1">
+      <c r="A119" s="37" t="inlineStr">
+        <is>
           <t>**Trigger:** A user with an admin-keyword role (admin, sysadmin, DBA, root,</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="15" customHeight="1">
-      <c r="A115" s="36" t="inlineStr">
+    <row r="120" ht="15" customHeight="1">
+      <c r="A120" s="36" t="inlineStr">
         <is>
           <t>service, superuser, power user) performs a modify or delete on a GxP-sensitive</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="15" customHeight="1">
-      <c r="A116" s="36" t="inlineStr">
+    <row r="121" ht="15" customHeight="1">
+      <c r="A121" s="36" t="inlineStr">
         <is>
           <t>record. Score: 8.0 if record is sensitive; 7.0 otherwise.</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="15" customHeight="1">
-      <c r="A117" s="37" t="inlineStr">
+    <row r="122" ht="15" customHeight="1">
+      <c r="A122" s="37" t="inlineStr">
         <is>
           <t>**Distinction from Rule 3:** Rule 3 fires on specific high-risk table names</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="15" customHeight="1">
-      <c r="A118" s="36" t="inlineStr">
+    <row r="123" ht="15" customHeight="1">
+      <c r="A123" s="36" t="inlineStr">
         <is>
           <t>(BATCH_RELEASE, SAMPLE_DATA etc.). Rule 8 fires on record type sensitivity</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="15" customHeight="1">
-      <c r="A119" s="36" t="inlineStr">
+    <row r="124" ht="15" customHeight="1">
+      <c r="A124" s="36" t="inlineStr">
         <is>
           <t>keywords and covers a broader range of tables.</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="15" customHeight="1">
-      <c r="A120" s="37" t="inlineStr">
-        <is>
-          <t>**Regulatory basis:** 21 CFR Part 11 §11.10(d); Segregation of Duties.</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="15" customHeight="1">
-      <c r="A121" s="36" t="inlineStr"/>
-    </row>
-    <row r="122" ht="8" customHeight="1">
-      <c r="A122" s="38" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="15" customHeight="1">
-      <c r="A123" s="36" t="inlineStr"/>
-    </row>
-    <row r="124" ht="18" customHeight="1">
-      <c r="A124" s="35" t="inlineStr">
-        <is>
-          <t>### Rule 9 — High-Volume Activity Burst [Risk: MEDIUM]</t>
         </is>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
       <c r="A125" s="37" t="inlineStr">
         <is>
-          <t>**Trigger:** Same user performs the same action_type 5+ times within 60 minutes.</t>
+          <t>**Regulatory basis:** 21 CFR Part 11 §11.10(d); Segregation of Duties.</t>
         </is>
       </c>
     </row>
     <row r="126" ht="15" customHeight="1">
-      <c r="A126" s="37" t="inlineStr">
-        <is>
-          <t>**Distinction from Rule 2:** Rule 2 is INSERT-specific with a 15-minute window</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="15" customHeight="1">
-      <c r="A127" s="36" t="inlineStr">
-        <is>
-          <t>and a threshold of 10. Rule 9 applies to any action type with a 60-minute window</t>
+      <c r="A126" s="36" t="inlineStr"/>
+    </row>
+    <row r="127" ht="8" customHeight="1">
+      <c r="A127" s="38" t="inlineStr">
+        <is>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="128" ht="15" customHeight="1">
-      <c r="A128" s="36" t="inlineStr">
-        <is>
-          <t>and a threshold of 5. Both can fire independently.</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="15" customHeight="1">
-      <c r="A129" s="37" t="inlineStr">
-        <is>
-          <t>**Score:** Proportional to (count ÷ threshold × 3.5), capped at 10.0.</t>
+      <c r="A128" s="36" t="inlineStr"/>
+    </row>
+    <row r="129" ht="18" customHeight="1">
+      <c r="A129" s="35" t="inlineStr">
+        <is>
+          <t>### Rule 9 — Audit Trail Timestamp Gap [Risk: HIGH]</t>
         </is>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
       <c r="A130" s="37" t="inlineStr">
         <is>
-          <t>**Regulatory basis:** ALCOA+ Contemporaneous.</t>
+          <t>**Trigger:** A gap of more than 2 hours between consecutive audit trail entries</t>
         </is>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1">
-      <c r="A131" s="36" t="inlineStr"/>
-    </row>
-    <row r="132" ht="8" customHeight="1">
-      <c r="A132" s="38" t="inlineStr">
-        <is>
-          <t>---</t>
+      <c r="A131" s="36" t="inlineStr">
+        <is>
+          <t>(sorted by timestamp). Score: 7.0 fixed, applied to the first event after the gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="15" customHeight="1">
+      <c r="A132" s="37" t="inlineStr">
+        <is>
+          <t>**Escalation:** Gap during business hours (07:00–20:00 weekday) with another</t>
         </is>
       </c>
     </row>
     <row r="133" ht="15" customHeight="1">
-      <c r="A133" s="36" t="inlineStr"/>
-    </row>
-    <row r="134" ht="18" customHeight="1">
-      <c r="A134" s="35" t="inlineStr">
-        <is>
-          <t>### Rule 9 — Audit Trail Timestamp Gap [Risk: HIGH]</t>
+      <c r="A133" s="36" t="inlineStr">
+        <is>
+          <t>rule ≥7.0 firing within ±10 rows → escalated to Critical (score 9.0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="15" customHeight="1">
+      <c r="A134" s="36" t="inlineStr">
+        <is>
+          <t>Gap during business hours OR with a nearby rule firing → escalated to High (score 7.0).</t>
         </is>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
       <c r="A135" s="37" t="inlineStr">
         <is>
-          <t>**Trigger:** A gap of more than 2 hours between consecutive audit trail entries</t>
+          <t>**SOP exemption:** Events whose comment cites a procedure reference (SOP/WOI/STP)</t>
         </is>
       </c>
     </row>
     <row r="136" ht="15" customHeight="1">
       <c r="A136" s="36" t="inlineStr">
         <is>
-          <t>(sorted by timestamp). Score: 7.0 fixed, applied to the first event after the gap.</t>
+          <t>are not escalated by this rule — the gap is considered a documented exception.</t>
         </is>
       </c>
     </row>
@@ -56200,325 +56208,345 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" s="36" t="inlineStr"/>
     </row>
-    <row r="204" ht="15" customHeight="1">
-      <c r="A204" s="36" t="inlineStr"/>
+    <row r="204" ht="18" customHeight="1">
+      <c r="A204" s="35" t="inlineStr">
+        <is>
+          <t>### Rule 13 — Dormant Account Sudden Activity [Risk: HIGH]</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="15" customHeight="1">
-      <c r="A205" s="36" t="inlineStr"/>
-    </row>
-    <row r="206" ht="8" customHeight="1">
-      <c r="A206" s="38" t="inlineStr">
-        <is>
-          <t>---</t>
+      <c r="A205" s="37" t="inlineStr">
+        <is>
+          <t>**Target:** All users with at least 4 events in the uploaded audit trail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="15" customHeight="1">
+      <c r="A206" s="37" t="inlineStr">
+        <is>
+          <t>**Trigger:** A user has no activity for 90 or more consecutive days, then</t>
         </is>
       </c>
     </row>
     <row r="207" ht="15" customHeight="1">
-      <c r="A207" s="36" t="inlineStr"/>
-    </row>
-    <row r="208" ht="18" customHeight="1">
-      <c r="A208" s="35" t="inlineStr">
-        <is>
-          <t>### Rule 15 — Suspicious Action Sequence *(Retired — merged into Rule 6)*</t>
+      <c r="A207" s="36" t="inlineStr">
+        <is>
+          <t>performs a data action on a GxP-sensitive record type or performs</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="15" customHeight="1">
+      <c r="A208" s="36" t="inlineStr">
+        <is>
+          <t>update/modify/delete/insert/approve/release on any record. Score: 8.0.</t>
         </is>
       </c>
     </row>
     <row r="209" ht="15" customHeight="1">
-      <c r="A209" s="36" t="inlineStr">
-        <is>
-          <t>UPDATE → DELETE → INSERT three-step sequence detection was merged into Rule 6</t>
+      <c r="A209" s="37" t="inlineStr">
+        <is>
+          <t>**Only the first re-activation event per user is flagged** to avoid filling</t>
         </is>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
       <c r="A210" s="36" t="inlineStr">
         <is>
-          <t>(Record Reconstruction Pattern). Rule 6 now covers both two-step and three-step</t>
+          <t>the top events list with multiple events from the same dormant account.</t>
         </is>
       </c>
     </row>
     <row r="211" ht="15" customHeight="1">
-      <c r="A211" s="36" t="inlineStr">
-        <is>
-          <t>reconstructions. This rule number is retired and will not appear in outputs.</t>
+      <c r="A211" s="37" t="inlineStr">
+        <is>
+          <t>**Regulatory basis:** 21 CFR Part 11 §11.10(d) — access controls; access review</t>
         </is>
       </c>
     </row>
     <row r="212" ht="15" customHeight="1">
-      <c r="A212" s="36" t="inlineStr"/>
-    </row>
-    <row r="213" ht="8" customHeight="1">
-      <c r="A213" s="38" t="inlineStr">
+      <c r="A212" s="36" t="inlineStr">
+        <is>
+          <t>best practice requiring deactivation of accounts inactive for 90+ days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="15" customHeight="1">
+      <c r="A213" s="37" t="inlineStr">
+        <is>
+          <t>**Limitation:** Requires the uploaded audit trail to cover at least 90+ days of</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="15" customHeight="1">
+      <c r="A214" s="36" t="inlineStr">
+        <is>
+          <t>history for reliable detection. Short-period extracts will not trigger this rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="15" customHeight="1">
+      <c r="A215" s="37" t="inlineStr">
+        <is>
+          <t>**Minimum event count:** A user must have at least 3 prior events before the gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="15" customHeight="1">
+      <c r="A216" s="36" t="inlineStr">
+        <is>
+          <t>to be considered an established account (excludes newly created accounts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="15" customHeight="1">
+      <c r="A217" s="36" t="inlineStr"/>
+    </row>
+    <row r="218" ht="8" customHeight="1">
+      <c r="A218" s="38" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="214" ht="15" customHeight="1">
-      <c r="A214" s="36" t="inlineStr"/>
-    </row>
-    <row r="215" ht="18" customHeight="1">
-      <c r="A215" s="35" t="inlineStr">
-        <is>
-          <t>## Event Chain IDs</t>
-        </is>
-      </c>
-    </row>
-    <row r="216" ht="15" customHeight="1">
-      <c r="A216" s="36" t="inlineStr"/>
-    </row>
-    <row r="217" ht="15" customHeight="1">
-      <c r="A217" s="36" t="inlineStr">
-        <is>
-          <t>When multiple events are causally linked, the engine assigns a shared Event Chain</t>
-        </is>
-      </c>
-    </row>
-    <row r="218" ht="15" customHeight="1">
-      <c r="A218" s="36" t="inlineStr">
-        <is>
-          <t>ID (format: EC-001, EC-002 etc.) to all related events. This allows reviewers to</t>
-        </is>
-      </c>
-    </row>
     <row r="219" ht="15" customHeight="1">
-      <c r="A219" s="36" t="inlineStr">
-        <is>
-          <t>filter the Full Audit Log by chain ID and read the complete event story in sequence.</t>
-        </is>
-      </c>
-    </row>
-    <row r="220" ht="15" customHeight="1">
-      <c r="A220" s="36" t="inlineStr"/>
+      <c r="A219" s="36" t="inlineStr"/>
+    </row>
+    <row r="220" ht="18" customHeight="1">
+      <c r="A220" s="35" t="inlineStr">
+        <is>
+          <t>### Rule 14 — First-Time Behavior Detection [Risk: HIGH]</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="15" customHeight="1">
-      <c r="A221" s="36" t="inlineStr">
-        <is>
-          <t>Chains are assigned for:</t>
+      <c r="A221" s="37" t="inlineStr">
+        <is>
+          <t>**Target:** All users with at least 5 prior recorded events in the uploaded file.</t>
         </is>
       </c>
     </row>
     <row r="222" ht="15" customHeight="1">
-      <c r="A222" s="36" t="inlineStr">
-        <is>
-          <t>- **Rule 6** (Delete → Recreate and UPDATE → DELETE → INSERT): all linked events share one chain ID</t>
+      <c r="A222" s="37" t="inlineStr">
+        <is>
+          <t>**Trigger:** A user performs an action_type they have never performed before</t>
         </is>
       </c>
     </row>
     <row r="223" ht="15" customHeight="1">
       <c r="A223" s="36" t="inlineStr">
         <is>
-          <t>- **Rule 5** (Failed Login → Manipulation): all login attempts and the triggering</t>
+          <t>in their recorded audit trail history. Score varies by prior history and action risk:</t>
         </is>
       </c>
     </row>
     <row r="224" ht="15" customHeight="1">
-      <c r="A224" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  data action share one chain ID</t>
-        </is>
-      </c>
+      <c r="A224" s="36" t="inlineStr"/>
     </row>
     <row r="225" ht="15" customHeight="1">
-      <c r="A225" s="36" t="inlineStr"/>
+      <c r="A225" s="37" t="inlineStr">
+        <is>
+          <t>| Prior events | Action type | Score |</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="15" customHeight="1">
       <c r="A226" s="36" t="inlineStr">
         <is>
-          <t>The Event_Chain_ID column appears in both the Events for Review sheet and the</t>
+          <t>|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="227" ht="15" customHeight="1">
-      <c r="A227" s="36" t="inlineStr">
-        <is>
-          <t>Full Audit Log sheet in the Excel output.</t>
+      <c r="A227" s="37" t="inlineStr">
+        <is>
+          <t>| ≥50 | First-time DELETE/APPROVE on GxP table | 9.0 |</t>
         </is>
       </c>
     </row>
     <row r="228" ht="15" customHeight="1">
-      <c r="A228" s="36" t="inlineStr"/>
+      <c r="A228" s="37" t="inlineStr">
+        <is>
+          <t>| ≥20 | First-time DELETE/APPROVE on any table | 8.0 |</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="15" customHeight="1">
-      <c r="A229" s="36" t="inlineStr"/>
-    </row>
-    <row r="230" ht="8" customHeight="1">
-      <c r="A230" s="38" t="inlineStr">
-        <is>
-          <t>---</t>
+      <c r="A229" s="37" t="inlineStr">
+        <is>
+          <t>| ≥20 | First-time any action | 6.0 |</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="15" customHeight="1">
+      <c r="A230" s="37" t="inlineStr">
+        <is>
+          <t>| ≥5  | First-time high-risk action | 5.0 |</t>
         </is>
       </c>
     </row>
     <row r="231" ht="15" customHeight="1">
-      <c r="A231" s="36" t="inlineStr"/>
-    </row>
-    <row r="232" ht="18" customHeight="1">
-      <c r="A232" s="35" t="inlineStr">
-        <is>
-          <t>### Rule 14 — First-Time Behavior Detection [Risk: HIGH]</t>
-        </is>
-      </c>
+      <c r="A231" s="37" t="inlineStr">
+        <is>
+          <t>| &lt;5  | (not enough history — skipped) | 0.0 |</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="15" customHeight="1">
+      <c r="A232" s="36" t="inlineStr"/>
     </row>
     <row r="233" ht="15" customHeight="1">
       <c r="A233" s="37" t="inlineStr">
         <is>
-          <t>**Target:** All users with at least 5 prior recorded events in the uploaded file.</t>
+          <t>**High-risk action types detected:** delete, del, remove, purge, void, cancel,</t>
         </is>
       </c>
     </row>
     <row r="234" ht="15" customHeight="1">
-      <c r="A234" s="37" t="inlineStr">
-        <is>
-          <t>**Trigger:** A user performs an action_type they have never performed before</t>
+      <c r="A234" s="36" t="inlineStr">
+        <is>
+          <t>approve, release, authorise, authorize, sign, override, batch_release, approve_result.</t>
         </is>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1">
-      <c r="A235" s="36" t="inlineStr">
-        <is>
-          <t>in their recorded audit trail history. Score varies by prior history and action risk:</t>
+      <c r="A235" s="37" t="inlineStr">
+        <is>
+          <t>**Regulatory basis:** 21 CFR Part 11 §11.10(d) access controls; ALCOA+ Attributable.</t>
         </is>
       </c>
     </row>
     <row r="236" ht="15" customHeight="1">
-      <c r="A236" s="36" t="inlineStr"/>
+      <c r="A236" s="37" t="inlineStr">
+        <is>
+          <t>**Why this matters:** An established user who suddenly performs an action they</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="15" customHeight="1">
-      <c r="A237" s="37" t="inlineStr">
-        <is>
-          <t>| Prior events | Action type | Score |</t>
+      <c r="A237" s="36" t="inlineStr">
+        <is>
+          <t>have never done before — especially a high-risk action like delete or approve —</t>
         </is>
       </c>
     </row>
     <row r="238" ht="15" customHeight="1">
       <c r="A238" s="36" t="inlineStr">
         <is>
-          <t>|---|---|---|</t>
+          <t>is a meaningful insider risk signal. This pattern may indicate:</t>
         </is>
       </c>
     </row>
     <row r="239" ht="15" customHeight="1">
-      <c r="A239" s="37" t="inlineStr">
-        <is>
-          <t>| ≥50 | First-time DELETE/APPROVE on GxP table | 9.0 |</t>
+      <c r="A239" s="36" t="inlineStr">
+        <is>
+          <t>- Unauthorised escalation of access or responsibilities</t>
         </is>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
-      <c r="A240" s="37" t="inlineStr">
-        <is>
-          <t>| ≥20 | First-time DELETE/APPROVE on any table | 8.0 |</t>
+      <c r="A240" s="36" t="inlineStr">
+        <is>
+          <t>- Credential sharing (someone else used the account)</t>
         </is>
       </c>
     </row>
     <row r="241" ht="15" customHeight="1">
-      <c r="A241" s="37" t="inlineStr">
-        <is>
-          <t>| ≥20 | First-time any action | 6.0 |</t>
+      <c r="A241" s="36" t="inlineStr">
+        <is>
+          <t>- A data integrity incident being covered up</t>
         </is>
       </c>
     </row>
     <row r="242" ht="15" customHeight="1">
-      <c r="A242" s="37" t="inlineStr">
-        <is>
-          <t>| ≥5  | First-time high-risk action | 5.0 |</t>
-        </is>
-      </c>
+      <c r="A242" s="36" t="inlineStr"/>
     </row>
     <row r="243" ht="15" customHeight="1">
       <c r="A243" s="37" t="inlineStr">
         <is>
-          <t>| &lt;5  | (not enough history — skipped) | 0.0 |</t>
+          <t>**Confidence labelling:** The rationale always states the number of prior events</t>
         </is>
       </c>
     </row>
     <row r="244" ht="15" customHeight="1">
-      <c r="A244" s="36" t="inlineStr"/>
+      <c r="A244" s="36" t="inlineStr">
+        <is>
+          <t>observed, so the reviewer can judge statistical significance. A user with 200 prior</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="15" customHeight="1">
-      <c r="A245" s="37" t="inlineStr">
-        <is>
-          <t>**High-risk action types detected:** delete, del, remove, purge, void, cancel,</t>
+      <c r="A245" s="36" t="inlineStr">
+        <is>
+          <t>events performing their first-ever delete is far more anomalous than a user with 6.</t>
         </is>
       </c>
     </row>
     <row r="246" ht="15" customHeight="1">
-      <c r="A246" s="36" t="inlineStr">
-        <is>
-          <t>approve, release, authorise, authorize, sign, override, batch_release, approve_result.</t>
-        </is>
-      </c>
+      <c r="A246" s="36" t="inlineStr"/>
     </row>
     <row r="247" ht="15" customHeight="1">
       <c r="A247" s="37" t="inlineStr">
         <is>
-          <t>**Regulatory basis:** 21 CFR Part 11 §11.10(d) access controls; ALCOA+ Attributable.</t>
+          <t>**Important limitation:** This rule requires sufficient history in the uploaded file.</t>
         </is>
       </c>
     </row>
     <row r="248" ht="15" customHeight="1">
-      <c r="A248" s="37" t="inlineStr">
-        <is>
-          <t>**Why this matters:** An established user who suddenly performs an action they</t>
+      <c r="A248" s="36" t="inlineStr">
+        <is>
+          <t>Short-period exports (under 30 days) will produce many "first-time" flags that</t>
         </is>
       </c>
     </row>
     <row r="249" ht="15" customHeight="1">
       <c r="A249" s="36" t="inlineStr">
         <is>
-          <t>have never done before — especially a high-risk action like delete or approve —</t>
+          <t>are simply normal activity not captured in the window. For reliable detection,</t>
         </is>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
       <c r="A250" s="36" t="inlineStr">
         <is>
-          <t>is a meaningful insider risk signal. This pattern may indicate:</t>
+          <t>upload audit trails covering at least 3 months.</t>
         </is>
       </c>
     </row>
     <row r="251" ht="15" customHeight="1">
-      <c r="A251" s="36" t="inlineStr">
-        <is>
-          <t>- Unauthorised escalation of access or responsibilities</t>
-        </is>
-      </c>
+      <c r="A251" s="36" t="inlineStr"/>
     </row>
     <row r="252" ht="15" customHeight="1">
-      <c r="A252" s="36" t="inlineStr">
-        <is>
-          <t>- Credential sharing (someone else used the account)</t>
+      <c r="A252" s="37" t="inlineStr">
+        <is>
+          <t>**Minimum prior events:** 5. Users with fewer than 5 recorded events are skipped</t>
         </is>
       </c>
     </row>
     <row r="253" ht="15" customHeight="1">
       <c r="A253" s="36" t="inlineStr">
         <is>
-          <t>- A data integrity incident being covered up</t>
+          <t>to exclude newly created accounts where any action is technically a "first time."</t>
         </is>
       </c>
     </row>
     <row r="254" ht="15" customHeight="1">
       <c r="A254" s="36" t="inlineStr"/>
     </row>
-    <row r="255" ht="15" customHeight="1">
-      <c r="A255" s="37" t="inlineStr">
-        <is>
-          <t>**Confidence labelling:** The rationale always states the number of prior events</t>
+    <row r="255" ht="8" customHeight="1">
+      <c r="A255" s="38" t="inlineStr">
+        <is>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="256" ht="15" customHeight="1">
-      <c r="A256" s="36" t="inlineStr">
-        <is>
-          <t>observed, so the reviewer can judge statistical significance. A user with 200 prior</t>
-        </is>
-      </c>
-    </row>
-    <row r="257" ht="15" customHeight="1">
-      <c r="A257" s="36" t="inlineStr">
-        <is>
-          <t>events performing their first-ever delete is far more anomalous than a user with 6.</t>
+      <c r="A256" s="36" t="inlineStr"/>
+    </row>
+    <row r="257" ht="18" customHeight="1">
+      <c r="A257" s="35" t="inlineStr">
+        <is>
+          <t>## Retired Rules</t>
         </is>
       </c>
     </row>
@@ -56526,161 +56554,153 @@
       <c r="A258" s="36" t="inlineStr"/>
     </row>
     <row r="259" ht="15" customHeight="1">
-      <c r="A259" s="37" t="inlineStr">
-        <is>
-          <t>**Important limitation:** This rule requires sufficient history in the uploaded file.</t>
+      <c r="A259" s="36" t="inlineStr">
+        <is>
+          <t>The following rule numbers have been retired or merged. They will not appear in</t>
         </is>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
       <c r="A260" s="36" t="inlineStr">
         <is>
-          <t>Short-period exports (under 30 days) will produce many "first-time" flags that</t>
+          <t>any output column. They are documented here for traceability and CSV purposes.</t>
         </is>
       </c>
     </row>
     <row r="261" ht="15" customHeight="1">
-      <c r="A261" s="36" t="inlineStr">
-        <is>
-          <t>are simply normal activity not captured in the window. For reliable detection,</t>
-        </is>
-      </c>
+      <c r="A261" s="36" t="inlineStr"/>
     </row>
     <row r="262" ht="15" customHeight="1">
-      <c r="A262" s="36" t="inlineStr">
-        <is>
-          <t>upload audit trails covering at least 3 months.</t>
+      <c r="A262" s="37" t="inlineStr">
+        <is>
+          <t>**Rule 9 (retired) — High-Volume Activity Burst:** Velocity-based scoring for</t>
         </is>
       </c>
     </row>
     <row r="263" ht="15" customHeight="1">
-      <c r="A263" s="36" t="inlineStr"/>
+      <c r="A263" s="36" t="inlineStr">
+        <is>
+          <t>5+ same-action events within 60 minutes. Retired and superseded by Rule 2</t>
+        </is>
+      </c>
     </row>
     <row r="264" ht="15" customHeight="1">
-      <c r="A264" s="37" t="inlineStr">
-        <is>
-          <t>**Minimum prior events:** 5. Users with fewer than 5 recorded events are skipped</t>
+      <c r="A264" s="36" t="inlineStr">
+        <is>
+          <t>(Contemporaneous Burst), which provides tighter targeting with INSERT-specific</t>
         </is>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
       <c r="A265" s="36" t="inlineStr">
         <is>
-          <t>to exclude newly created accounts where any action is technically a "first time."</t>
+          <t>logic and a stricter 15-minute window. Not implemented in the current engine.</t>
         </is>
       </c>
     </row>
     <row r="266" ht="15" customHeight="1">
       <c r="A266" s="36" t="inlineStr"/>
     </row>
-    <row r="267" ht="18" customHeight="1">
-      <c r="A267" s="35" t="inlineStr">
-        <is>
-          <t>### Rule 13 — Dormant Account Sudden Activity [Risk: HIGH]</t>
+    <row r="267" ht="15" customHeight="1">
+      <c r="A267" s="37" t="inlineStr">
+        <is>
+          <t>**Rule 15 (retired) — Suspicious Action Sequence (UPDATE → DELETE → INSERT):**</t>
         </is>
       </c>
     </row>
     <row r="268" ht="15" customHeight="1">
-      <c r="A268" s="37" t="inlineStr">
-        <is>
-          <t>**Target:** All users with at least 4 events in the uploaded audit trail.</t>
+      <c r="A268" s="36" t="inlineStr">
+        <is>
+          <t>Three-step record reconstruction detection merged into Rule 6 (Delete and Recreate</t>
         </is>
       </c>
     </row>
     <row r="269" ht="15" customHeight="1">
-      <c r="A269" s="37" t="inlineStr">
-        <is>
-          <t>**Trigger:** A user has no activity for 90 or more consecutive days, then</t>
+      <c r="A269" s="36" t="inlineStr">
+        <is>
+          <t>Pattern), which now covers both two-step and three-step sequences. Not scored</t>
         </is>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
       <c r="A270" s="36" t="inlineStr">
         <is>
-          <t>performs a data action on a GxP-sensitive record type or performs</t>
+          <t>separately; Rule 6 handles all reconstruction patterns.</t>
         </is>
       </c>
     </row>
     <row r="271" ht="15" customHeight="1">
-      <c r="A271" s="36" t="inlineStr">
-        <is>
-          <t>update/modify/delete/insert/approve/release on any record. Score: 8.0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="272" ht="15" customHeight="1">
-      <c r="A272" s="37" t="inlineStr">
-        <is>
-          <t>**Only the first re-activation event per user is flagged** to avoid filling</t>
+      <c r="A271" s="36" t="inlineStr"/>
+    </row>
+    <row r="272" ht="8" customHeight="1">
+      <c r="A272" s="38" t="inlineStr">
+        <is>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="273" ht="15" customHeight="1">
-      <c r="A273" s="36" t="inlineStr">
-        <is>
-          <t>the Top 20 with multiple events from the same dormant account.</t>
-        </is>
-      </c>
-    </row>
-    <row r="274" ht="15" customHeight="1">
-      <c r="A274" s="37" t="inlineStr">
-        <is>
-          <t>**Regulatory basis:** 21 CFR Part 11 §11.10(d) — access controls; access review</t>
+      <c r="A273" s="36" t="inlineStr"/>
+    </row>
+    <row r="274" ht="18" customHeight="1">
+      <c r="A274" s="35" t="inlineStr">
+        <is>
+          <t>## Event Chain IDs</t>
         </is>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
-      <c r="A275" s="36" t="inlineStr">
-        <is>
-          <t>best practice requiring deactivation of accounts inactive for 90+ days.</t>
-        </is>
-      </c>
+      <c r="A275" s="36" t="inlineStr"/>
     </row>
     <row r="276" ht="15" customHeight="1">
-      <c r="A276" s="37" t="inlineStr">
-        <is>
-          <t>**Limitation:** Requires the uploaded audit trail to cover at least 90+ days of</t>
+      <c r="A276" s="36" t="inlineStr">
+        <is>
+          <t>When multiple events are causally linked, the engine assigns a shared Event Chain</t>
         </is>
       </c>
     </row>
     <row r="277" ht="15" customHeight="1">
       <c r="A277" s="36" t="inlineStr">
         <is>
-          <t>history for reliable detection. Short-period extracts will not trigger this rule.</t>
+          <t>ID (format: EC-001, EC-002 etc.) to all related events. This allows reviewers to</t>
         </is>
       </c>
     </row>
     <row r="278" ht="15" customHeight="1">
-      <c r="A278" s="37" t="inlineStr">
-        <is>
-          <t>**Minimum event count:** A user must have at least 3 prior events before the gap</t>
+      <c r="A278" s="36" t="inlineStr">
+        <is>
+          <t>filter the Full Audit Log by chain ID and read the complete event story in sequence.</t>
         </is>
       </c>
     </row>
     <row r="279" ht="15" customHeight="1">
-      <c r="A279" s="36" t="inlineStr">
-        <is>
-          <t>to be considered an established account (excludes newly created accounts).</t>
-        </is>
-      </c>
+      <c r="A279" s="36" t="inlineStr"/>
     </row>
     <row r="280" ht="15" customHeight="1">
-      <c r="A280" s="36" t="inlineStr"/>
-    </row>
-    <row r="281" ht="8" customHeight="1">
-      <c r="A281" s="38" t="inlineStr">
-        <is>
-          <t>---</t>
+      <c r="A280" s="36" t="inlineStr">
+        <is>
+          <t>Chains are assigned for:</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="15" customHeight="1">
+      <c r="A281" s="36" t="inlineStr">
+        <is>
+          <t>- **Rule 6** (Delete → Recreate): both the delete and recreate events share one chain ID</t>
         </is>
       </c>
     </row>
     <row r="282" ht="15" customHeight="1">
-      <c r="A282" s="36" t="inlineStr"/>
-    </row>
-    <row r="283" ht="18" customHeight="1">
-      <c r="A283" s="35" t="inlineStr">
-        <is>
-          <t>## Composite Scoring</t>
+      <c r="A282" s="36" t="inlineStr">
+        <is>
+          <t>- **Rule 5** (Failed Login → Manipulation): all login attempts and the triggering</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="15" customHeight="1">
+      <c r="A283" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  data action share one chain ID</t>
         </is>
       </c>
     </row>
@@ -56690,129 +56710,109 @@
     <row r="285" ht="15" customHeight="1">
       <c r="A285" s="36" t="inlineStr">
         <is>
-          <t>Each event receives scores across all 14 active rules. A weighted composite (0–10):</t>
+          <t>The Event_Chain_ID column appears in both the Events for Review sheet and the</t>
         </is>
       </c>
     </row>
     <row r="286" ht="15" customHeight="1">
-      <c r="A286" s="36" t="inlineStr"/>
+      <c r="A286" s="36" t="inlineStr">
+        <is>
+          <t>Full Audit Log sheet in the Excel output.</t>
+        </is>
+      </c>
     </row>
     <row r="287" ht="15" customHeight="1">
-      <c r="A287" s="37" t="inlineStr">
-        <is>
-          <t>| Rule | Dimension / Name | Weight |</t>
-        </is>
-      </c>
-    </row>
-    <row r="288" ht="15" customHeight="1">
-      <c r="A288" s="36" t="inlineStr">
-        <is>
-          <t>|------|-----------------|--------|</t>
+      <c r="A287" s="36" t="inlineStr"/>
+    </row>
+    <row r="288" ht="8" customHeight="1">
+      <c r="A288" s="38" t="inlineStr">
+        <is>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="289" ht="15" customHeight="1">
-      <c r="A289" s="37" t="inlineStr">
-        <is>
-          <t>| 1  | Vague Rationale | 7% |</t>
-        </is>
-      </c>
-    </row>
-    <row r="290" ht="15" customHeight="1">
-      <c r="A290" s="37" t="inlineStr">
-        <is>
-          <t>| 2  | Contemporaneous Burst | 7% |</t>
+      <c r="A289" s="36" t="inlineStr"/>
+    </row>
+    <row r="290" ht="18" customHeight="1">
+      <c r="A290" s="35" t="inlineStr">
+        <is>
+          <t>## Out-of-Period Events</t>
         </is>
       </c>
     </row>
     <row r="291" ht="15" customHeight="1">
-      <c r="A291" s="37" t="inlineStr">
-        <is>
-          <t>| 3  | Admin/GxP Conflict | 10% |</t>
-        </is>
-      </c>
+      <c r="A291" s="36" t="inlineStr"/>
     </row>
     <row r="292" ht="15" customHeight="1">
-      <c r="A292" s="37" t="inlineStr">
-        <is>
-          <t>| 4  | Change Control Drift | 6% |</t>
+      <c r="A292" s="36" t="inlineStr">
+        <is>
+          <t>When a Review Period (Start Date → End Date) is specified, events whose timestamp</t>
         </is>
       </c>
     </row>
     <row r="293" ht="15" customHeight="1">
-      <c r="A293" s="37" t="inlineStr">
-        <is>
-          <t>| 5  | Failed Login → Data Manipulation | 8% |</t>
+      <c r="A293" s="36" t="inlineStr">
+        <is>
+          <t>falls outside that window are tagged as **Out of Period** and excluded from all</t>
         </is>
       </c>
     </row>
     <row r="294" ht="15" customHeight="1">
-      <c r="A294" s="37" t="inlineStr">
-        <is>
-          <t>| 6  | Record Reconstruction (Delete-Recreate) | 10% |</t>
+      <c r="A294" s="36" t="inlineStr">
+        <is>
+          <t>risk scoring. They appear in the Full Audit Log with Risk Level = "Out of Period"</t>
         </is>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
-      <c r="A295" s="37" t="inlineStr">
-        <is>
-          <t>| 7  | Audit Trail Integrity / Record Sensitivity | 8% |</t>
+      <c r="A295" s="36" t="inlineStr">
+        <is>
+          <t>and are not included in the Events for Review sheet. The Summary sheet Scope Note</t>
         </is>
       </c>
     </row>
     <row r="296" ht="15" customHeight="1">
-      <c r="A296" s="37" t="inlineStr">
-        <is>
-          <t>| 8  | Privileged User on GxP Data | 9% |</t>
+      <c r="A296" s="36" t="inlineStr">
+        <is>
+          <t>reports the count of out-of-period events detected.</t>
         </is>
       </c>
     </row>
     <row r="297" ht="15" customHeight="1">
-      <c r="A297" s="37" t="inlineStr">
-        <is>
-          <t>| 9  | Timestamp Gap | 6% |</t>
-        </is>
-      </c>
+      <c r="A297" s="36" t="inlineStr"/>
     </row>
     <row r="298" ht="15" customHeight="1">
-      <c r="A298" s="37" t="inlineStr">
-        <is>
-          <t>| 10 | Off-Hours / Holiday Activity | 6% |</t>
+      <c r="A298" s="36" t="inlineStr">
+        <is>
+          <t>This ensures risk tier counts, escalation rates, and the Events for Review list</t>
         </is>
       </c>
     </row>
     <row r="299" ht="15" customHeight="1">
-      <c r="A299" s="37" t="inlineStr">
-        <is>
-          <t>| 11 | Timestamp Reversal | 9% |</t>
+      <c r="A299" s="36" t="inlineStr">
+        <is>
+          <t>reflect only the declared review scope.</t>
         </is>
       </c>
     </row>
     <row r="300" ht="15" customHeight="1">
-      <c r="A300" s="37" t="inlineStr">
-        <is>
-          <t>| 12 | Service / Shared Account GxP Action | 9% |</t>
-        </is>
-      </c>
-    </row>
-    <row r="301" ht="15" customHeight="1">
-      <c r="A301" s="37" t="inlineStr">
-        <is>
-          <t>| 13 | Dormant Account Sudden Activity | 7% |</t>
+      <c r="A300" s="36" t="inlineStr"/>
+    </row>
+    <row r="301" ht="8" customHeight="1">
+      <c r="A301" s="38" t="inlineStr">
+        <is>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="302" ht="15" customHeight="1">
-      <c r="A302" s="37" t="inlineStr">
-        <is>
-          <t>| 14 | First-Time Behavior Detection | 7% |</t>
-        </is>
-      </c>
-    </row>
-    <row r="303" ht="15" customHeight="1">
-      <c r="A303" s="37" t="inlineStr">
-        <is>
-          <t>| | **Total** | **109%** |</t>
+      <c r="A302" s="36" t="inlineStr"/>
+    </row>
+    <row r="303" ht="18" customHeight="1">
+      <c r="A303" s="35" t="inlineStr">
+        <is>
+          <t>## Composite Scoring</t>
         </is>
       </c>
     </row>
@@ -56822,7 +56822,7 @@
     <row r="305" ht="15" customHeight="1">
       <c r="A305" s="36" t="inlineStr">
         <is>
-          <t>*Note: Weights are normalised internally — the sum does not need to equal 100%.*</t>
+          <t>Each event receives scores across all 14 active rules. A weighted composite (0–10):</t>
         </is>
       </c>
     </row>
@@ -56832,746 +56832,746 @@
     <row r="307" ht="15" customHeight="1">
       <c r="A307" s="37" t="inlineStr">
         <is>
-          <t>**Named rule tier overrides:** Rules 3, 5, 11, and 12 at score ≥9 always produce</t>
+          <t>| Rule | Dimension / Name | Weight |</t>
         </is>
       </c>
     </row>
     <row r="308" ht="15" customHeight="1">
       <c r="A308" s="36" t="inlineStr">
         <is>
-          <t>a Critical tier, regardless of composite score. Rule 6 at ≥9 and Rule 7 at 10.0</t>
+          <t>|------|-----------------|--------|</t>
         </is>
       </c>
     </row>
     <row r="309" ht="15" customHeight="1">
-      <c r="A309" s="36" t="inlineStr">
-        <is>
-          <t>also produce Critical. This ensures named Critical violations are never</t>
+      <c r="A309" s="37" t="inlineStr">
+        <is>
+          <t>| 1  | Vague Rationale | 7% |</t>
         </is>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
-      <c r="A310" s="36" t="inlineStr">
-        <is>
-          <t>downgraded by a low composite score.</t>
+      <c r="A310" s="37" t="inlineStr">
+        <is>
+          <t>| 2  | Contemporaneous Burst | 7% |</t>
         </is>
       </c>
     </row>
     <row r="311" ht="15" customHeight="1">
-      <c r="A311" s="36" t="inlineStr"/>
-    </row>
-    <row r="312" ht="8" customHeight="1">
-      <c r="A312" s="38" t="inlineStr">
-        <is>
-          <t>---</t>
+      <c r="A311" s="37" t="inlineStr">
+        <is>
+          <t>| 3  | Admin/GxP Conflict | 10% |</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="15" customHeight="1">
+      <c r="A312" s="37" t="inlineStr">
+        <is>
+          <t>| 4  | Change Control Drift | 6% |</t>
         </is>
       </c>
     </row>
     <row r="313" ht="15" customHeight="1">
-      <c r="A313" s="36" t="inlineStr"/>
-    </row>
-    <row r="314" ht="18" customHeight="1">
-      <c r="A314" s="35" t="inlineStr">
-        <is>
-          <t>## Suggested Disposition Logic</t>
+      <c r="A313" s="37" t="inlineStr">
+        <is>
+          <t>| 5  | Failed Login → Data Manipulation | 8% |</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="15" customHeight="1">
+      <c r="A314" s="37" t="inlineStr">
+        <is>
+          <t>| 6  | Record Reconstruction (Delete-Recreate) | 10% |</t>
         </is>
       </c>
     </row>
     <row r="315" ht="15" customHeight="1">
-      <c r="A315" s="36" t="inlineStr"/>
+      <c r="A315" s="37" t="inlineStr">
+        <is>
+          <t>| 7  | Audit Trail Integrity / Record Sensitivity | 8% |</t>
+        </is>
+      </c>
     </row>
     <row r="316" ht="15" customHeight="1">
       <c r="A316" s="37" t="inlineStr">
         <is>
-          <t>| Condition | Suggested Disposition |</t>
+          <t>| 8  | Privileged User on GxP Data | 9% |</t>
         </is>
       </c>
     </row>
     <row r="317" ht="15" customHeight="1">
-      <c r="A317" s="36" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
+      <c r="A317" s="37" t="inlineStr">
+        <is>
+          <t>| 9  | Timestamp Gap | 6% |</t>
         </is>
       </c>
     </row>
     <row r="318" ht="15" customHeight="1">
       <c r="A318" s="37" t="inlineStr">
         <is>
-          <t>| Rule 11 fired | Escalate to CAPA |</t>
+          <t>| 10 | Off-Hours / Holiday Activity | 6% |</t>
         </is>
       </c>
     </row>
     <row r="319" ht="15" customHeight="1">
       <c r="A319" s="37" t="inlineStr">
         <is>
-          <t>| Rule 12 fired (Critical) | Escalate to CAPA |</t>
+          <t>| 11 | Timestamp Reversal | 9% |</t>
         </is>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1">
       <c r="A320" s="37" t="inlineStr">
         <is>
-          <t>| Rule 5 fired | Escalate to CAPA |</t>
+          <t>| 12 | Service / Shared Account GxP Action | 9% |</t>
         </is>
       </c>
     </row>
     <row r="321" ht="15" customHeight="1">
       <c r="A321" s="37" t="inlineStr">
         <is>
-          <t>| Rule 3 fired | Escalate to CAPA |</t>
+          <t>| 13 | Dormant Account Sudden Activity | 7% |</t>
         </is>
       </c>
     </row>
     <row r="322" ht="15" customHeight="1">
       <c r="A322" s="37" t="inlineStr">
         <is>
-          <t>| Rule 6 fired | Escalate to CAPA |</t>
+          <t>| 14 | First-Time Behavior Detection | 7% |</t>
         </is>
       </c>
     </row>
     <row r="323" ht="15" customHeight="1">
       <c r="A323" s="37" t="inlineStr">
         <is>
-          <t>| Rule 7 (audit ctrl) fired | Escalate to CAPA |</t>
+          <t>| | **Total** | **109%** |</t>
         </is>
       </c>
     </row>
     <row r="324" ht="15" customHeight="1">
-      <c r="A324" s="37" t="inlineStr">
-        <is>
-          <t>| Rule 9 (gap) during business hours | Escalate to CAPA |</t>
-        </is>
-      </c>
+      <c r="A324" s="36" t="inlineStr"/>
     </row>
     <row r="325" ht="15" customHeight="1">
-      <c r="A325" s="37" t="inlineStr">
-        <is>
-          <t>| Rule 9 (gap) outside business hours | Investigate — Verify Source Data |</t>
+      <c r="A325" s="36" t="inlineStr">
+        <is>
+          <t>*Note: Weights are normalised internally — the sum does not need to equal 100%.*</t>
         </is>
       </c>
     </row>
     <row r="326" ht="15" customHeight="1">
-      <c r="A326" s="37" t="inlineStr">
-        <is>
-          <t>| Rule 4 fired | Escalate to CAPA |</t>
-        </is>
-      </c>
+      <c r="A326" s="36" t="inlineStr"/>
     </row>
     <row r="327" ht="15" customHeight="1">
       <c r="A327" s="37" t="inlineStr">
         <is>
+          <t>**Named rule tier overrides:** Rules 3, 5, 11, and 12 at score ≥9 always produce</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="15" customHeight="1">
+      <c r="A328" s="36" t="inlineStr">
+        <is>
+          <t>a Critical tier, regardless of composite score. Rule 6 at ≥9 and Rule 7 at 10.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="15" customHeight="1">
+      <c r="A329" s="36" t="inlineStr">
+        <is>
+          <t>also produce Critical. This ensures named Critical violations are never</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="15" customHeight="1">
+      <c r="A330" s="36" t="inlineStr">
+        <is>
+          <t>downgraded by a low composite score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="15" customHeight="1">
+      <c r="A331" s="36" t="inlineStr"/>
+    </row>
+    <row r="332" ht="8" customHeight="1">
+      <c r="A332" s="38" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="15" customHeight="1">
+      <c r="A333" s="36" t="inlineStr"/>
+    </row>
+    <row r="334" ht="18" customHeight="1">
+      <c r="A334" s="35" t="inlineStr">
+        <is>
+          <t>## Suggested Disposition Logic</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="15" customHeight="1">
+      <c r="A335" s="36" t="inlineStr"/>
+    </row>
+    <row r="336" ht="15" customHeight="1">
+      <c r="A336" s="37" t="inlineStr">
+        <is>
+          <t>| Condition | Suggested Disposition |</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="15" customHeight="1">
+      <c r="A337" s="36" t="inlineStr">
+        <is>
+          <t>|---|---|</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="15" customHeight="1">
+      <c r="A338" s="37" t="inlineStr">
+        <is>
+          <t>| Rule 11 fired | Escalate to CAPA |</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="15" customHeight="1">
+      <c r="A339" s="37" t="inlineStr">
+        <is>
+          <t>| Rule 12 fired (Critical) | Escalate to CAPA |</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="15" customHeight="1">
+      <c r="A340" s="37" t="inlineStr">
+        <is>
+          <t>| Rule 5 fired | Escalate to CAPA |</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="15" customHeight="1">
+      <c r="A341" s="37" t="inlineStr">
+        <is>
+          <t>| Rule 3 fired | Escalate to CAPA |</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="15" customHeight="1">
+      <c r="A342" s="37" t="inlineStr">
+        <is>
+          <t>| Rule 6 fired | Escalate to CAPA |</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="15" customHeight="1">
+      <c r="A343" s="37" t="inlineStr">
+        <is>
+          <t>| Rule 7 (audit ctrl) fired | Escalate to CAPA |</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="15" customHeight="1">
+      <c r="A344" s="37" t="inlineStr">
+        <is>
+          <t>| Rule 9 (gap) during business hours | Escalate to CAPA |</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="15" customHeight="1">
+      <c r="A345" s="37" t="inlineStr">
+        <is>
+          <t>| Rule 9 (gap) outside business hours | Investigate — Verify Source Data |</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="15" customHeight="1">
+      <c r="A346" s="37" t="inlineStr">
+        <is>
+          <t>| Rule 4 fired | Escalate to CAPA |</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="15" customHeight="1">
+      <c r="A347" s="37" t="inlineStr">
+        <is>
           <t>| Rule 1 — blank comment | Escalate to CAPA |</t>
         </is>
       </c>
     </row>
-    <row r="328" ht="15" customHeight="1">
-      <c r="A328" s="37" t="inlineStr">
+    <row r="348" ht="15" customHeight="1">
+      <c r="A348" s="37" t="inlineStr">
         <is>
           <t>| Rule 1 — vague term | Justified — Amendment Required |</t>
         </is>
       </c>
     </row>
-    <row r="329" ht="15" customHeight="1">
-      <c r="A329" s="37" t="inlineStr">
+    <row r="349" ht="15" customHeight="1">
+      <c r="A349" s="37" t="inlineStr">
         <is>
           <t>| Rule 13 fired | Investigate — Verify Source Data |</t>
         </is>
       </c>
     </row>
-    <row r="330" ht="15" customHeight="1">
-      <c r="A330" s="37" t="inlineStr">
+    <row r="350" ht="15" customHeight="1">
+      <c r="A350" s="37" t="inlineStr">
+        <is>
+          <t>| Rule 14 fired | Investigate — Verify Source Data |</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" ht="15" customHeight="1">
+      <c r="A351" s="37" t="inlineStr">
         <is>
           <t>| Rule 2 burst | Investigate — Verify Source Data |</t>
         </is>
       </c>
     </row>
-    <row r="331" ht="15" customHeight="1">
-      <c r="A331" s="37" t="inlineStr">
+    <row r="352" ht="15" customHeight="1">
+      <c r="A352" s="37" t="inlineStr">
         <is>
           <t>| Off-hours with comment | Justified — Document Rationale |</t>
         </is>
       </c>
     </row>
-    <row r="332" ht="15" customHeight="1">
-      <c r="A332" s="37" t="inlineStr">
+    <row r="353" ht="15" customHeight="1">
+      <c r="A353" s="37" t="inlineStr">
         <is>
           <t>| Off-hours, no comment | Escalate to CAPA |</t>
         </is>
       </c>
     </row>
-    <row r="333" ht="15" customHeight="1">
-      <c r="A333" s="37" t="inlineStr">
+    <row r="354" ht="15" customHeight="1">
+      <c r="A354" s="37" t="inlineStr">
         <is>
           <t>| No rule triggered significantly | Justified — No Action Required |</t>
         </is>
       </c>
     </row>
-    <row r="334" ht="15" customHeight="1">
-      <c r="A334" s="36" t="inlineStr"/>
-    </row>
-    <row r="335" ht="8" customHeight="1">
-      <c r="A335" s="38" t="inlineStr">
+    <row r="355" ht="15" customHeight="1">
+      <c r="A355" s="36" t="inlineStr"/>
+    </row>
+    <row r="356" ht="8" customHeight="1">
+      <c r="A356" s="38" t="inlineStr">
         <is>
           <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="336" ht="15" customHeight="1">
-      <c r="A336" s="36" t="inlineStr"/>
-    </row>
-    <row r="337" ht="18" customHeight="1">
-      <c r="A337" s="35" t="inlineStr">
-        <is>
-          <t>## Review Narrative (Summary Sheet)</t>
-        </is>
-      </c>
-    </row>
-    <row r="338" ht="15" customHeight="1">
-      <c r="A338" s="36" t="inlineStr"/>
-    </row>
-    <row r="339" ht="15" customHeight="1">
-      <c r="A339" s="36" t="inlineStr">
-        <is>
-          <t>Following the detection analysis, the Summary sheet includes a **Review Narrative**</t>
-        </is>
-      </c>
-    </row>
-    <row r="340" ht="15" customHeight="1">
-      <c r="A340" s="36" t="inlineStr">
-        <is>
-          <t>section — a plain-English paragraph summarising the key findings of the review.</t>
-        </is>
-      </c>
-    </row>
-    <row r="341" ht="15" customHeight="1">
-      <c r="A341" s="36" t="inlineStr">
-        <is>
-          <t>This section is generated deterministically from the scored data with no LLM</t>
-        </is>
-      </c>
-    </row>
-    <row r="342" ht="15" customHeight="1">
-      <c r="A342" s="36" t="inlineStr">
-        <is>
-          <t>involvement, making it fully reproducible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="343" ht="15" customHeight="1">
-      <c r="A343" s="36" t="inlineStr"/>
-    </row>
-    <row r="344" ht="15" customHeight="1">
-      <c r="A344" s="36" t="inlineStr">
-        <is>
-          <t>The narrative covers:</t>
-        </is>
-      </c>
-    </row>
-    <row r="345" ht="15" customHeight="1">
-      <c r="A345" s="36" t="inlineStr">
-        <is>
-          <t>1. **Volume statement** — total events reviewed, period covered, events escalated</t>
-        </is>
-      </c>
-    </row>
-    <row r="346" ht="15" customHeight="1">
-      <c r="A346" s="36" t="inlineStr">
-        <is>
-          <t>2. **Key findings** — one sentence per significant rule triggered (max 4 findings),</t>
-        </is>
-      </c>
-    </row>
-    <row r="347" ht="15" customHeight="1">
-      <c r="A347" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   naming the user, record, and action type involved</t>
-        </is>
-      </c>
-    </row>
-    <row r="348" ht="15" customHeight="1">
-      <c r="A348" s="36" t="inlineStr">
-        <is>
-          <t>3. **Overall risk assessment** — concludes with one of five risk levels:</t>
-        </is>
-      </c>
-    </row>
-    <row r="349" ht="15" customHeight="1">
-      <c r="A349" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - High risk — 2+ Critical findings</t>
-        </is>
-      </c>
-    </row>
-    <row r="350" ht="15" customHeight="1">
-      <c r="A350" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Moderate-to-high risk — 1 Critical finding</t>
-        </is>
-      </c>
-    </row>
-    <row r="351" ht="15" customHeight="1">
-      <c r="A351" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Moderate risk — 3+ High findings</t>
-        </is>
-      </c>
-    </row>
-    <row r="352" ht="15" customHeight="1">
-      <c r="A352" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Low-to-moderate risk — 1–2 High findings</t>
-        </is>
-      </c>
-    </row>
-    <row r="353" ht="15" customHeight="1">
-      <c r="A353" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Low risk — no Critical or High findings</t>
-        </is>
-      </c>
-    </row>
-    <row r="354" ht="15" customHeight="1">
-      <c r="A354" s="36" t="inlineStr"/>
-    </row>
-    <row r="355" ht="15" customHeight="1">
-      <c r="A355" s="36" t="inlineStr">
-        <is>
-          <t>The narrative is intended to be copied into the introduction of the Periodic Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="356" ht="15" customHeight="1">
-      <c r="A356" s="36" t="inlineStr">
-        <is>
-          <t>Report Section 9.1.6 or used as a management summary.</t>
         </is>
       </c>
     </row>
     <row r="357" ht="15" customHeight="1">
       <c r="A357" s="36" t="inlineStr"/>
     </row>
-    <row r="358" ht="8" customHeight="1">
-      <c r="A358" s="38" t="inlineStr">
-        <is>
-          <t>---</t>
+    <row r="358" ht="18" customHeight="1">
+      <c r="A358" s="35" t="inlineStr">
+        <is>
+          <t>## Review Narrative (Summary Sheet)</t>
         </is>
       </c>
     </row>
     <row r="359" ht="15" customHeight="1">
       <c r="A359" s="36" t="inlineStr"/>
     </row>
-    <row r="360" ht="8" customHeight="1">
-      <c r="A360" s="38" t="inlineStr">
-        <is>
-          <t>---</t>
+    <row r="360" ht="15" customHeight="1">
+      <c r="A360" s="36" t="inlineStr">
+        <is>
+          <t>Following the detection analysis, the Summary sheet includes a **Review Narrative**</t>
         </is>
       </c>
     </row>
     <row r="361" ht="15" customHeight="1">
-      <c r="A361" s="36" t="inlineStr"/>
-    </row>
-    <row r="362" ht="18" customHeight="1">
-      <c r="A362" s="35" t="inlineStr">
-        <is>
-          <t>## Not Yet Implemented — Planned Rules</t>
+      <c r="A361" s="36" t="inlineStr">
+        <is>
+          <t>section — a plain-English paragraph summarising the key findings of the review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="362" ht="15" customHeight="1">
+      <c r="A362" s="36" t="inlineStr">
+        <is>
+          <t>This section is generated deterministically from the scored data with no LLM</t>
         </is>
       </c>
     </row>
     <row r="363" ht="15" customHeight="1">
-      <c r="A363" s="36" t="inlineStr"/>
+      <c r="A363" s="36" t="inlineStr">
+        <is>
+          <t>involvement, making it fully reproducible.</t>
+        </is>
+      </c>
     </row>
     <row r="364" ht="15" customHeight="1">
-      <c r="A364" s="36" t="inlineStr">
-        <is>
-          <t>These checks were designed and scoped but not yet built into the engine.</t>
-        </is>
-      </c>
+      <c r="A364" s="36" t="inlineStr"/>
     </row>
     <row r="365" ht="15" customHeight="1">
       <c r="A365" s="36" t="inlineStr">
         <is>
-          <t>They are documented here for transparency and future CSV planning.</t>
+          <t>The narrative covers:</t>
         </is>
       </c>
     </row>
     <row r="366" ht="15" customHeight="1">
-      <c r="A366" s="36" t="inlineStr"/>
-    </row>
-    <row r="367" ht="18" customHeight="1">
-      <c r="A367" s="35" t="inlineStr">
-        <is>
-          <t>### Planned Rule 16 — Shared Account / Same User, Two Locations</t>
+      <c r="A366" s="36" t="inlineStr">
+        <is>
+          <t>1. **Volume statement** — total events reviewed, period covered, events escalated</t>
+        </is>
+      </c>
+    </row>
+    <row r="367" ht="15" customHeight="1">
+      <c r="A367" s="36" t="inlineStr">
+        <is>
+          <t>2. **Key findings** — one sentence per significant rule triggered (max 4 findings),</t>
         </is>
       </c>
     </row>
     <row r="368" ht="15" customHeight="1">
-      <c r="A368" s="37" t="inlineStr">
-        <is>
-          <t>**What it detects:** The same user_id performing actions from two different</t>
+      <c r="A368" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   naming the user, record, and action type involved</t>
         </is>
       </c>
     </row>
     <row r="369" ht="15" customHeight="1">
       <c r="A369" s="36" t="inlineStr">
         <is>
-          <t>IP addresses within 30 minutes — physically impossible for one person.</t>
+          <t>3. **Overall risk assessment** — concludes with one of five risk levels:</t>
         </is>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
-      <c r="A370" s="37" t="inlineStr">
-        <is>
-          <t>**Why not yet built:** Requires an IP address or workstation column in the</t>
+      <c r="A370" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - High risk — 2+ Critical findings</t>
         </is>
       </c>
     </row>
     <row r="371" ht="15" customHeight="1">
       <c r="A371" s="36" t="inlineStr">
         <is>
-          <t>audit trail export. Many systems do not include this by default. Will be</t>
+          <t xml:space="preserve">   - Moderate-to-high risk — 1 Critical finding</t>
         </is>
       </c>
     </row>
     <row r="372" ht="15" customHeight="1">
       <c r="A372" s="36" t="inlineStr">
         <is>
-          <t>activated automatically when the column mapper detects an IP column.</t>
+          <t xml:space="preserve">   - Moderate risk — 3+ High findings</t>
         </is>
       </c>
     </row>
     <row r="373" ht="15" customHeight="1">
-      <c r="A373" s="37" t="inlineStr">
-        <is>
-          <t>**Regulatory basis:** 21 CFR Part 11 §11.300.</t>
+      <c r="A373" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Low-to-moderate risk — 1–2 High findings</t>
         </is>
       </c>
     </row>
     <row r="374" ht="15" customHeight="1">
-      <c r="A374" s="36" t="inlineStr"/>
-    </row>
-    <row r="375" ht="18" customHeight="1">
-      <c r="A375" s="35" t="inlineStr">
-        <is>
-          <t>### Planned Rule 17 — Bulk Export Before Departure</t>
-        </is>
-      </c>
+      <c r="A374" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Low risk — no Critical or High findings</t>
+        </is>
+      </c>
+    </row>
+    <row r="375" ht="15" customHeight="1">
+      <c r="A375" s="36" t="inlineStr"/>
     </row>
     <row r="376" ht="15" customHeight="1">
-      <c r="A376" s="37" t="inlineStr">
-        <is>
-          <t>**What it detects:** A user exporting or printing large volumes of records</t>
+      <c r="A376" s="36" t="inlineStr">
+        <is>
+          <t>The narrative is intended to be copied into the introduction of the Periodic Review</t>
         </is>
       </c>
     </row>
     <row r="377" ht="15" customHeight="1">
       <c r="A377" s="36" t="inlineStr">
         <is>
-          <t>(SELECT, EXPORT, PRINT actions) close to their account deactivation date.</t>
+          <t>Report Section 9.1.6 or used as a management summary.</t>
         </is>
       </c>
     </row>
     <row r="378" ht="15" customHeight="1">
-      <c r="A378" s="37" t="inlineStr">
-        <is>
-          <t>**Why not yet built:** Requires an HR termination date as a second input file.</t>
-        </is>
-      </c>
-    </row>
-    <row r="379" ht="15" customHeight="1">
-      <c r="A379" s="36" t="inlineStr">
-        <is>
-          <t>Cannot be determined from the audit trail alone.</t>
+      <c r="A378" s="36" t="inlineStr"/>
+    </row>
+    <row r="379" ht="8" customHeight="1">
+      <c r="A379" s="38" t="inlineStr">
+        <is>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1">
-      <c r="A380" s="37" t="inlineStr">
-        <is>
-          <t>**Regulatory basis:** Data protection and confidentiality requirements.</t>
-        </is>
-      </c>
-    </row>
-    <row r="381" ht="15" customHeight="1">
-      <c r="A381" s="36" t="inlineStr"/>
-    </row>
-    <row r="382" ht="18" customHeight="1">
-      <c r="A382" s="35" t="inlineStr">
-        <is>
-          <t>### Planned Rule 18 — Activity During Approved Maintenance Window</t>
-        </is>
-      </c>
+      <c r="A380" s="36" t="inlineStr"/>
+    </row>
+    <row r="381" ht="18" customHeight="1">
+      <c r="A381" s="35" t="inlineStr">
+        <is>
+          <t>## Not Yet Implemented — Planned Rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="382" ht="15" customHeight="1">
+      <c r="A382" s="36" t="inlineStr"/>
     </row>
     <row r="383" ht="15" customHeight="1">
-      <c r="A383" s="37" t="inlineStr">
-        <is>
-          <t>**What it detects:** User activity during a scheduled system maintenance</t>
+      <c r="A383" s="36" t="inlineStr">
+        <is>
+          <t>These checks were designed and scoped but not yet built into the engine.</t>
         </is>
       </c>
     </row>
     <row r="384" ht="15" customHeight="1">
       <c r="A384" s="36" t="inlineStr">
         <is>
-          <t>window, indicating either the maintenance did not occur as planned, or</t>
+          <t>They are documented here for transparency and future CSV planning.</t>
         </is>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
-      <c r="A385" s="36" t="inlineStr">
-        <is>
-          <t>unauthorised activity occurred during the maintenance period.</t>
-        </is>
-      </c>
-    </row>
-    <row r="386" ht="15" customHeight="1">
-      <c r="A386" s="37" t="inlineStr">
-        <is>
-          <t>**Why not yet built:** Requires the approved maintenance schedule (from the</t>
+      <c r="A385" s="36" t="inlineStr"/>
+    </row>
+    <row r="386" ht="18" customHeight="1">
+      <c r="A386" s="35" t="inlineStr">
+        <is>
+          <t>### Planned — Shared Account / Concurrent Location Conflict</t>
         </is>
       </c>
     </row>
     <row r="387" ht="15" customHeight="1">
-      <c r="A387" s="36" t="inlineStr">
-        <is>
-          <t>change control system) as a second input file.</t>
+      <c r="A387" s="37" t="inlineStr">
+        <is>
+          <t>**What it detects:** The same user_id performing actions from two different</t>
         </is>
       </c>
     </row>
     <row r="388" ht="15" customHeight="1">
-      <c r="A388" s="37" t="inlineStr">
-        <is>
-          <t>**Regulatory basis:** 21 CFR Part 11 §11.10(e).</t>
+      <c r="A388" s="36" t="inlineStr">
+        <is>
+          <t>IP addresses within 30 minutes — physically impossible for one person.</t>
         </is>
       </c>
     </row>
     <row r="389" ht="15" customHeight="1">
-      <c r="A389" s="36" t="inlineStr"/>
-    </row>
-    <row r="390" ht="18" customHeight="1">
-      <c r="A390" s="35" t="inlineStr">
-        <is>
-          <t>### Planned Rule 19 — Account Created and Used Same Day</t>
+      <c r="A389" s="37" t="inlineStr">
+        <is>
+          <t>**Why not yet built:** Requires an IP address or workstation column in the</t>
+        </is>
+      </c>
+    </row>
+    <row r="390" ht="15" customHeight="1">
+      <c r="A390" s="36" t="inlineStr">
+        <is>
+          <t>audit trail export. Many systems do not include this by default. Will be</t>
         </is>
       </c>
     </row>
     <row r="391" ht="15" customHeight="1">
-      <c r="A391" s="37" t="inlineStr">
-        <is>
-          <t>**What it detects:** A new user account that is created and then used to</t>
+      <c r="A391" s="36" t="inlineStr">
+        <is>
+          <t>activated automatically when the column mapper detects an IP column.</t>
         </is>
       </c>
     </row>
     <row r="392" ht="15" customHeight="1">
-      <c r="A392" s="36" t="inlineStr">
-        <is>
-          <t>perform GxP data actions on the same day, before training records could</t>
+      <c r="A392" s="37" t="inlineStr">
+        <is>
+          <t>**Regulatory basis:** 21 CFR Part 11 §11.300.</t>
         </is>
       </c>
     </row>
     <row r="393" ht="15" customHeight="1">
-      <c r="A393" s="36" t="inlineStr">
-        <is>
-          <t>have been completed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="394" ht="15" customHeight="1">
-      <c r="A394" s="37" t="inlineStr">
-        <is>
-          <t>**Why not yet built:** Requires a user account creation log or training</t>
+      <c r="A393" s="36" t="inlineStr"/>
+    </row>
+    <row r="394" ht="18" customHeight="1">
+      <c r="A394" s="35" t="inlineStr">
+        <is>
+          <t>### Planned — Bulk Export Before Departure</t>
         </is>
       </c>
     </row>
     <row r="395" ht="15" customHeight="1">
-      <c r="A395" s="36" t="inlineStr">
-        <is>
-          <t>completion record as a second input file to confirm training status.</t>
+      <c r="A395" s="37" t="inlineStr">
+        <is>
+          <t>**What it detects:** A user exporting or printing large volumes of records</t>
         </is>
       </c>
     </row>
     <row r="396" ht="15" customHeight="1">
-      <c r="A396" s="37" t="inlineStr">
-        <is>
-          <t>**Regulatory basis:** 21 CFR Part 11 §11.10(i) — training.</t>
+      <c r="A396" s="36" t="inlineStr">
+        <is>
+          <t>(SELECT, EXPORT, PRINT actions) close to their account deactivation date.</t>
         </is>
       </c>
     </row>
     <row r="397" ht="15" customHeight="1">
-      <c r="A397" s="36" t="inlineStr"/>
-    </row>
-    <row r="398" ht="8" customHeight="1">
-      <c r="A398" s="38" t="inlineStr">
-        <is>
-          <t>---</t>
+      <c r="A397" s="37" t="inlineStr">
+        <is>
+          <t>**Why not yet built:** Requires an HR termination date as a second input file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="398" ht="15" customHeight="1">
+      <c r="A398" s="36" t="inlineStr">
+        <is>
+          <t>Cannot be determined from the audit trail alone.</t>
         </is>
       </c>
     </row>
     <row r="399" ht="15" customHeight="1">
-      <c r="A399" s="36" t="inlineStr"/>
-    </row>
-    <row r="400" ht="18" customHeight="1">
-      <c r="A400" s="35" t="inlineStr">
-        <is>
-          <t>## Validation Evidence</t>
-        </is>
-      </c>
-    </row>
-    <row r="401" ht="15" customHeight="1">
-      <c r="A401" s="36" t="inlineStr"/>
+      <c r="A399" s="37" t="inlineStr">
+        <is>
+          <t>**Regulatory basis:** Data protection and confidentiality requirements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="400" ht="15" customHeight="1">
+      <c r="A400" s="36" t="inlineStr"/>
+    </row>
+    <row r="401" ht="18" customHeight="1">
+      <c r="A401" s="35" t="inlineStr">
+        <is>
+          <t>### Planned — Activity During Approved Maintenance Window</t>
+        </is>
+      </c>
     </row>
     <row r="402" ht="15" customHeight="1">
-      <c r="A402" s="36" t="inlineStr">
-        <is>
-          <t>This document constitutes part of the functional specification for the</t>
+      <c r="A402" s="37" t="inlineStr">
+        <is>
+          <t>**What it detects:** User activity during a scheduled system maintenance</t>
         </is>
       </c>
     </row>
     <row r="403" ht="15" customHeight="1">
       <c r="A403" s="36" t="inlineStr">
         <is>
-          <t>Audit Trail Intelligence module. For Computer System Validation purposes,</t>
+          <t>window, indicating either the maintenance did not occur as planned, or</t>
         </is>
       </c>
     </row>
     <row r="404" ht="15" customHeight="1">
       <c r="A404" s="36" t="inlineStr">
         <is>
-          <t>the following test cases should be executed against the sample CSV template</t>
+          <t>unauthorised activity occurred during the maintenance period.</t>
         </is>
       </c>
     </row>
     <row r="405" ht="15" customHeight="1">
-      <c r="A405" s="36" t="inlineStr">
-        <is>
-          <t>(downloadable from the tool's upload screen) to verify each rule fires correctly:</t>
+      <c r="A405" s="37" t="inlineStr">
+        <is>
+          <t>**Why not yet built:** Requires the approved maintenance schedule (from the</t>
         </is>
       </c>
     </row>
     <row r="406" ht="15" customHeight="1">
-      <c r="A406" s="36" t="inlineStr"/>
+      <c r="A406" s="36" t="inlineStr">
+        <is>
+          <t>change control system) as a second input file.</t>
+        </is>
+      </c>
     </row>
     <row r="407" ht="15" customHeight="1">
       <c r="A407" s="37" t="inlineStr">
         <is>
-          <t>| Test Case | Expected Rule | Expected Tier |</t>
+          <t>**Regulatory basis:** 21 CFR Part 11 §11.10(e).</t>
         </is>
       </c>
     </row>
     <row r="408" ht="15" customHeight="1">
-      <c r="A408" s="36" t="inlineStr">
-        <is>
-          <t>|---|---|---|</t>
-        </is>
-      </c>
-    </row>
-    <row r="409" ht="15" customHeight="1">
-      <c r="A409" s="37" t="inlineStr">
-        <is>
-          <t>| UPDATE RESULTS with comment "fixed" | Rule 1 | High |</t>
+      <c r="A408" s="36" t="inlineStr"/>
+    </row>
+    <row r="409" ht="18" customHeight="1">
+      <c r="A409" s="35" t="inlineStr">
+        <is>
+          <t>### Planned — Account Created and Used Same Day</t>
         </is>
       </c>
     </row>
     <row r="410" ht="15" customHeight="1">
       <c r="A410" s="37" t="inlineStr">
         <is>
-          <t>| 12 RESULT_INSERT in 12 minutes, same user | Rule 2 | Medium |</t>
+          <t>**What it detects:** A new user account that is created and then used to</t>
         </is>
       </c>
     </row>
     <row r="411" ht="15" customHeight="1">
-      <c r="A411" s="37" t="inlineStr">
-        <is>
-          <t>| admin_sys INSERT BATCH_RELEASE | Rule 3 | Critical |</t>
+      <c r="A411" s="36" t="inlineStr">
+        <is>
+          <t>perform GxP data actions on the same day, before training records could</t>
         </is>
       </c>
     </row>
     <row r="412" ht="15" customHeight="1">
-      <c r="A412" s="37" t="inlineStr">
-        <is>
-          <t>| new_value = 147.3 when mean ≈ 7.1 | Rule 4 | High |</t>
+      <c r="A412" s="36" t="inlineStr">
+        <is>
+          <t>have been completed.</t>
         </is>
       </c>
     </row>
     <row r="413" ht="15" customHeight="1">
       <c r="A413" s="37" t="inlineStr">
         <is>
-          <t>| 3x LOGIN_FAILED → LOGIN → DELETE, 18 min | Rule 5 | Critical |</t>
+          <t>**Why not yet built:** Requires a user account creation log or training</t>
         </is>
       </c>
     </row>
     <row r="414" ht="15" customHeight="1">
-      <c r="A414" s="37" t="inlineStr">
-        <is>
-          <t>| DELETE then INSERT same record_id, 3 min | Rule 6 | Critical |</t>
+      <c r="A414" s="36" t="inlineStr">
+        <is>
+          <t>completion record as a second input file to confirm training status.</t>
         </is>
       </c>
     </row>
     <row r="415" ht="15" customHeight="1">
       <c r="A415" s="37" t="inlineStr">
         <is>
-          <t>| UPDATE AUDIT_TRAIL, new_value = DISABLED | Rule 7 | Critical |</t>
+          <t>**Regulatory basis:** 21 CFR Part 11 §11.10(i) — training.</t>
         </is>
       </c>
     </row>
     <row r="416" ht="15" customHeight="1">
-      <c r="A416" s="37" t="inlineStr">
-        <is>
-          <t>| admin_sys DELETE RESULTS | Rule 8 | High |</t>
-        </is>
-      </c>
-    </row>
-    <row r="417" ht="15" customHeight="1">
-      <c r="A417" s="37" t="inlineStr">
-        <is>
-          <t>| Same user, same action, 5+ times in 60 min | Rule 2 | Medium |</t>
+      <c r="A416" s="36" t="inlineStr"/>
+    </row>
+    <row r="417" ht="8" customHeight="1">
+      <c r="A417" s="38" t="inlineStr">
+        <is>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="418" ht="15" customHeight="1">
-      <c r="A418" s="37" t="inlineStr">
-        <is>
-          <t>| &gt;2 hour gap in timestamps | Rule 9 | High |</t>
-        </is>
-      </c>
-    </row>
-    <row r="419" ht="15" customHeight="1">
-      <c r="A419" s="37" t="inlineStr">
-        <is>
-          <t>| Timestamp 02:14 AM weekday | Rule 10 | High |</t>
+      <c r="A418" s="36" t="inlineStr"/>
+    </row>
+    <row r="419" ht="18" customHeight="1">
+      <c r="A419" s="35" t="inlineStr">
+        <is>
+          <t>## Validation Evidence</t>
         </is>
       </c>
     </row>
     <row r="420" ht="15" customHeight="1">
-      <c r="A420" s="37" t="inlineStr">
-        <is>
-          <t>| Any event on 2024-07-04 | Rule 10 (Holiday) | Medium-High |</t>
-        </is>
-      </c>
+      <c r="A420" s="36" t="inlineStr"/>
     </row>
     <row r="421" ht="15" customHeight="1">
-      <c r="A421" s="37" t="inlineStr">
-        <is>
-          <t>| Approval timestamp before creation, same record | Rule 11 | Critical |</t>
+      <c r="A421" s="36" t="inlineStr">
+        <is>
+          <t>This document constitutes part of the functional specification for the</t>
         </is>
       </c>
     </row>
     <row r="422" ht="15" customHeight="1">
-      <c r="A422" s="37" t="inlineStr">
-        <is>
-          <t>| svc_batch INSERT RESULTS | Rule 12 | Critical |</t>
+      <c r="A422" s="36" t="inlineStr">
+        <is>
+          <t>Audit Trail Intelligence module. For Computer System Validation purposes,</t>
         </is>
       </c>
     </row>
     <row r="423" ht="15" customHeight="1">
-      <c r="A423" s="37" t="inlineStr">
-        <is>
-          <t>| Same user, 90+ day gap, then GxP action | Rule 13 | High |</t>
+      <c r="A423" s="36" t="inlineStr">
+        <is>
+          <t>the following test cases should be executed against the sample CSV template</t>
         </is>
       </c>
     </row>
     <row r="424" ht="15" customHeight="1">
-      <c r="A424" s="37" t="inlineStr">
-        <is>
-          <t>| User with 50+ events performs first-ever DELETE | Rule 14 | High |</t>
+      <c r="A424" s="36" t="inlineStr">
+        <is>
+          <t>(downloadable from the tool's upload screen) to verify each rule fires correctly:</t>
         </is>
       </c>
     </row>
@@ -57579,28 +57579,150 @@
       <c r="A425" s="36" t="inlineStr"/>
     </row>
     <row r="426" ht="15" customHeight="1">
-      <c r="A426" s="36" t="inlineStr">
-        <is>
-          <t>*This document was generated by the Audit Trail Intelligence module and</t>
+      <c r="A426" s="37" t="inlineStr">
+        <is>
+          <t>| Test Case | Expected Rule | Expected Tier |</t>
         </is>
       </c>
     </row>
     <row r="427" ht="15" customHeight="1">
       <c r="A427" s="36" t="inlineStr">
         <is>
+          <t>|---|---|---|</t>
+        </is>
+      </c>
+    </row>
+    <row r="428" ht="15" customHeight="1">
+      <c r="A428" s="37" t="inlineStr">
+        <is>
+          <t>| UPDATE RESULTS with comment "fixed" | Rule 1 | High |</t>
+        </is>
+      </c>
+    </row>
+    <row r="429" ht="15" customHeight="1">
+      <c r="A429" s="37" t="inlineStr">
+        <is>
+          <t>| 12 RESULT_INSERT in 12 minutes, same user | Rule 2 | Medium |</t>
+        </is>
+      </c>
+    </row>
+    <row r="430" ht="15" customHeight="1">
+      <c r="A430" s="37" t="inlineStr">
+        <is>
+          <t>| admin_sys INSERT BATCH_RELEASE | Rule 3 | Critical |</t>
+        </is>
+      </c>
+    </row>
+    <row r="431" ht="15" customHeight="1">
+      <c r="A431" s="37" t="inlineStr">
+        <is>
+          <t>| new_value = 147.3 when mean ≈ 7.1 | Rule 4 | High |</t>
+        </is>
+      </c>
+    </row>
+    <row r="432" ht="15" customHeight="1">
+      <c r="A432" s="37" t="inlineStr">
+        <is>
+          <t>| 3x LOGIN_FAILED → LOGIN → DELETE, 18 min | Rule 5 | Critical |</t>
+        </is>
+      </c>
+    </row>
+    <row r="433" ht="15" customHeight="1">
+      <c r="A433" s="37" t="inlineStr">
+        <is>
+          <t>| DELETE then INSERT same record_id, 3 min | Rule 6 | Critical |</t>
+        </is>
+      </c>
+    </row>
+    <row r="434" ht="15" customHeight="1">
+      <c r="A434" s="37" t="inlineStr">
+        <is>
+          <t>| UPDATE AUDIT_TRAIL, new_value = DISABLED | Rule 7 | Critical |</t>
+        </is>
+      </c>
+    </row>
+    <row r="435" ht="15" customHeight="1">
+      <c r="A435" s="37" t="inlineStr">
+        <is>
+          <t>| admin_sys DELETE RESULTS | Rule 8 | High |</t>
+        </is>
+      </c>
+    </row>
+    <row r="436" ht="15" customHeight="1">
+      <c r="A436" s="37" t="inlineStr">
+        <is>
+          <t>| &gt;2 hour gap in timestamps | Rule 9 | High |</t>
+        </is>
+      </c>
+    </row>
+    <row r="437" ht="15" customHeight="1">
+      <c r="A437" s="37" t="inlineStr">
+        <is>
+          <t>| Timestamp 02:14 AM weekday | Rule 10 | High |</t>
+        </is>
+      </c>
+    </row>
+    <row r="438" ht="15" customHeight="1">
+      <c r="A438" s="37" t="inlineStr">
+        <is>
+          <t>| Any event on 2024-07-04 | Rule 10 (Holiday) | Medium-High |</t>
+        </is>
+      </c>
+    </row>
+    <row r="439" ht="15" customHeight="1">
+      <c r="A439" s="37" t="inlineStr">
+        <is>
+          <t>| Approval timestamp before creation, same record | Rule 11 | Critical |</t>
+        </is>
+      </c>
+    </row>
+    <row r="440" ht="15" customHeight="1">
+      <c r="A440" s="37" t="inlineStr">
+        <is>
+          <t>| svc_batch INSERT RESULTS | Rule 12 | Critical |</t>
+        </is>
+      </c>
+    </row>
+    <row r="441" ht="15" customHeight="1">
+      <c r="A441" s="37" t="inlineStr">
+        <is>
+          <t>| Same user, 90+ day gap, then GxP action | Rule 13 | High |</t>
+        </is>
+      </c>
+    </row>
+    <row r="442" ht="15" customHeight="1">
+      <c r="A442" s="37" t="inlineStr">
+        <is>
+          <t>| User with 50+ events performs first-ever DELETE | Rule 14 | High |</t>
+        </is>
+      </c>
+    </row>
+    <row r="443" ht="15" customHeight="1">
+      <c r="A443" s="36" t="inlineStr"/>
+    </row>
+    <row r="444" ht="15" customHeight="1">
+      <c r="A444" s="36" t="inlineStr">
+        <is>
+          <t>*This document was generated by the Audit Trail Intelligence module and</t>
+        </is>
+      </c>
+    </row>
+    <row r="445" ht="15" customHeight="1">
+      <c r="A445" s="36" t="inlineStr">
+        <is>
           <t>represents the validated detection logic at the time of this release.</t>
         </is>
       </c>
     </row>
-    <row r="428" ht="15" customHeight="1">
-      <c r="A428" s="36" t="inlineStr">
+    <row r="446" ht="15" customHeight="1">
+      <c r="A446" s="36" t="inlineStr">
         <is>
           <t>Review and approve as part of the Computer System Validation package.*</t>
         </is>
       </c>
     </row>
-    <row r="429" ht="15" customHeight="1">
-      <c r="A429" s="36" t="inlineStr"/>
+    <row r="447" ht="15" customHeight="1">
+      <c r="A447" s="36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
